--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -2581,25 +2581,25 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="J32" t="n">
         <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4926019487549621</v>
+        <v>0.5022421524663677</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2674124864669794</v>
+        <v>0.2654708520179372</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2399855647780585</v>
+        <v>0.2322869955156951</v>
       </c>
       <c r="O32" t="n">
-        <v>0.06844033159822627</v>
+        <v>0.07625482625482616</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
@@ -2617,19 +2617,19 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0.2904844870607921</v>
+        <v>0.2808442833493865</v>
       </c>
       <c r="V32" t="n">
         <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>0.2904844870607921</v>
+        <v>0.2808442833493865</v>
       </c>
       <c r="X32" t="n">
         <v>0.7830864358157542</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB32"/>
+  <dimension ref="A1:AB42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,27 +572,27 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>zuzbQnCF</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45527.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>hallescher</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>st  pauli</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>59</v>
       </c>
       <c r="F2" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -601,62 +601,96 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1975093616650701</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.223373682835496</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.579116955499434</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.06590550450199562</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.06933647147111377</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.3855435714454001</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.5451199570834862</v>
+      </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>-0.03399699841594783</v>
+      </c>
       <c r="V2" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.03399699841594783</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.5451199570834862</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.62</v>
+      </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.65058346814375</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3.65058346814375</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45528.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wehen</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>werder bremen</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -665,76 +699,96 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.4308880308880309</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.2633204633204634</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.3057915057915058</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.05490387748452252</v>
+      </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0971796147990323</v>
+        <v>0.2899334504434845</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1193467756926307</v>
+        <v>0.3943982079165658</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7834736095083371</v>
+        <v>0.3156683416399498</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>0.1310777445961024</v>
+      </c>
       <c r="V3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.1310777445961024</v>
+      </c>
       <c r="X3" t="n">
-        <v>0.2165263904916629</v>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+        <v>0.3943982079165658</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.6</v>
+      </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>1.450043520282718</v>
+        <v>2.641223383911499</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.450043520282718</v>
+        <v>2.641223383911499</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>GbeXvnR8</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45528.4375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>wurzburger kickers</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>stuttgart</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>59</v>
       </c>
       <c r="F4" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -743,62 +797,96 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.2906808305166586</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.269917914051183</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4394012554321584</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0585228724763609</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.2294938040551285</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.4516619673405217</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.3188442286043498</v>
+      </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>0.1817440532893387</v>
+      </c>
       <c r="V4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1817440532893387</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.4516619673405217</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.5</v>
+      </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.024709863832906</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>3.024709863832906</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>O48oHrZ1</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45520.65625</v>
+        <v>45528.4375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ulm</t>
+          <t>hoffenheim</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>holstein kiel</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -807,62 +895,96 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5746381507885073</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.225750702095485</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1996111471160078</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.05468215994531778</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5782851363207071</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.2848988261201276</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.1368160375591653</v>
+      </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>0.003646985532199776</v>
+      </c>
       <c r="V5" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.003646985532199776</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.5782851363207071</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.65</v>
+      </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.872685509113203</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>3.872685509113203</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>2FREIeA6</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45528.4375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>aue</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>b  monchengladbach</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -871,62 +993,96 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4759511844938981</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2799712849964106</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.2440775305096913</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.05052790346907998</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.2053091059252788</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.4241474100852874</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.3705434839894338</v>
+      </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>0.1441761250888768</v>
+      </c>
       <c r="V6" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1441761250888768</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.4241474100852874</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.4</v>
+      </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.840449158378914</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.840449158378914</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>dfO6OQtS</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45528.4375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>schott mainz</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>greuther furth</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -935,62 +1091,96 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.7099057574385776</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1642042882423145</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1258899543191078</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.05912607605971454</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.6288231773237837</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.2650511246634477</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.1061256980127687</v>
+      </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>-0.08108258011479397</v>
+      </c>
       <c r="V7" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.08108258011479397</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.6288231773237837</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.33</v>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.211130900078676</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.211130900078676</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>SxFxJ44k</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45528.5625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>aalen</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>schalke</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>59</v>
       </c>
       <c r="F8" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -999,62 +1189,96 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5503745604647607</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.238036997401009</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2115884421342302</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.05025690430314711</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.3990590270826507</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3278136837514093</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.2731272891659399</v>
+      </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="n">
+        <v>-0.15131553338211</v>
+      </c>
       <c r="V8" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.15131553338211</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.6009409729173493</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.117647058823529</v>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
+      <c r="AA8" t="n">
+        <v>4.024408118902008</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4.024408118902008</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>t0w6KHuf</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45529.4375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>greifswald</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1063,62 +1287,96 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.6315789473684211</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.05555555555555536</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.1278847175422664</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.4167325819505354</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.4553827005071984</v>
+      </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="n">
+        <v>-0.1761962468612227</v>
+      </c>
       <c r="V9" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.1761962468612227</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.5446172994928016</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.571428571428571</v>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
+      <c r="AA9" t="n">
+        <v>3.647217248531267</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.647217248531267</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>AuVMGZvJ</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45529.52083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ingolstadt</t>
+          <t>st  pauli</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>kaiserslautern</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1127,55 +1385,89 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.4394012554321584</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.269917914051183</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2906808305166586</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0585228724763609</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1492421482679454</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.4113614740324936</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.4393963776995611</v>
+      </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="n">
+        <v>0.1487155471829025</v>
+      </c>
       <c r="V10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.1487155471829025</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.4393963776995611</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.25</v>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.942569119968215</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.942569119968215</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rw essen</t>
+          <t>hallescher</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>st  pauli</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1210,7 +1502,7 @@
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
@@ -1226,20 +1518,20 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>vfl osnabruck</t>
+          <t>wehen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1269,13 +1561,13 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.05890705866981628</v>
+        <v>0.09680829329283069</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0850825161689492</v>
+        <v>0.1189610364447533</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8560104251612345</v>
+        <v>0.784230670262416</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1286,7 +1578,7 @@
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>0.1439895748387655</v>
+        <v>0.215769329737584</v>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr">
@@ -1295,29 +1587,29 @@
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>0.9642757610705874</v>
+        <v>1.444973602299881</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9642757610705874</v>
+        <v>1.444973602299881</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>villingen</t>
+          <t>wurzburger kickers</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>hoffenheim</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1352,7 +1644,7 @@
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
@@ -1368,20 +1660,20 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>lONsG15D</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45520.65625</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>alemannia aachen</t>
+          <t>ulm</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>holstein kiel</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1416,7 +1708,7 @@
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -1432,20 +1724,20 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45521.33333333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>arminia bielefeld</t>
+          <t>aue</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>hannover</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1480,7 +1772,7 @@
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
@@ -1496,20 +1788,20 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45521.33333333334</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>I1Vk6k3R</t>
+          <t>schott mainz</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>greuther furth</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1544,7 +1836,7 @@
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -1560,20 +1852,20 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45522.33333333334</v>
+        <v>45521.4375</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>saarbrucken</t>
+          <t>aalen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>nurnberg</t>
+          <t>schalke</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1608,7 +1900,7 @@
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -1624,20 +1916,20 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45522.33333333334</v>
+        <v>45521.4375</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>viktoria berlin</t>
+          <t>greifswald</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1672,7 +1964,7 @@
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
@@ -1688,20 +1980,20 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.4375</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bremer</t>
+          <t>ingolstadt</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>paderborn</t>
+          <t>kaiserslautern</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1736,7 +2028,7 @@
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
@@ -1752,20 +2044,20 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.4375</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>hansa rostock</t>
+          <t>rw essen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>hertha berlin</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1791,59 +2083,45 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.1794567954919975</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.1125722033075784</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.7079710012004241</v>
-      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr"/>
-      <c r="X20" t="n">
-        <v>0.2920289987995759</v>
-      </c>
+      <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
-      <c r="AA20" t="n">
-        <v>1.955672731081154</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.955672731081154</v>
-      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.4375</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>E3xs5mIe</t>
+          <t>vfl osnabruck</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>elversberg</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1869,45 +2147,59 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.05797259585987867</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.08443438111248826</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.857593023027633</v>
+      </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>-100</v>
+        <v>-2</v>
       </c>
       <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="n">
+        <v>0.142406976972367</v>
+      </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
+      <c r="AA21" t="n">
+        <v>0.9536773495967088</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9536773495967088</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.4375</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>regensburg</t>
+          <t>villingen</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>bochum</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1942,7 +2234,7 @@
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
@@ -1958,20 +2250,20 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>sandhausen</t>
+          <t>alemannia aachen</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>fc koln</t>
+          <t>holstein kiel</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2006,7 +2298,7 @@
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
@@ -2022,20 +2314,20 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>teutonia ottensen</t>
+          <t>arminia bielefeld</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>darmstadt</t>
+          <t>hannover</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2070,7 +2362,7 @@
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
@@ -2086,20 +2378,20 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45522.54166666666</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>lotte</t>
+          <t>I1Vk6k3R</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>karlsruher sc</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2134,7 +2426,7 @@
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
@@ -2150,20 +2442,20 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45522.54166666666</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>meppen</t>
+          <t>saarbrucken</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>hamburger sv</t>
+          <t>nurnberg</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2198,7 +2490,7 @@
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
@@ -2214,20 +2506,20 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45522.54166666666</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sg dynamo dresden</t>
+          <t>viktoria berlin</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>dusseldorf</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2262,7 +2554,7 @@
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
@@ -2278,20 +2570,20 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45523.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>cottbus</t>
+          <t>bremer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>paderborn</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2326,7 +2618,7 @@
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
@@ -2342,20 +2634,20 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45523.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>offenbach</t>
+          <t>hansa rostock</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>magdeburg</t>
+          <t>hertha berlin</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2381,45 +2673,59 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.1769161383950233</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.1067413001055537</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.716342561499423</v>
+      </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>-100</v>
+        <v>-2</v>
       </c>
       <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="n">
+        <v>0.283657438500577</v>
+      </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
+      <c r="AA29" t="n">
+        <v>1.899609695353013</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.899609695353013</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>EkP2bxvB</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45523.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>tus koblenz</t>
+          <t>E3xs5mIe</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>wolfsburg</t>
+          <t>elversberg</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2454,7 +2760,7 @@
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
@@ -2470,20 +2776,20 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>pAXo2Kvn</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45522.4375</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>braunschweig</t>
+          <t>regensburg</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2509,138 +2815,792 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0.03866522508709244</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.0701925108605358</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0.8911422640523718</v>
-      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="W31" t="inlineStr"/>
-      <c r="X31" t="n">
-        <v>0.1088577359476282</v>
-      </c>
+      <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
-      <c r="AA31" t="n">
-        <v>0.7290033066411972</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0.7290033066411972</v>
-      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
+          <t>tvOIPExA</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>sandhausen</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>fc koln</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>59</v>
+      </c>
+      <c r="F32" t="n">
+        <v>593</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>teutonia ottensen</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>darmstadt</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>59</v>
+      </c>
+      <c r="F33" t="n">
+        <v>593</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45522.54166666666</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>lotte</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>karlsruher sc</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>59</v>
+      </c>
+      <c r="F34" t="n">
+        <v>593</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45522.54166666666</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>meppen</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>hamburger sv</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>59</v>
+      </c>
+      <c r="F35" t="n">
+        <v>593</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45522.54166666666</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sg dynamo dresden</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>dusseldorf</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>59</v>
+      </c>
+      <c r="F36" t="n">
+        <v>593</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45523.54166666666</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>cottbus</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>werder bremen</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>59</v>
+      </c>
+      <c r="F37" t="n">
+        <v>593</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45523.54166666666</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>offenbach</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>magdeburg</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>59</v>
+      </c>
+      <c r="F38" t="n">
+        <v>593</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45523.54166666666</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>tus koblenz</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>wolfsburg</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>59</v>
+      </c>
+      <c r="F39" t="n">
+        <v>593</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45523.65625</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>braunschweig</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>eintracht frankfurt</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>59</v>
+      </c>
+      <c r="F40" t="n">
+        <v>593</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.03481419666434622</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.07188856293285911</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.8932972404027947</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="n">
+        <v>0.1067027595972053</v>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.7145717655888678</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.7145717655888678</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>W67CmLPh</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>preussen munster</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>59</v>
+      </c>
+      <c r="F41" t="n">
+        <v>593</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.2702975615649746</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.1088186248565082</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.6208838135785172</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="n">
+        <v>0.3791161864214828</v>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.538882065629469</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>2.538882065629469</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B42" s="2" t="n">
         <v>45521.64583333334</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>bayer leverkusen</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>stuttgart</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>59</v>
-      </c>
-      <c r="F32" t="n">
+      <c r="E42" t="n">
+        <v>59</v>
+      </c>
+      <c r="F42" t="n">
         <v>594</v>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>super cup</t>
         </is>
       </c>
-      <c r="I32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="J32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.5022421524663677</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.2654708520179372</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.2322869955156951</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.07625482625482616</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.7830864358157542</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.04088231273115332</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.1760312514530925</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.2808442833493865</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0.2808442833493865</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0.7830864358157542</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z32" t="inlineStr">
+      <c r="I42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.5157232704402516</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.2578616352201258</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.2264150943396226</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.07723577235772372</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.7850213839801177</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.04098582600164608</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.1739927900182362</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.2692981135398661</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.2692981135398661</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.7850213839801177</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z42" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
-      <c r="AA32" t="n">
-        <v>5.24420792078758</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>5.24420792078758</v>
+      <c r="AA42" t="n">
+        <v>5.257165967339999</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>5.257165967339999</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB42"/>
+  <dimension ref="A1:AB33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,27 +670,27 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>hallescher</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>st  pauli</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -699,96 +699,62 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.4308880308880309</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.2633204633204634</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.3057915057915058</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.05490387748452252</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.2899334504434845</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.3943982079165658</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.3156683416399498</v>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
-        <v>0.1310777445961024</v>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
         <v>0</v>
       </c>
-      <c r="W3" t="n">
-        <v>0.1310777445961024</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.3943982079165658</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>3.6</v>
-      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.641223383911499</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.641223383911499</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>wehen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>stuttgart</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>59</v>
       </c>
       <c r="F4" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -797,96 +763,76 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.2906808305166586</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.269917914051183</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.4394012554321584</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.0585228724763609</v>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2294938040551285</v>
+        <v>0.09680829329283069</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4516619673405217</v>
+        <v>0.1189610364447533</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3188442286043498</v>
+        <v>0.784230670262416</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
-        <v>0.1817440532893387</v>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.1817440532893387</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>0.4516619673405217</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>3.5</v>
-      </c>
+        <v>0.215769329737584</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>3.024709863832906</v>
+        <v>1.444973602299881</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.024709863832906</v>
+        <v>1.444973602299881</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>wurzburger kickers</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>hoffenheim</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>holstein kiel</t>
-        </is>
-      </c>
       <c r="E5" t="n">
         <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -895,96 +841,62 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.5746381507885073</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.225750702095485</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.1996111471160078</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.05468215994531778</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.5782851363207071</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.2848988261201276</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.1368160375591653</v>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0.003646985532199776</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.003646985532199776</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.5782851363207071</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.65</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.872685509113203</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>3.872685509113203</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>lONsG15D</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45520.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>ulm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -993,96 +905,62 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.4759511844938981</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.2799712849964106</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.2440775305096913</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.05052790346907998</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.2053091059252788</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.4241474100852874</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.3705434839894338</v>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>0.1441761250888768</v>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
         <v>0</v>
       </c>
-      <c r="W6" t="n">
-        <v>0.1441761250888768</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.4241474100852874</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>3.4</v>
-      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.840449158378914</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.840449158378914</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45521.33333333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>aue</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>bochum</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1091,96 +969,62 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.7099057574385776</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.1642042882423145</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.1258899543191078</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.05912607605971454</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.6288231773237837</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.2650511246634477</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.1061256980127687</v>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>-0.08108258011479397</v>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.08108258011479397</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.6288231773237837</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.33</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA7" t="n">
-        <v>4.211130900078676</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>4.211130900078676</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45521.33333333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>schott mainz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>greuther furth</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>59</v>
       </c>
       <c r="F8" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1189,96 +1033,62 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.5503745604647607</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.238036997401009</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.2115884421342302</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.05025690430314711</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.3990590270826507</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.3278136837514093</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.2731272891659399</v>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>-0.15131553338211</v>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.15131553338211</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.6009409729173493</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.117647058823529</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
-      <c r="AA8" t="n">
-        <v>4.024408118902008</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>4.024408118902008</v>
-      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45529.4375</v>
+        <v>45521.4375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wolfsburg</t>
+          <t>aalen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>schalke</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1287,96 +1097,62 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.1578947368421053</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.2105263157894737</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.6315789473684211</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.05555555555555536</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.1278847175422664</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.4167325819505354</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.4553827005071984</v>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>-0.1761962468612227</v>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-2</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.1761962468612227</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.5446172994928016</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.571428571428571</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
-      <c r="AA9" t="n">
-        <v>3.647217248531267</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>3.647217248531267</v>
-      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45529.52083333334</v>
+        <v>45521.4375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>st  pauli</t>
+          <t>greifswald</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1385,89 +1161,55 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.4394012554321584</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.269917914051183</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.2906808305166586</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.0585228724763609</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.1492421482679454</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.4113614740324936</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.4393963776995611</v>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>0.1487155471829025</v>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>2</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.1487155471829025</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.4393963776995611</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>3.25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.942569119968215</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.942569119968215</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45521.4375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hallescher</t>
+          <t>ingolstadt</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>st  pauli</t>
+          <t>kaiserslautern</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1518,20 +1260,20 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45521.4375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>wehen</t>
+          <t>rw essen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1557,59 +1299,45 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.09680829329283069</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.1189610364447533</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.784230670262416</v>
-      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="n">
-        <v>0.215769329737584</v>
-      </c>
+      <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
-      <c r="AA12" t="n">
-        <v>1.444973602299881</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.444973602299881</v>
-      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45521.4375</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>wurzburger kickers</t>
+          <t>vfl osnabruck</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1635,45 +1363,59 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.05797259585987867</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.08443438111248826</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.857593023027633</v>
+      </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="n">
+        <v>0.142406976972367</v>
+      </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
+      <c r="AA13" t="n">
+        <v>0.9536773495967088</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9536773495967088</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45520.65625</v>
+        <v>45521.4375</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ulm</t>
+          <t>villingen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1724,20 +1466,20 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>aue</t>
+          <t>alemannia aachen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>b  monchengladbach</t>
+          <t>holstein kiel</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1788,20 +1530,20 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>schott mainz</t>
+          <t>arminia bielefeld</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>greuther furth</t>
+          <t>hannover</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1852,20 +1594,20 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>aalen</t>
+          <t>I1Vk6k3R</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>schalke</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1916,20 +1658,20 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>greifswald</t>
+          <t>saarbrucken</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>nurnberg</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1980,20 +1722,20 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ingolstadt</t>
+          <t>viktoria berlin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>kaiserslautern</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2044,20 +1786,20 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.4375</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rw essen</t>
+          <t>bremer</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>paderborn</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2108,20 +1850,20 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.4375</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>vfl osnabruck</t>
+          <t>hansa rostock</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>hertha berlin</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2151,13 +1893,13 @@
         <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.05797259585987867</v>
+        <v>0.1769161383950233</v>
       </c>
       <c r="R21" t="n">
-        <v>0.08443438111248826</v>
+        <v>0.1067413001055537</v>
       </c>
       <c r="S21" t="n">
-        <v>0.857593023027633</v>
+        <v>0.716342561499423</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
@@ -2168,7 +1910,7 @@
       </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="n">
-        <v>0.142406976972367</v>
+        <v>0.283657438500577</v>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr">
@@ -2177,29 +1919,29 @@
         </is>
       </c>
       <c r="AA21" t="n">
-        <v>0.9536773495967088</v>
+        <v>1.899609695353013</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9536773495967088</v>
+        <v>1.899609695353013</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.4375</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>villingen</t>
+          <t>E3xs5mIe</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>elversberg</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2250,20 +1992,20 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>alemannia aachen</t>
+          <t>regensburg</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>holstein kiel</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2314,20 +2056,20 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>arminia bielefeld</t>
+          <t>sandhausen</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>hannover</t>
+          <t>fc koln</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2378,20 +2120,20 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>KSwfVwAO</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>I1Vk6k3R</t>
+          <t>teutonia ottensen</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>darmstadt</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2442,20 +2184,20 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45522.33333333334</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>saarbrucken</t>
+          <t>lotte</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>nurnberg</t>
+          <t>karlsruher sc</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2506,20 +2248,20 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45522.33333333334</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>viktoria berlin</t>
+          <t>meppen</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>hamburger sv</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2570,20 +2312,20 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>bremer</t>
+          <t>sg dynamo dresden</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>paderborn</t>
+          <t>dusseldorf</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2634,20 +2376,20 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>hansa rostock</t>
+          <t>cottbus</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>hertha berlin</t>
+          <t>werder bremen</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2673,59 +2415,45 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.1769161383950233</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.1067413001055537</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0.716342561499423</v>
-      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="W29" t="inlineStr"/>
-      <c r="X29" t="n">
-        <v>0.283657438500577</v>
-      </c>
+      <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
-      <c r="AA29" t="n">
-        <v>1.899609695353013</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.899609695353013</v>
-      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>E3xs5mIe</t>
+          <t>offenbach</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>elversberg</t>
+          <t>magdeburg</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2776,20 +2504,20 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>regensburg</t>
+          <t>tus koblenz</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>bochum</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2840,20 +2568,20 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45523.65625</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sandhausen</t>
+          <t>braunschweig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>fc koln</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2879,52 +2607,66 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.03481419666434622</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.07188856293285911</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.8932972404027947</v>
+      </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="n">
+        <v>0.1067027595972053</v>
+      </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
+      <c r="AA32" t="n">
+        <v>0.7145717655888678</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.7145717655888678</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>fcxqFy2l</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>teutonia ottensen</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>darmstadt</t>
+          <t>stuttgart</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>59</v>
       </c>
       <c r="F33" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2933,673 +2675,69 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+          <t>super cup</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.5157232704402516</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.2578616352201258</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.2264150943396226</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.07723577235772372</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.7850213839801177</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.04098582600164608</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.1739927900182362</v>
+      </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
-      <c r="U33" t="inlineStr"/>
+      <c r="U33" t="n">
+        <v>0.2692981135398661</v>
+      </c>
       <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.2692981135398661</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.7850213839801177</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.8</v>
+      </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>45522.54166666666</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>lotte</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>karlsruher sc</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>59</v>
-      </c>
-      <c r="F34" t="n">
-        <v>593</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="n">
-        <v>1</v>
-      </c>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>45522.54166666666</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>meppen</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>hamburger sv</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>59</v>
-      </c>
-      <c r="F35" t="n">
-        <v>593</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="n">
-        <v>1</v>
-      </c>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>45522.54166666666</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>sg dynamo dresden</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>dusseldorf</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>59</v>
-      </c>
-      <c r="F36" t="n">
-        <v>593</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="n">
-        <v>1</v>
-      </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>45523.54166666666</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>cottbus</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>werder bremen</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>59</v>
-      </c>
-      <c r="F37" t="n">
-        <v>593</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="n">
-        <v>1</v>
-      </c>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>45523.54166666666</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>offenbach</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>magdeburg</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>59</v>
-      </c>
-      <c r="F38" t="n">
-        <v>593</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>45523.54166666666</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>tus koblenz</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>wolfsburg</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>59</v>
-      </c>
-      <c r="F39" t="n">
-        <v>593</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="n">
-        <v>1</v>
-      </c>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>45523.65625</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>braunschweig</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>eintracht frankfurt</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>59</v>
-      </c>
-      <c r="F40" t="n">
-        <v>593</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0.03481419666434622</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0.07188856293285911</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0.8932972404027947</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1</v>
-      </c>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="n">
-        <v>-2</v>
-      </c>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="n">
-        <v>0.1067027595972053</v>
-      </c>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA40" t="n">
-        <v>0.7145717655888678</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0.7145717655888678</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>W67CmLPh</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>preussen munster</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>stuttgart</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>59</v>
-      </c>
-      <c r="F41" t="n">
-        <v>593</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0.2702975615649746</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0.1088186248565082</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0.6208838135785172</v>
-      </c>
-      <c r="T41" t="n">
-        <v>1</v>
-      </c>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="n">
-        <v>-2</v>
-      </c>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="n">
-        <v>0.3791161864214828</v>
-      </c>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.538882065629469</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>2.538882065629469</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>fcxqFy2l</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>45521.64583333334</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>bayer leverkusen</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>stuttgart</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>59</v>
-      </c>
-      <c r="F42" t="n">
-        <v>594</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>super cup</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J42" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K42" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.5157232704402516</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.2578616352201258</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.2264150943396226</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0.07723577235772372</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.7850213839801177</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0.04098582600164608</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0.1739927900182362</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.2692981135398661</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0.2692981135398661</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0.7850213839801177</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
           <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
-      <c r="AA42" t="n">
+      <c r="AA33" t="n">
         <v>5.257165967339999</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AB33" t="n">
         <v>5.257165967339999</v>
       </c>
     </row>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,29 +634,29 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.06970817810399164</v>
+        <v>0.06838888361318179</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3844043987010784</v>
+        <v>0.3865482299682644</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5458874231949299</v>
+        <v>0.5450628864185538</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.04599840981945036</v>
+        <v>-0.04682294659582642</v>
       </c>
       <c r="W2" t="n">
         <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.04599840981945036</v>
+        <v>-0.04682294659582642</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5458874231949299</v>
+        <v>0.5450628864185538</v>
       </c>
       <c r="Z2" t="n">
         <v>1.6</v>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>3.655723069184568</v>
+        <v>3.650201274787571</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.655723069184568</v>
+        <v>3.650201274787571</v>
       </c>
     </row>
     <row r="3">
@@ -733,29 +733,29 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.296474130685205</v>
+        <v>0.2884298740477725</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3897043741190533</v>
+        <v>0.3982935122874999</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3138214951957416</v>
+        <v>0.3132766136647276</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.12638391079859</v>
+        <v>0.1349730489670365</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.12638391079859</v>
+        <v>0.1349730489670365</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3897043741190533</v>
+        <v>0.3982935122874999</v>
       </c>
       <c r="Z3" t="n">
         <v>3.6</v>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2.609789509879275</v>
+        <v>2.667309630718534</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.609789509879275</v>
+        <v>2.667309630718534</v>
       </c>
     </row>
     <row r="4">
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J4" t="n">
         <v>3.5</v>
@@ -817,44 +817,44 @@
         <v>2.15</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2906808305166586</v>
+        <v>0.2875429881543752</v>
       </c>
       <c r="M4" t="n">
-        <v>0.269917914051183</v>
+        <v>0.2711119602598395</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4394012554321584</v>
+        <v>0.4413450515857852</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0585228724763609</v>
+        <v>0.05386086781435617</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2162111509044098</v>
+        <v>0.2662159723409031</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4520718885264109</v>
+        <v>0.4201214634845208</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3317169605691793</v>
+        <v>0.3136625641745759</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1821539744752279</v>
+        <v>0.1490095032246813</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1821539744752279</v>
+        <v>0.1490095032246813</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4520718885264109</v>
+        <v>0.4201214634845208</v>
       </c>
       <c r="Z4" t="n">
         <v>3.5</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>3.027455042183108</v>
+        <v>2.813488020901906</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.027455042183108</v>
+        <v>2.813488020901906</v>
       </c>
     </row>
     <row r="5">
@@ -931,29 +931,29 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5529537648329218</v>
+        <v>0.5462238476938435</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2962074135860309</v>
+        <v>0.3064988036937072</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1508388215810472</v>
+        <v>0.1472773486124494</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.02168438595558553</v>
+        <v>-0.02841430309466386</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.02168438595558553</v>
+        <v>-0.02841430309466386</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5529537648329218</v>
+        <v>0.5462238476938435</v>
       </c>
       <c r="Z5" t="n">
         <v>1.65</v>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>3.703045258784679</v>
+        <v>3.657976051666778</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.703045258784679</v>
+        <v>3.657976051666778</v>
       </c>
     </row>
     <row r="6">
@@ -1030,29 +1030,29 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.209693942824908</v>
+        <v>0.2078151346267432</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4242970883997606</v>
+        <v>0.4229439288710368</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3660089687753315</v>
+        <v>0.3692409365022199</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.14432580340335</v>
+        <v>0.1429726438746262</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.14432580340335</v>
+        <v>0.1429726438746262</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4242970883997606</v>
+        <v>0.4229439288710368</v>
       </c>
       <c r="Z6" t="n">
         <v>3.4</v>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>2.841451530743482</v>
+        <v>2.832389632089561</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.841451530743482</v>
+        <v>2.832389632089561</v>
       </c>
     </row>
     <row r="7">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
         <v>7.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7099057574385776</v>
+        <v>0.7194244604316546</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1642042882423145</v>
+        <v>0.1558752997601918</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1258899543191078</v>
+        <v>0.1247002398081535</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05912607605971454</v>
+        <v>0.06923076923076921</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6231874682247995</v>
+        <v>0.6341428517788732</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2681073089489887</v>
+        <v>0.2590412097024586</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1087052228262117</v>
+        <v>0.1068159385186683</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.08671828921377811</v>
+        <v>-0.08528160865278145</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.08671828921377811</v>
+        <v>-0.08528160865278145</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6231874682247995</v>
+        <v>0.6341428517788732</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.173389433818492</v>
+        <v>4.246755931540664</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.173389433818492</v>
+        <v>4.246755931540664</v>
       </c>
     </row>
     <row r="8">
@@ -1204,67 +1204,67 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
         <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5503745604647607</v>
+        <v>0.5579074690051407</v>
       </c>
       <c r="M8" t="n">
-        <v>0.238036997401009</v>
+        <v>0.231327487148473</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2115884421342302</v>
+        <v>0.2107650438463864</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05025690430314711</v>
+        <v>0.05435995536425953</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4277162317695554</v>
+        <v>0.3817700307829515</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3214396384368219</v>
+        <v>0.3530078160977211</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2508441297936226</v>
+        <v>0.2652221531193274</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.1226583286952053</v>
+        <v>-0.1761374382221891</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1226583286952053</v>
+        <v>0.1761374382221891</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4277162317695554</v>
+        <v>0.6182299692170485</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.73</v>
+        <v>2.145348837209302</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>2.86434900147225</v>
+        <v>4.140189834930458</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.86434900147225</v>
+        <v>4.140189834930458</v>
       </c>
     </row>
     <row r="9">
@@ -1327,29 +1327,29 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1109334508511782</v>
+        <v>0.1165417462303732</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4094727422295901</v>
+        <v>0.427694401204095</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4795938069192318</v>
+        <v>0.4557638525655318</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.1519851404491893</v>
+        <v>-0.1758150948028894</v>
       </c>
       <c r="W9" t="n">
         <v>-2</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1519851404491893</v>
+        <v>0.1758150948028894</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5204061930807682</v>
+        <v>0.5442361474344682</v>
       </c>
       <c r="Z9" t="n">
         <v>2.571428571428571</v>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>3.485079238970736</v>
+        <v>3.644664732548464</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.485079238970736</v>
+        <v>3.644664732548464</v>
       </c>
     </row>
     <row r="10">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="J10" t="n">
         <v>3.5</v>
@@ -1411,44 +1411,44 @@
         <v>3.25</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4394012554321584</v>
+        <v>0.4452054794520548</v>
       </c>
       <c r="M10" t="n">
-        <v>0.269917914051183</v>
+        <v>0.2671232876712329</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2906808305166586</v>
+        <v>0.2876712328767124</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0585228724763609</v>
+        <v>0.06959706959706957</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1507377016229152</v>
+        <v>0.1474659893928866</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4132123383926922</v>
+        <v>0.3945271273585023</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4360499599843927</v>
+        <v>0.4580068832486109</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1453691294677341</v>
+        <v>0.1703356503718986</v>
       </c>
       <c r="W10" t="n">
         <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1453691294677341</v>
+        <v>0.1703356503718986</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4360499599843927</v>
+        <v>0.4580068832486109</v>
       </c>
       <c r="Z10" t="n">
         <v>3.25</v>
@@ -1459,10 +1459,901 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>2.920158681623859</v>
+        <v>3.067200777658109</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.920158681623859</v>
+        <v>3.067200777658109</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>djSMofvg</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45534.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>union berlin</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>st  pauli</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" t="n">
+        <v>591</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4640029460504511</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2717731541152641</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.2642238998342846</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05129694154084419</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.5503760186245251</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2960562286610389</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1535677527144358</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.08637307257407406</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.08637307257407406</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.5503760186245251</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.685782493825953</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.685782493825953</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>U3QUqY85</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bochum</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>b  monchengladbach</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F12" t="n">
+        <v>591</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4157043879907621</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2655889145496536</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3187066974595843</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.04589371980676327</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1769046634243255</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3967319879499094</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.426363348625765</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1076566511661807</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1076566511661807</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.426363348625765</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.85528895372519</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.85528895372519</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>AgAeVYgC</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>eintracht frankfurt</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>hoffenheim</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F13" t="n">
+        <v>591</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.4885742581520742</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2522099548839085</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.2592157869640171</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.07160825747213195</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4453891390382599</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3499129270049161</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.204697933956824</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.04318511911381429</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.04318511911381429</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4453891390382599</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.982701709478663</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.982701709478663</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>QVJwrCwI</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>holstein kiel</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>wolfsburg</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>59</v>
+      </c>
+      <c r="F14" t="n">
+        <v>591</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.3163064833005893</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2711198428290766</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.4125736738703339</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0538302277432714</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.06900240254916105</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.403404419851537</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.527593177599302</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.1150195037289681</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.1150195037289681</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.527593177599302</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.53320935515569</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.53320935515569</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>mainz</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>59</v>
+      </c>
+      <c r="F15" t="n">
+        <v>591</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6174990513369328</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2181925054377615</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1643084432253056</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.05845469693718108</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.4150557608433468</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3583941456475557</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2265500935090974</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-0.202443290493586</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.202443290493586</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.5849442391566532</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.46999007936508</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.917280483870017</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.917280483870017</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>werder bremen</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>dortmund</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>59</v>
+      </c>
+      <c r="F16" t="n">
+        <v>591</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06837606837606858</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.08504984113257555</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.4029427638402989</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.5120073950271256</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.03200739502712557</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.03200739502712557</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.5120073950271256</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>3.428833796241128</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.428833796241128</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>bayer leverkusen</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>rb leipzig</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>59</v>
+      </c>
+      <c r="F17" t="n">
+        <v>591</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.5158730158730158</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2420634920634921</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2420634920634921</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.0592686002522067</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.2944486686154041</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.4309788634890854</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2745724678955104</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.1889153714255933</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.1889153714255933</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.4309788634890854</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.886198338050719</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.886198338050719</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45536.4375</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>heidenheim</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>augsburg</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>59</v>
+      </c>
+      <c r="F18" t="n">
+        <v>591</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.4029376736800317</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2705438666137356</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3265184597062326</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.05607378681479935</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2149330591715474</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.425704153392019</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.3593627874364336</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.1551602867782834</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.1551602867782834</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.425704153392019</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.850874425892698</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.850874425892698</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45536.52083333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>bayern munich</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>59</v>
+      </c>
+      <c r="F19" t="n">
+        <v>591</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>13</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.7803121248499399</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1464585834333733</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.07322929171668667</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.05044136191677184</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.5570435324044843</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2912776062762418</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.1516788613192739</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>-0.2232685924454556</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.2232685924454556</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.4429564675955157</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.966410487634904</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.966410487634904</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,29 +634,29 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.06970817810399164</v>
+        <v>0.06838888361318179</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3844043987010784</v>
+        <v>0.3865482299682644</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5458874231949299</v>
+        <v>0.5450628864185538</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.04599840981945036</v>
+        <v>-0.04682294659582642</v>
       </c>
       <c r="W2" t="n">
         <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.04599840981945036</v>
+        <v>-0.04682294659582642</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5458874231949299</v>
+        <v>0.5450628864185538</v>
       </c>
       <c r="Z2" t="n">
         <v>1.6</v>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>3.655723069184568</v>
+        <v>3.650201274787571</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.655723069184568</v>
+        <v>3.650201274787571</v>
       </c>
     </row>
     <row r="3">
@@ -733,29 +733,29 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.296474130685205</v>
+        <v>0.2794162171712321</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3897043741190533</v>
+        <v>0.387798783406023</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3138214951957416</v>
+        <v>0.332784999422745</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.12638391079859</v>
+        <v>0.1244783200855596</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.12638391079859</v>
+        <v>0.1244783200855596</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3897043741190533</v>
+        <v>0.387798783406023</v>
       </c>
       <c r="Z3" t="n">
         <v>3.6</v>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2.609789509879275</v>
+        <v>2.59702806560698</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.609789509879275</v>
+        <v>2.59702806560698</v>
       </c>
     </row>
     <row r="4">
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J4" t="n">
         <v>3.5</v>
@@ -817,44 +817,44 @@
         <v>2.15</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2906808305166586</v>
+        <v>0.2875429881543752</v>
       </c>
       <c r="M4" t="n">
-        <v>0.269917914051183</v>
+        <v>0.2711119602598395</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4394012554321584</v>
+        <v>0.4413450515857852</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0585228724763609</v>
+        <v>0.05386086781435617</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2162111509044098</v>
+        <v>0.2662159723409032</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4520718885264109</v>
+        <v>0.4201214634845208</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3317169605691793</v>
+        <v>0.313662564174576</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1821539744752279</v>
+        <v>0.1490095032246813</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1821539744752279</v>
+        <v>0.1490095032246813</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4520718885264109</v>
+        <v>0.4201214634845208</v>
       </c>
       <c r="Z4" t="n">
         <v>3.5</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>3.027455042183108</v>
+        <v>2.813488020901906</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.027455042183108</v>
+        <v>2.813488020901906</v>
       </c>
     </row>
     <row r="5">
@@ -931,29 +931,29 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5529537648329218</v>
+        <v>0.5461627831902344</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2962074135860309</v>
+        <v>0.3065763329090344</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1508388215810472</v>
+        <v>0.1472608839007312</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.02168438595558553</v>
+        <v>-0.02847536759827296</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.02168438595558553</v>
+        <v>-0.02847536759827296</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5529537648329218</v>
+        <v>0.5461627831902344</v>
       </c>
       <c r="Z5" t="n">
         <v>1.65</v>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>3.703045258784679</v>
+        <v>3.65756711219489</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.703045258784679</v>
+        <v>3.65756711219489</v>
       </c>
     </row>
     <row r="6">
@@ -1030,29 +1030,29 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.209693942824908</v>
+        <v>0.2077322430245421</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4242970883997606</v>
+        <v>0.4233594316670704</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3660089687753315</v>
+        <v>0.3689083253083874</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.14432580340335</v>
+        <v>0.1433881466706598</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.14432580340335</v>
+        <v>0.1433881466706598</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4242970883997606</v>
+        <v>0.4233594316670704</v>
       </c>
       <c r="Z6" t="n">
         <v>3.4</v>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>2.841451530743482</v>
+        <v>2.83517218961375</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.841451530743482</v>
+        <v>2.83517218961375</v>
       </c>
     </row>
     <row r="7">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
         <v>7.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7099057574385776</v>
+        <v>0.7194244604316546</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1642042882423145</v>
+        <v>0.1558752997601918</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1258899543191078</v>
+        <v>0.1247002398081535</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05912607605971454</v>
+        <v>0.06923076923076921</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6231874682247995</v>
+        <v>0.6341428517788732</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2681073089489887</v>
+        <v>0.2590412097024586</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1087052228262117</v>
+        <v>0.1068159385186683</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.08671828921377811</v>
+        <v>-0.08528160865278145</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.08671828921377811</v>
+        <v>-0.08528160865278145</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6231874682247995</v>
+        <v>0.6341428517788732</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.173389433818492</v>
+        <v>4.246755931540664</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.173389433818492</v>
+        <v>4.246755931540664</v>
       </c>
     </row>
     <row r="8">
@@ -1204,67 +1204,67 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
         <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5503745604647607</v>
+        <v>0.5579074690051407</v>
       </c>
       <c r="M8" t="n">
-        <v>0.238036997401009</v>
+        <v>0.231327487148473</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2115884421342302</v>
+        <v>0.2107650438463864</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05025690430314711</v>
+        <v>0.05435995536425953</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4277162317695554</v>
+        <v>0.3799273330325321</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3214396384368219</v>
+        <v>0.3485985228476672</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2508441297936226</v>
+        <v>0.2714741441198005</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.1226583286952053</v>
+        <v>-0.1779801359726086</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1226583286952053</v>
+        <v>0.1779801359726086</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4277162317695554</v>
+        <v>0.6200726669674679</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.73</v>
+        <v>2.145348837209302</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>2.86434900147225</v>
+        <v>4.15253009482565</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.86434900147225</v>
+        <v>4.15253009482565</v>
       </c>
     </row>
     <row r="9">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.1479221462388217</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.2024197790636507</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6315789473684211</v>
+        <v>0.6496580746975277</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05555555555555536</v>
+        <v>0.04004814531130307</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1109334508511782</v>
+        <v>0.115526486868512</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4094727422295901</v>
+        <v>0.4359838600267355</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4795938069192318</v>
+        <v>0.4484896531047526</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.1519851404491893</v>
+        <v>-0.2011684215927751</v>
       </c>
       <c r="W9" t="n">
         <v>-2</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1519851404491893</v>
+        <v>0.2011684215927751</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5204061930807682</v>
+        <v>0.5515103468952474</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.571428571428571</v>
+        <v>2.744444444444444</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>3.485079238970736</v>
+        <v>3.693378913620784</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.485079238970736</v>
+        <v>3.693378913620784</v>
       </c>
     </row>
     <row r="10">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="J10" t="n">
         <v>3.5</v>
@@ -1411,44 +1411,44 @@
         <v>3.25</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4394012554321584</v>
+        <v>0.4452054794520548</v>
       </c>
       <c r="M10" t="n">
-        <v>0.269917914051183</v>
+        <v>0.2671232876712329</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2906808305166586</v>
+        <v>0.2876712328767124</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0585228724763609</v>
+        <v>0.06959706959706957</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1507377016229152</v>
+        <v>0.1474195239146204</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4132123383926922</v>
+        <v>0.3949478120626924</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4360499599843927</v>
+        <v>0.4576326640226871</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1453691294677341</v>
+        <v>0.1699614311459747</v>
       </c>
       <c r="W10" t="n">
         <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1453691294677341</v>
+        <v>0.1699614311459747</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4360499599843927</v>
+        <v>0.4576326640226871</v>
       </c>
       <c r="Z10" t="n">
         <v>3.25</v>
@@ -1459,10 +1459,901 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>2.920158681623859</v>
+        <v>3.064694689774392</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.920158681623859</v>
+        <v>3.064694689774392</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>djSMofvg</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45534.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>union berlin</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>st  pauli</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" t="n">
+        <v>591</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4640029460504511</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2717731541152641</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.2642238998342846</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05129694154084419</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.5503165860218741</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2961322443467427</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.153551169631383</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.086313639971423</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.086313639971423</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.5503165860218741</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.685384482940665</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.685384482940665</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>U3QUqY85</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bochum</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>b  monchengladbach</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F12" t="n">
+        <v>591</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4157043879907621</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2655889145496536</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3187066974595843</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.04589371980676327</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1768455743783334</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3971475057747061</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.4260069198469605</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1073002223873762</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1073002223873762</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4260069198469605</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.852902005695556</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.852902005695556</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>AgAeVYgC</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>eintracht frankfurt</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>hoffenheim</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F13" t="n">
+        <v>591</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5093833780160858</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2453083109919571</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.2453083109919571</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.072763876905378</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4456707385012158</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3497857186364307</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.2045435428623534</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.06371263951487</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.06371263951487</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4456707385012158</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.984587537232255</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.984587537232255</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>QVJwrCwI</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>holstein kiel</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>wolfsburg</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>59</v>
+      </c>
+      <c r="F14" t="n">
+        <v>591</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.3163064833005893</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2711198428290766</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.4125736738703339</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0538302277432714</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.06742366949341573</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3980165281892039</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.5345598023173804</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.1219861284470465</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.1219861284470465</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.5345598023173804</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.579863756070759</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.579863756070759</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>mainz</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>59</v>
+      </c>
+      <c r="F15" t="n">
+        <v>591</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6174990513369328</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2181925054377615</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1643084432253056</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.05845469693718108</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.4150557608433468</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3583941456475557</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2265500935090975</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-0.202443290493586</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.202443290493586</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.5849442391566532</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.46999007936508</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.917280483870017</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.917280483870017</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>werder bremen</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>dortmund</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>59</v>
+      </c>
+      <c r="F16" t="n">
+        <v>591</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06837606837606858</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.08325612829513089</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.4147978300959643</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.5019460416089049</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.0219460416089049</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.0219460416089049</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.5019460416089049</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>3.361454479123075</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.361454479123075</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>bayer leverkusen</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>rb leipzig</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>59</v>
+      </c>
+      <c r="F17" t="n">
+        <v>591</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.5158730158730158</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2420634920634921</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2420634920634921</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.0592686002522067</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.2944486686154041</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.4309788634890854</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2745724678955104</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.1889153714255933</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.1889153714255933</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.4309788634890854</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.886198338050719</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.886198338050719</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45536.4375</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>heidenheim</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>augsburg</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>59</v>
+      </c>
+      <c r="F18" t="n">
+        <v>591</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.4221789883268482</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2714007782101167</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.306420233463035</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.05273937532002049</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2148120532559113</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.4262078219006251</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.3589801248434636</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.1548070436905084</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.1548070436905084</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.4262078219006251</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.854247415465083</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.854247415465083</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45536.52083333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>bayern munich</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>59</v>
+      </c>
+      <c r="F19" t="n">
+        <v>591</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>13</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.7803121248499399</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1464585834333733</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.07322929171668667</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.05044136191677184</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.5568618094090434</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2915849481069179</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.1515532424840386</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>-0.2234503154408966</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.2234503154408966</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.4431381905909566</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.967627458238012</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.967627458238012</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -616,61 +616,61 @@
         <v>4.33</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1894034665646017</v>
+        <v>0.1872852849047196</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2187107004210181</v>
+        <v>0.2162647631694221</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5918858330143802</v>
+        <v>0.5964499519258584</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0559468822170901</v>
+        <v>0.06788955737632563</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.06838888361318179</v>
+        <v>0.0332989612630136</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3865482299682644</v>
+        <v>0.2862225669792112</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5450628864185538</v>
+        <v>0.6804784717577752</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.04682294659582642</v>
+        <v>0.08402851983191684</v>
       </c>
       <c r="W2" t="n">
         <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.04682294659582642</v>
+        <v>0.08402851983191684</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5450628864185538</v>
+        <v>0.6804784717577752</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>3.650201274787571</v>
+        <v>2.939469859977928</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.650201274787571</v>
+        <v>2.939469859977928</v>
       </c>
     </row>
     <row r="3">
@@ -733,43 +733,43 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2794162171712321</v>
+        <v>0.2346636067687149</v>
       </c>
       <c r="R3" t="n">
-        <v>0.387798783406023</v>
+        <v>0.3836683950726748</v>
       </c>
       <c r="S3" t="n">
-        <v>0.332784999422745</v>
+        <v>0.3816679981586102</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1244783200855596</v>
+        <v>0.1203479317522114</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1244783200855596</v>
+        <v>0.1203479317522114</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.387798783406023</v>
+        <v>0.3836683950726748</v>
       </c>
       <c r="Z3" t="n">
         <v>3.6</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2.59702806560698</v>
+        <v>1.657336316061561</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.59702806560698</v>
+        <v>1.657336316061561</v>
       </c>
     </row>
     <row r="4">
@@ -808,67 +808,67 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2875429881543752</v>
+        <v>0.2806236080178174</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2711119602598395</v>
+        <v>0.2650334075723831</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4413450515857852</v>
+        <v>0.4543429844097996</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05386086781435617</v>
+        <v>0.04808590102707733</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2662159723409032</v>
+        <v>0.2548200576322532</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4201214634845208</v>
+        <v>0.4056882288870197</v>
       </c>
       <c r="S4" t="n">
-        <v>0.313662564174576</v>
+        <v>0.3394917134807272</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1490095032246813</v>
+        <v>0.1406548213146366</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1490095032246813</v>
+        <v>0.1406548213146366</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4201214634845208</v>
+        <v>0.4056882288870197</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>2.813488020901906</v>
+        <v>1.752455618883576</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.813488020901906</v>
+        <v>1.752455618883576</v>
       </c>
     </row>
     <row r="5">
@@ -907,67 +907,67 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="K5" t="n">
         <v>4.75</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5746381507885073</v>
+        <v>0.5830269494941478</v>
       </c>
       <c r="M5" t="n">
-        <v>0.225750702095485</v>
+        <v>0.2181301750994271</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1996111471160078</v>
+        <v>0.1988428754064251</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05468215994531778</v>
+        <v>0.05875714862384762</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5461627831902344</v>
+        <v>0.5796457246495701</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3065763329090344</v>
+        <v>0.2700014328808418</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1472608839007312</v>
+        <v>0.1503528424695882</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.02847536759827296</v>
+        <v>-0.003381224844577702</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.02847536759827296</v>
+        <v>-0.003381224844577702</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5461627831902344</v>
+        <v>0.5796457246495701</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>3.65756711219489</v>
+        <v>2.503901604221483</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.65756711219489</v>
+        <v>2.503901604221483</v>
       </c>
     </row>
     <row r="6">
@@ -1030,43 +1030,43 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2077322430245421</v>
+        <v>0.2777075384682832</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4233594316670704</v>
+        <v>0.3702299299283254</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3689083253083874</v>
+        <v>0.3520625316033914</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1433881466706598</v>
+        <v>0.09025864493191477</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1433881466706598</v>
+        <v>0.09025864493191477</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4233594316670704</v>
+        <v>0.3702299299283254</v>
       </c>
       <c r="Z6" t="n">
         <v>3.4</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>2.83517218961375</v>
+        <v>1.599286039828516</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.83517218961375</v>
+        <v>1.599286039828516</v>
       </c>
     </row>
     <row r="7">
@@ -1105,67 +1105,67 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="K7" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7194244604316546</v>
+        <v>0.7466216216216217</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1558752997601918</v>
+        <v>0.1435810810810811</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1247002398081535</v>
+        <v>0.1097972972972973</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06923076923076921</v>
+        <v>0.07149321266968323</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6341428517788732</v>
+        <v>0.5590050247947679</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2590412097024586</v>
+        <v>0.3594827256395218</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1068159385186683</v>
+        <v>0.08151224956571015</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.08528160865278145</v>
+        <v>-0.1876165968268538</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.08528160865278145</v>
+        <v>0.1876165968268538</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6341428517788732</v>
+        <v>0.4409949752052321</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.3</v>
+        <v>3.683333333333334</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.246755931540664</v>
+        <v>1.904970534437311</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.246755931540664</v>
+        <v>1.904970534437311</v>
       </c>
     </row>
     <row r="8">
@@ -1228,43 +1228,43 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3799273330325321</v>
+        <v>0.6032287233137945</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3485985228476672</v>
+        <v>0.2640580705349358</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2714741441198005</v>
+        <v>0.1327132061512696</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.1779801359726086</v>
+        <v>0.04532125430865386</v>
       </c>
       <c r="W8" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1779801359726086</v>
+        <v>0.04532125430865386</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6200726669674679</v>
+        <v>0.6032287233137945</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.145348837209302</v>
+        <v>1.7</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>4.15253009482565</v>
+        <v>2.605773326338305</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.15253009482565</v>
+        <v>2.605773326338305</v>
       </c>
     </row>
     <row r="9">
@@ -1327,43 +1327,43 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.115526486868512</v>
+        <v>0.1371082897684723</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4359838600267355</v>
+        <v>0.3863967918267899</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4484896531047526</v>
+        <v>0.4764949184047379</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.2011684215927751</v>
+        <v>-0.1731631562927898</v>
       </c>
       <c r="W9" t="n">
         <v>-2</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2011684215927751</v>
+        <v>0.1731631562927898</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5515103468952474</v>
+        <v>0.5235050815952621</v>
       </c>
       <c r="Z9" t="n">
         <v>2.744444444444444</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>3.693378913620784</v>
+        <v>2.261390290451869</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.693378913620784</v>
+        <v>2.261390290451869</v>
       </c>
     </row>
     <row r="10">
@@ -1408,61 +1408,61 @@
         <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4452054794520548</v>
+        <v>0.4471544715447154</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2671232876712329</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2876712328767124</v>
+        <v>0.2845528455284553</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06959706959706957</v>
+        <v>0.06493506493506485</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1474195239146204</v>
+        <v>0.2310214101079057</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3949478120626924</v>
+        <v>0.4757411918709668</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4576326640226871</v>
+        <v>0.2932373980211276</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1699614311459747</v>
+        <v>0.2074485089441375</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1699614311459747</v>
+        <v>0.2074485089441375</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4576326640226871</v>
+        <v>0.4757411918709668</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>3.064694689774392</v>
+        <v>2.055064124280586</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.064694689774392</v>
+        <v>2.055064124280586</v>
       </c>
     </row>
     <row r="11">
@@ -1507,61 +1507,61 @@
         <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4640029460504511</v>
+        <v>0.4673403103572718</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2717731541152641</v>
+        <v>0.273727896066402</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2642238998342846</v>
+        <v>0.2589317935763262</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05129694154084419</v>
+        <v>0.04378943403333646</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5503165860218741</v>
+        <v>0.5864101075026901</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2961322443467427</v>
+        <v>0.2863208677608263</v>
       </c>
       <c r="S11" t="n">
-        <v>0.153551169631383</v>
+        <v>0.1272690247364837</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.086313639971423</v>
+        <v>0.1190697971454183</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>0.086313639971423</v>
+        <v>0.1190697971454183</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5503165860218741</v>
+        <v>0.5864101075026901</v>
       </c>
       <c r="Z11" t="n">
         <v>2.05</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>3.685384482940665</v>
+        <v>2.533121778471427</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.685384482940665</v>
+        <v>2.533121778471427</v>
       </c>
     </row>
     <row r="12">
@@ -1624,43 +1624,43 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1768455743783334</v>
+        <v>0.190129093525317</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3971475057747061</v>
+        <v>0.322978033860898</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4260069198469605</v>
+        <v>0.4868928726137849</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1073002223873762</v>
+        <v>0.1681861751542006</v>
       </c>
       <c r="W12" t="n">
         <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1073002223873762</v>
+        <v>0.1681861751542006</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4260069198469605</v>
+        <v>0.4868928726137849</v>
       </c>
       <c r="Z12" t="n">
         <v>3</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>2.852902005695556</v>
+        <v>2.10323615439189</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.852902005695556</v>
+        <v>2.10323615439189</v>
       </c>
     </row>
     <row r="13">
@@ -1699,67 +1699,67 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>3.8</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5093833780160858</v>
+        <v>0.5167364016736402</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2453083109919571</v>
+        <v>0.2447698744769874</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2453083109919571</v>
+        <v>0.2384937238493724</v>
       </c>
       <c r="O13" t="n">
-        <v>0.072763876905378</v>
+        <v>0.075123706702654</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4456707385012158</v>
+        <v>0.3834996490478769</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3497857186364307</v>
+        <v>0.3345946163079804</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2045435428623534</v>
+        <v>0.2819057346441427</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>-0.06371263951487</v>
+        <v>-0.1332367526257633</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.06371263951487</v>
+        <v>0.1332367526257633</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4456707385012158</v>
+        <v>0.6165003509521231</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.83</v>
+        <v>1.924675324675325</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>2.984587537232255</v>
+        <v>2.663102912878999</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.984587537232255</v>
+        <v>2.663102912878999</v>
       </c>
     </row>
     <row r="14">
@@ -1798,67 +1798,67 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3163064833005893</v>
+        <v>0.3057915057915058</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2711198428290766</v>
+        <v>0.2633204633204633</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4125736738703339</v>
+        <v>0.4308880308880308</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0538302277432714</v>
+        <v>0.05490387748452275</v>
       </c>
       <c r="P14" t="n">
         <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.06742366949341573</v>
+        <v>0.06949278788174991</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3980165281892039</v>
+        <v>0.3801217379633041</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5345598023173804</v>
+        <v>0.5503854741549461</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1219861284470465</v>
+        <v>0.1194974432669152</v>
       </c>
       <c r="W14" t="n">
         <v>2</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1219861284470465</v>
+        <v>0.1194974432669152</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.5345598023173804</v>
+        <v>0.5503854741549461</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>3.579863756070759</v>
+        <v>2.377505798925577</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.579863756070759</v>
+        <v>2.377505798925577</v>
       </c>
     </row>
     <row r="15">
@@ -1897,67 +1897,67 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="J15" t="n">
         <v>4.33</v>
       </c>
       <c r="K15" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6174990513369328</v>
+        <v>0.6098357297414951</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2181925054377615</v>
+        <v>0.2183014736949925</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1643084432253056</v>
+        <v>0.1718627965635123</v>
       </c>
       <c r="O15" t="n">
-        <v>0.05845469693718108</v>
+        <v>0.05792635435785254</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.4150557608433468</v>
+        <v>0.4959298926532823</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3583941456475557</v>
+        <v>0.3042471008390001</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2265500935090975</v>
+        <v>0.1998230065077176</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>-0.202443290493586</v>
+        <v>-0.1139058370882128</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>0.202443290493586</v>
+        <v>0.1139058370882128</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5849442391566532</v>
+        <v>0.5040701073467178</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.46999007936508</v>
+        <v>2.422685656154629</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>3.917280483870017</v>
+        <v>2.177436832107372</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.917280483870017</v>
+        <v>2.177436832107372</v>
       </c>
     </row>
     <row r="16">
@@ -2020,43 +2020,43 @@
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.08325612829513089</v>
+        <v>0.1086962288444902</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4147978300959643</v>
+        <v>0.3402277316203847</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5019460416089049</v>
+        <v>0.5510760395351252</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.0219460416089049</v>
+        <v>0.0710760395351252</v>
       </c>
       <c r="W16" t="n">
         <v>2</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0219460416089049</v>
+        <v>0.0710760395351252</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5019460416089049</v>
+        <v>0.5510760395351252</v>
       </c>
       <c r="Z16" t="n">
         <v>1.95</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>3.361454479123075</v>
+        <v>2.380488841307707</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.361454479123075</v>
+        <v>2.380488841307707</v>
       </c>
     </row>
     <row r="17">
@@ -2116,46 +2116,46 @@
         <v>0.0592686002522067</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.2944486686154041</v>
+        <v>0.3986165358049383</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4309788634890854</v>
+        <v>0.3950083384352972</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2745724678955104</v>
+        <v>0.2063751257597645</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1889153714255933</v>
+        <v>-0.1172564800680775</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1889153714255933</v>
+        <v>0.1172564800680775</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.4309788634890854</v>
+        <v>0.6013834641950617</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>2.886198338050719</v>
+        <v>2.597802341526172</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.886198338050719</v>
+        <v>2.597802341526172</v>
       </c>
     </row>
     <row r="18">
@@ -2215,46 +2215,46 @@
         <v>0.05273937532002049</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2148120532559113</v>
+        <v>0.2124655061087739</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4262078219006251</v>
+        <v>0.366165770768149</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3589801248434636</v>
+        <v>0.421368723123077</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1548070436905084</v>
+        <v>0.1149484896600421</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1548070436905084</v>
+        <v>0.1149484896600421</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.4262078219006251</v>
+        <v>0.421368723123077</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>2.854247415465083</v>
+        <v>1.820190811265761</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.854247415465083</v>
+        <v>1.820190811265761</v>
       </c>
     </row>
     <row r="19">
@@ -2293,67 +2293,67 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="J19" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="K19" t="n">
         <v>13</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7803121248499399</v>
+        <v>0.771513353115727</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1464585834333733</v>
+        <v>0.1543026706231454</v>
       </c>
       <c r="N19" t="n">
-        <v>0.07322929171668667</v>
+        <v>0.07418397626112759</v>
       </c>
       <c r="O19" t="n">
-        <v>0.05044136191677184</v>
+        <v>0.03692307692307706</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.5568618094090434</v>
+        <v>0.614264058670636</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2915849481069179</v>
+        <v>0.30388907837108</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1515532424840386</v>
+        <v>0.08184686295828413</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>-0.2234503154408966</v>
+        <v>-0.1572492944450909</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>0.2234503154408966</v>
+        <v>0.1572492944450909</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.4431381905909566</v>
+        <v>0.385735941329364</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.333333333333333</v>
+        <v>4.220779220779221</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>2.967627458238012</v>
+        <v>1.666267516911969</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.967627458238012</v>
+        <v>1.666267516911969</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>t0w6KHuf</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45529.4375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,86 +610,86 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4308880308880309</v>
+        <v>0.169811320754717</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2633204633204634</v>
+        <v>0.2075471698113207</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3057915057915058</v>
+        <v>0.6226415094339622</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05490387748452252</v>
+        <v>0.07070707070707072</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2784386416496532</v>
+        <v>0.2862284800244926</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3617236691644891</v>
+        <v>0.4191889255542917</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3598376891858576</v>
+        <v>0.2945825944212156</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.09840320584402573</v>
+        <v>0.2116417557429709</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.09840320584402573</v>
+        <v>0.2116417557429709</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3617236691644891</v>
+        <v>0.4191889255542917</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>1.562541457635018</v>
+        <v>1.631922352164138</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.562541457635018</v>
+        <v>1.631922352164138</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>AuVMGZvJ</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45529.52083333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>st  pauli</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>stuttgart</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,86 +709,86 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="J3" t="n">
         <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2775479503572772</v>
+        <v>0.4640029460504511</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.2642238998342846</v>
       </c>
       <c r="N3" t="n">
-        <v>0.46032342986085</v>
+        <v>0.2717731541152641</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05970030288538175</v>
+        <v>0.05129694154084419</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2939014781623062</v>
+        <v>0.2424513864116839</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3844116601339095</v>
+        <v>0.3901760221005395</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3216868617037843</v>
+        <v>0.3673725914877766</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1222830403520366</v>
+        <v>0.1259521222662549</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1222830403520366</v>
+        <v>0.1259521222662549</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3844116601339095</v>
+        <v>0.3901760221005395</v>
       </c>
       <c r="Z3" t="n">
         <v>3.6</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>1.66054700579849</v>
+        <v>1.335193547721989</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.66054700579849</v>
+        <v>1.335193547721989</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45534.64583333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>holstein kiel</t>
+          <t>st  pauli</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,86 +808,86 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5692192187805826</v>
+        <v>0.4640029460504511</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2112435767474606</v>
+        <v>0.2717731541152641</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2195372044719568</v>
+        <v>0.2642238998342846</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05197149964889314</v>
+        <v>0.05129694154084419</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.428600351343007</v>
+        <v>0.6601473524492966</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3670207083212907</v>
+        <v>0.2564734495342519</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2043789403357023</v>
+        <v>0.08337919801645156</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.1406188674375756</v>
+        <v>0.1961444063988455</v>
       </c>
       <c r="W4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1406188674375756</v>
+        <v>0.1961444063988455</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.571399648656993</v>
+        <v>0.6601473524492966</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.206681766704417</v>
+        <v>2.05</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>2.468280944862996</v>
+        <v>2.215177071547251</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.468280944862996</v>
+        <v>2.215177071547251</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45535.4375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,86 +907,86 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4471544715447154</v>
+        <v>0.3888834331729352</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2845528455284553</v>
+        <v>0.2646567809093587</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2682926829268292</v>
+        <v>0.346459785917706</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06493506493506507</v>
+        <v>0.04957740672026389</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.341096225343002</v>
+        <v>0.2944810525548903</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3377383972739379</v>
+        <v>0.4273155015522135</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3211653773830601</v>
+        <v>0.2782034458928962</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.1060582462017133</v>
+        <v>0.1626587206428548</v>
       </c>
       <c r="W5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1060582462017133</v>
+        <v>0.1626587206428548</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6589037746569979</v>
+        <v>0.4273155015522135</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.698529411764706</v>
+        <v>3.6</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2.846273418800194</v>
+        <v>1.526229064225069</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.846273418800194</v>
+        <v>1.526229064225069</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45535.4375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>bochum</t>
+          <t>hoffenheim</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,86 +1006,86 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.22</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>9.5</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7745407109468422</v>
+        <v>0.5167364016736402</v>
       </c>
       <c r="M6" t="n">
-        <v>0.125991955647353</v>
+        <v>0.2447698744769874</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09946733340580499</v>
+        <v>0.2384937238493724</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05826862237561103</v>
+        <v>0.075123706702654</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5054526715256167</v>
+        <v>0.4629405730520928</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4031366151393873</v>
+        <v>0.3782169234398582</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09141071333499608</v>
+        <v>0.1588425035080489</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.2690880394212255</v>
+        <v>-0.05379582862154741</v>
       </c>
       <c r="W6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2690880394212255</v>
+        <v>-0.05379582862154741</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4945473284743833</v>
+        <v>0.4629405730520928</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.191176470588236</v>
+        <v>1.8</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>2.13630118617554</v>
+        <v>1.058433702580262</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.13630118617554</v>
+        <v>1.058433702580262</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45535.4375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>holstein kiel</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,67 +1105,562 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="L7" t="n">
-        <v>0.54584017471928</v>
+        <v>0.3057915057915058</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.2633204633204633</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.4308880308880308</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.05490387748452275</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5601452813802659</v>
+        <v>0.1495829533343152</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2927308379892415</v>
+        <v>0.3898711388722733</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1471238806304927</v>
+        <v>0.4605459077934116</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.01430510666098583</v>
+        <v>0.02965787690538074</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01430510666098583</v>
+        <v>0.02965787690538074</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5601452813802659</v>
+        <v>0.4605459077934116</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>2.419665338674006</v>
+        <v>1.26812873419587</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.419665338674006</v>
+        <v>1.26812873419587</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>mainz</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>59</v>
+      </c>
+      <c r="F8" t="n">
+        <v>591</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5932203389830508</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2259887005649717</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.1807909604519774</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0535714285714286</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.539792983116164</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3224578409192884</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.1377491759645477</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>-0.05342735586688685</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.05342735586688685</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.539792983116164</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.258199643682852</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.258199643682852</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>werder bremen</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>dortmund</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>59</v>
+      </c>
+      <c r="F9" t="n">
+        <v>591</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2528714338643941</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2673212300852167</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.479807336050389</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.06880506880506898</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.1399741911688833</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3743520197213582</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.4856737891097586</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.005866453059369559</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.005866453059369559</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.4856737891097586</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.271586072088936</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.271586072088936</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>bayer leverkusen</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>rb leipzig</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>59</v>
+      </c>
+      <c r="F10" t="n">
+        <v>591</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.509891622226045</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2418716669533804</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2482367108205746</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.06010869168763899</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.3894322903000509</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3161555809281153</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2944121287718337</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>-0.1204593319259941</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.1204593319259941</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.3894322903000509</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.6958174291644785</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.6958174291644785</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45536.4375</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>heidenheim</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>augsburg</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" t="n">
+        <v>591</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4134954884268341</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2797175362887407</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.3067869752844253</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05148090091576596</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.3466060813416837</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.4215332068447334</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2318607118135829</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.1418156705559927</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1418156705559927</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4215332068447334</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.457350842869996</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.457350842869996</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45536.52083333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bayern munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F12" t="n">
+        <v>591</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7809330628803246</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1338742393509128</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.08519269776876268</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0670995670995671</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.6360072866567322</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.2644155838728855</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.09957712947038226</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.1449257762235924</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.1449257762235924</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.6360072866567322</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.270399359717771</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.270399359717771</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,10 +565,15 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>dif_prob_limited</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -577,20 +582,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.4375</v>
+        <v>45534.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>wolfsburg</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>st  pauli</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +615,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>0.169811320754717</v>
+        <v>0.4640029460504511</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2075471698113207</v>
+        <v>0.2717731541152641</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6226415094339622</v>
+        <v>0.2642238998342846</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07070707070707072</v>
+        <v>0.05129694154084419</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2862284800244926</v>
+        <v>0.6367051529275674</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4191889255542917</v>
+        <v>0.2736915926060542</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2945825944212156</v>
+        <v>0.08960325446637839</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2116417557429709</v>
+        <v>0.1727022068771163</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2116417557429709</v>
+        <v>0.1727022068771163</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4191889255542917</v>
+        <v>0.6367051529275674</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.5</v>
+        <v>2.05</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +672,32 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>1.631922352164138</v>
+        <v>0.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.631922352164138</v>
+        <v>2.035160561602784</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.035160561602784</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.52083333334</v>
+        <v>45535.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>st  pauli</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,53 +717,53 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="J3" t="n">
         <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4640029460504511</v>
+        <v>0.3888834331729352</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2642238998342846</v>
+        <v>0.2646567809093587</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2717731541152641</v>
+        <v>0.346459785917706</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05129694154084419</v>
+        <v>0.04957740672026389</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2424513864116839</v>
+        <v>0.2944810525548903</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3901760221005395</v>
+        <v>0.4273155015522135</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3673725914877766</v>
+        <v>0.2782034458928962</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1259521222662549</v>
+        <v>0.1626587206428548</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1259521222662549</v>
+        <v>0.1626587206428548</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3901760221005395</v>
+        <v>0.4273155015522135</v>
       </c>
       <c r="Z3" t="n">
         <v>3.6</v>
@@ -766,29 +774,32 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>1.335193547721989</v>
+        <v>0.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.335193547721989</v>
+        <v>1.493481688773396</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.493481688773396</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45534.64583333334</v>
+        <v>45535.4375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>st  pauli</t>
+          <t>hoffenheim</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +819,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4640029460504511</v>
+        <v>0.5167364016736402</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2717731541152641</v>
+        <v>0.2447698744769874</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2642238998342846</v>
+        <v>0.2384937238493724</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05129694154084419</v>
+        <v>0.075123706702654</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6601473524492966</v>
+        <v>0.4629405730520928</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2564734495342519</v>
+        <v>0.3782169234398582</v>
       </c>
       <c r="S4" t="n">
-        <v>0.08337919801645156</v>
+        <v>0.1588425035080489</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1961444063988455</v>
+        <v>-0.05379582862154741</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1961444063988455</v>
+        <v>-0.05379582862154741</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6601473524492966</v>
+        <v>0.4629405730520928</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,16 +876,19 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>2.215177071547251</v>
+        <v>-0.05379582862154741</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.215177071547251</v>
+        <v>1.058433702580262</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.058433702580262</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -882,12 +896,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bochum</t>
+          <t>holstein kiel</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>b  monchengladbach</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +921,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="J5" t="n">
         <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3888834331729352</v>
+        <v>0.296097934200459</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2646567809093587</v>
+        <v>0.2631981637337414</v>
       </c>
       <c r="N5" t="n">
-        <v>0.346459785917706</v>
+        <v>0.4407039020657995</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04957740672026389</v>
+        <v>0.05539405684754528</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2944810525548903</v>
+        <v>0.1554765193282126</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4273155015522135</v>
+        <v>0.3886075687926011</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2782034458928962</v>
+        <v>0.4559159118791863</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1626587206428548</v>
+        <v>0.01521200981338677</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1626587206428548</v>
+        <v>0.01521200981338677</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4273155015522135</v>
+        <v>0.4559159118791863</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,16 +978,19 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>1.526229064225069</v>
+        <v>0.01521200981338677</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.526229064225069</v>
+        <v>1.218780583971704</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.218780583971704</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -981,12 +998,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>stuttgart</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1023,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5167364016736402</v>
+        <v>0.5932203389830508</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2447698744769874</v>
+        <v>0.2259887005649717</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2384937238493724</v>
+        <v>0.1807909604519774</v>
       </c>
       <c r="O6" t="n">
-        <v>0.075123706702654</v>
+        <v>0.0535714285714286</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4629405730520928</v>
+        <v>0.539792983116164</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3782169234398582</v>
+        <v>0.3224578409192884</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1588425035080489</v>
+        <v>0.1377491759645477</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.05379582862154741</v>
+        <v>-0.05342735586688685</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.05379582862154741</v>
+        <v>-0.05342735586688685</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4629405730520928</v>
+        <v>0.539792983116164</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,16 +1080,19 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>1.058433702580262</v>
+        <v>-0.05342735586688685</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.058433702580262</v>
+        <v>1.258199643682852</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.258199643682852</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1080,12 +1100,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>holstein kiel</t>
+          <t>werder bremen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>wolfsburg</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1125,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3057915057915058</v>
+        <v>0.2528714338643941</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2633204633204633</v>
+        <v>0.2673212300852167</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4308880308880308</v>
+        <v>0.479807336050389</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05490387748452275</v>
+        <v>0.06880506880506898</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1495829533343152</v>
+        <v>0.1399741911688833</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3898711388722733</v>
+        <v>0.3743520197213582</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4605459077934116</v>
+        <v>0.4856737891097586</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.02965787690538074</v>
+        <v>0.005866453059369559</v>
       </c>
       <c r="W7" t="n">
         <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>0.02965787690538074</v>
+        <v>0.005866453059369559</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4605459077934116</v>
+        <v>0.4856737891097586</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1182,32 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>1.26812873419587</v>
+        <v>0.005866453059369559</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.26812873419587</v>
+        <v>1.271586072088936</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.271586072088936</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45535.5625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>stuttgart</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1227,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5932203389830508</v>
+        <v>0.5190138736400838</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2259887005649717</v>
+        <v>0.2435372791695778</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1807909604519774</v>
+        <v>0.2374488471903384</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0535714285714286</v>
+        <v>0.05285834384195032</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.539792983116164</v>
+        <v>0.3894322903000509</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3224578409192884</v>
+        <v>0.3161555809281153</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1377491759645477</v>
+        <v>0.2944121287718337</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.05342735586688685</v>
+        <v>-0.1295815833400328</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.05342735586688685</v>
+        <v>-0.1295815833400328</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.539792983116164</v>
+        <v>0.3894322903000509</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1284,32 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>1.258199643682852</v>
+        <v>-0.1295815833400328</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.258199643682852</v>
+        <v>0.6722186943121771</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.6722186943121771</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45536.4375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1329,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2528714338643941</v>
+        <v>0.3772968558595345</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2673212300852167</v>
+        <v>0.2858309514087382</v>
       </c>
       <c r="N9" t="n">
-        <v>0.479807336050389</v>
+        <v>0.3368721927317272</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06880506880506898</v>
+        <v>0.06017316017316032</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1399741911688833</v>
+        <v>0.345798198928346</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3743520197213582</v>
+        <v>0.4220051128978362</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4856737891097586</v>
+        <v>0.2321966881738179</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.005866453059369559</v>
+        <v>0.136174161489098</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.005866453059369559</v>
+        <v>0.136174161489098</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4856737891097586</v>
+        <v>0.4220051128978362</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1386,32 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>1.271586072088936</v>
+        <v>0.136174161489098</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.271586072088936</v>
+        <v>1.443977379973941</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.443977379973941</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.52083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bayer leverkusen</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1431,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.85</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>11</v>
       </c>
       <c r="L10" t="n">
-        <v>0.509891622226045</v>
+        <v>0.7809330628803246</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2418716669533804</v>
+        <v>0.1338742393509128</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2482367108205746</v>
+        <v>0.08519269776876268</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06010869168763899</v>
+        <v>0.0670995670995671</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3894322903000509</v>
+        <v>0.6526417007134011</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3161555809281153</v>
+        <v>0.258353778745503</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2944121287718337</v>
+        <v>0.08900452054109596</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.1204593319259941</v>
+        <v>-0.1282913621669235</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1204593319259941</v>
+        <v>-0.1282913621669235</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3894322903000509</v>
+        <v>0.6526417007134011</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.85</v>
+        <v>1.2</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,208 +1488,13 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>0.6958174291644785</v>
+        <v>-0.1282913621669235</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.6958174291644785</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45536.4375</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>heidenheim</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>augsburg</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>59</v>
-      </c>
-      <c r="F11" t="n">
-        <v>591</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.4134954884268341</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.2797175362887407</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.3067869752844253</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.05148090091576596</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.3466060813416837</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.4215332068447334</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.2318607118135829</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
-        <v>0.1418156705559927</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.1418156705559927</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.4215332068447334</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.457350842869996</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.457350842869996</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2T6mXfPa</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45536.52083333334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>bayern munich</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>freiburg</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>59</v>
-      </c>
-      <c r="F12" t="n">
-        <v>591</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.7809330628803246</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.1338742393509128</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.08519269776876268</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.0670995670995671</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.6360072866567322</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.2644155838728855</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.09957712947038226</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
-        <v>-0.1449257762235924</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-0.1449257762235924</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.6360072866567322</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.270399359717771</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.270399359717771</v>
+        <v>1.356463886758235</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.356463886758235</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,15 +565,10 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>dif_prob_limited</t>
+          <t>multiplier</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>multiplier</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -672,12 +667,9 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0.15</v>
+        <v>2.035160561602784</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.035160561602784</v>
-      </c>
-      <c r="AD2" t="n">
         <v>2.035160561602784</v>
       </c>
     </row>
@@ -774,12 +766,9 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0.15</v>
+        <v>1.493481688773396</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.493481688773396</v>
-      </c>
-      <c r="AD3" t="n">
         <v>1.493481688773396</v>
       </c>
     </row>
@@ -876,12 +865,9 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-0.05379582862154741</v>
+        <v>1.058433702580262</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.058433702580262</v>
-      </c>
-      <c r="AD4" t="n">
         <v>1.058433702580262</v>
       </c>
     </row>
@@ -978,12 +964,9 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0.01521200981338677</v>
+        <v>1.218780583971704</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.218780583971704</v>
-      </c>
-      <c r="AD5" t="n">
         <v>1.218780583971704</v>
       </c>
     </row>
@@ -1080,12 +1063,9 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>-0.05342735586688685</v>
+        <v>1.258199643682852</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.258199643682852</v>
-      </c>
-      <c r="AD6" t="n">
         <v>1.258199643682852</v>
       </c>
     </row>
@@ -1182,12 +1162,9 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>0.005866453059369559</v>
+        <v>1.271586072088936</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.271586072088936</v>
-      </c>
-      <c r="AD7" t="n">
         <v>1.271586072088936</v>
       </c>
     </row>
@@ -1284,12 +1261,9 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>-0.1295815833400328</v>
+        <v>0.6722186943121771</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.6722186943121771</v>
-      </c>
-      <c r="AD8" t="n">
         <v>0.6722186943121771</v>
       </c>
     </row>
@@ -1386,12 +1360,9 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>0.136174161489098</v>
+        <v>1.443977379973941</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.443977379973941</v>
-      </c>
-      <c r="AD9" t="n">
         <v>1.443977379973941</v>
       </c>
     </row>
@@ -1488,12 +1459,9 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>-0.1282913621669235</v>
+        <v>1.356463886758235</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.356463886758235</v>
-      </c>
-      <c r="AD10" t="n">
         <v>1.356463886758235</v>
       </c>
     </row>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4640029460504511</v>
+        <v>0.4803370786516853</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2717731541152641</v>
+        <v>0.2668539325842696</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2642238998342846</v>
+        <v>0.2528089887640449</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05129694154084419</v>
+        <v>0.04093567251461994</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6367051529275674</v>
+        <v>0.6297801158206143</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2736915926060542</v>
+        <v>0.2787482353976901</v>
       </c>
       <c r="S2" t="n">
-        <v>0.08960325446637839</v>
+        <v>0.09147164878169556</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1727022068771163</v>
+        <v>0.149443037168929</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1727022068771163</v>
+        <v>0.149443037168929</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6367051529275674</v>
+        <v>0.6297801158206143</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>2.035160561602784</v>
+        <v>2.762433692723559</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.035160561602784</v>
+        <v>2.762433692723559</v>
       </c>
     </row>
     <row r="3">
@@ -709,53 +709,53 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="J3" t="n">
         <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3888834331729352</v>
+        <v>0.3734248358279596</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2646567809093587</v>
+        <v>0.2645092587114714</v>
       </c>
       <c r="N3" t="n">
-        <v>0.346459785917706</v>
+        <v>0.3620659054605692</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04957740672026389</v>
+        <v>0.05016277740500508</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2944810525548903</v>
+        <v>0.2972399663468631</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4273155015522135</v>
+        <v>0.4269036452393538</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2782034458928962</v>
+        <v>0.275856388413783</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1626587206428548</v>
+        <v>0.1623943865278825</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1626587206428548</v>
+        <v>0.1623943865278825</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4273155015522135</v>
+        <v>0.4269036452393538</v>
       </c>
       <c r="Z3" t="n">
         <v>3.6</v>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>1.493481688773396</v>
+        <v>1.994486216976943</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.493481688773396</v>
+        <v>1.994486216976943</v>
       </c>
     </row>
     <row r="4">
@@ -814,47 +814,47 @@
         <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5167364016736402</v>
+        <v>0.5198358413132695</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2447698744769874</v>
+        <v>0.2462380300957592</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2384937238493724</v>
+        <v>0.2339261285909713</v>
       </c>
       <c r="O4" t="n">
-        <v>0.075123706702654</v>
+        <v>0.06871345029239762</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4629405730520928</v>
+        <v>0.4566852233153452</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3782169234398582</v>
+        <v>0.3809080728794988</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1588425035080489</v>
+        <v>0.1624067038051559</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.05379582862154741</v>
+        <v>-0.06315061799792432</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.05379582862154741</v>
+        <v>-0.06315061799792432</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4629405730520928</v>
+        <v>0.4566852233153452</v>
       </c>
       <c r="Z4" t="n">
         <v>1.8</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>1.058433702580262</v>
+        <v>1.48964493470624</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.058433702580262</v>
+        <v>1.48964493470624</v>
       </c>
     </row>
     <row r="5">
@@ -931,29 +931,29 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1554765193282126</v>
+        <v>0.1514538444399252</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3886075687926011</v>
+        <v>0.3870476271589403</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4559159118791863</v>
+        <v>0.4614985284011345</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.01521200981338677</v>
+        <v>0.02079462633533496</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01521200981338677</v>
+        <v>0.02079462633533496</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4559159118791863</v>
+        <v>0.4614985284011345</v>
       </c>
       <c r="Z5" t="n">
         <v>2.15</v>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>1.218780583971704</v>
+        <v>1.825622309421007</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.218780583971704</v>
+        <v>1.825622309421007</v>
       </c>
     </row>
     <row r="6">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K6" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5932203389830508</v>
+        <v>0.5816922989614663</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2259887005649717</v>
+        <v>0.2298393961750184</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1807909604519774</v>
+        <v>0.1884683048635151</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0535714285714286</v>
+        <v>0.06118638964167422</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.539792983116164</v>
+        <v>0.5411474257773473</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3224578409192884</v>
+        <v>0.3218229682050365</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1377491759645477</v>
+        <v>0.1370296060176162</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.05342735586688685</v>
+        <v>-0.04054487318411903</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.05342735586688685</v>
+        <v>-0.04054487318411903</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.539792983116164</v>
+        <v>0.5411474257773473</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>1.258199643682852</v>
+        <v>1.894928798370925</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.258199643682852</v>
+        <v>1.894928798370925</v>
       </c>
     </row>
     <row r="7">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J7" t="n">
         <v>3.7</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K7" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2528714338643941</v>
+        <v>0.2280041081821294</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2673212300852167</v>
+        <v>0.2526532009585758</v>
       </c>
       <c r="N7" t="n">
-        <v>0.479807336050389</v>
+        <v>0.5193426908592949</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06880506880506898</v>
+        <v>0.06972826485021599</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1399741911688833</v>
+        <v>0.1419416928438318</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3743520197213582</v>
+        <v>0.3752684862615773</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4856737891097586</v>
+        <v>0.4827898208945908</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.005866453059369559</v>
+        <v>-0.03655286996470403</v>
       </c>
       <c r="W7" t="n">
         <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>0.005866453059369559</v>
+        <v>-0.03655286996470403</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4856737891097586</v>
+        <v>0.4827898208945908</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>1.271586072088936</v>
+        <v>1.68913890836943</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.271586072088936</v>
+        <v>1.68913890836943</v>
       </c>
     </row>
     <row r="8">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5190138736400838</v>
+        <v>0.5393258426966292</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2435372791695778</v>
+        <v>0.2359550561797753</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2374488471903384</v>
+        <v>0.2247191011235955</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05285834384195032</v>
+        <v>0.05952380952380953</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3894322903000509</v>
+        <v>0.3839512902815304</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3161555809281153</v>
+        <v>0.3170760805874334</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2944121287718337</v>
+        <v>0.2989726291310363</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.1295815833400328</v>
+        <v>-0.1553745524150988</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1295815833400328</v>
+        <v>-0.1553745524150988</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3894322903000509</v>
+        <v>0.3839512902815304</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>0.6722186943121771</v>
+        <v>0.8652305925669825</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.6722186943121771</v>
+        <v>0.8652305925669825</v>
       </c>
     </row>
     <row r="9">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>1.443977379973941</v>
+        <v>1.975943822505304</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.443977379973941</v>
+        <v>1.975943822505304</v>
       </c>
     </row>
     <row r="10">
@@ -1426,29 +1426,29 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6526417007134011</v>
+        <v>0.6441791259908952</v>
       </c>
       <c r="R10" t="n">
-        <v>0.258353778745503</v>
+        <v>0.2630939763086747</v>
       </c>
       <c r="S10" t="n">
-        <v>0.08900452054109596</v>
+        <v>0.09272689770043006</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.1282913621669235</v>
+        <v>-0.1367539368894294</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1282913621669235</v>
+        <v>-0.1367539368894294</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.6526417007134011</v>
+        <v>0.6441791259908952</v>
       </c>
       <c r="Z10" t="n">
         <v>1.2</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>1.356463886758235</v>
+        <v>1.920754496488732</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.356463886758235</v>
+        <v>1.920754496488732</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45534.64583333334</v>
+        <v>45535.4375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>st  pauli</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4803370786516853</v>
+        <v>0.3533568904593639</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2668539325842696</v>
+        <v>0.265017667844523</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2528089887640449</v>
+        <v>0.3816254416961131</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04093567251461994</v>
+        <v>0.04814814814814827</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6297801158206143</v>
+        <v>0.2938564130461177</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2787482353976901</v>
+        <v>0.426822698542927</v>
       </c>
       <c r="S2" t="n">
-        <v>0.09147164878169556</v>
+        <v>0.2793208884109552</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.149443037168929</v>
+        <v>0.1618050306984041</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.149443037168929</v>
+        <v>0.1618050306984041</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6297801158206143</v>
+        <v>0.426822698542927</v>
       </c>
       <c r="Z2" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,16 +667,16 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>2.762433692723559</v>
+        <v>1.994179809777464</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.762433692723559</v>
+        <v>1.994179809777464</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -684,12 +684,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bochum</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>b  monchengladbach</t>
+          <t>hoffenheim</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>2.63</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3734248358279596</v>
+        <v>0.5290697674418605</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2645092587114714</v>
+        <v>0.2267441860465116</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3620659054605692</v>
+        <v>0.2441860465116279</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05016277740500508</v>
+        <v>0.05006105006105011</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2972399663468631</v>
+        <v>0.4708083309583022</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4269036452393538</v>
+        <v>0.3811860625703036</v>
       </c>
       <c r="S3" t="n">
-        <v>0.275856388413783</v>
+        <v>0.1480056064713942</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1623943865278825</v>
+        <v>-0.05826143648355836</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1623943865278825</v>
+        <v>-0.05826143648355836</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4269036452393538</v>
+        <v>0.4708083309583022</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,16 +766,16 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>1.994486216976943</v>
+        <v>1.561612075226278</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.994486216976943</v>
+        <v>1.561612075226278</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -783,12 +783,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>holstein kiel</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5198358413132695</v>
+        <v>0.3079833522512297</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2462380300957592</v>
+        <v>0.2580401059402194</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2339261285909713</v>
+        <v>0.4339765418085509</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06871345029239762</v>
+        <v>0.04739636997701502</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4566852233153452</v>
+        <v>0.1581151798668755</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3809080728794988</v>
+        <v>0.3901184052593505</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1624067038051559</v>
+        <v>0.451766414873774</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.06315061799792432</v>
+        <v>0.01778987306522306</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.06315061799792432</v>
+        <v>0.01778987306522306</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4566852233153452</v>
+        <v>0.451766414873774</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>1.48964493470624</v>
+        <v>1.777409499537162</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.48964493470624</v>
+        <v>1.777409499537162</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -882,12 +882,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>holstein kiel</t>
+          <t>stuttgart</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>wolfsburg</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3.2</v>
+        <v>1.65</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="K5" t="n">
-        <v>2.15</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.296097934200459</v>
+        <v>0.5804311774461028</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2631981637337414</v>
+        <v>0.2280265339966833</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4407039020657995</v>
+        <v>0.1915422885572139</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05539405684754528</v>
+        <v>0.04415584415584406</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1514538444399252</v>
+        <v>0.4902520027614342</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3870476271589403</v>
+        <v>0.3267975762170628</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4614985284011345</v>
+        <v>0.1829504210215032</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.02079462633533496</v>
+        <v>-0.09017917468466868</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02079462633533496</v>
+        <v>-0.09017917468466868</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4614985284011345</v>
+        <v>0.4902520027614342</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>1.825622309421007</v>
+        <v>1.514394042621623</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.825622309421007</v>
+        <v>1.514394042621623</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -981,12 +981,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>stuttgart</t>
+          <t>werder bremen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.62</v>
+        <v>3.9</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5816922989614663</v>
+        <v>0.2449114678139998</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2298393961750184</v>
+        <v>0.2387886811186497</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1884683048635151</v>
+        <v>0.5162998510673507</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06118638964167422</v>
+        <v>0.04695079695079674</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5411474257773473</v>
+        <v>0.1355951324524358</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3218229682050365</v>
+        <v>0.3623243469936115</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1370296060176162</v>
+        <v>0.5020805205539526</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.04054487318411903</v>
+        <v>-0.01421933051339808</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.04054487318411903</v>
+        <v>-0.01421933051339808</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5411474257773473</v>
+        <v>0.5020805205539526</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>1.894928798370925</v>
+        <v>1.846698970723272</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.894928798370925</v>
+        <v>1.846698970723272</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45535.5625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K7" t="n">
         <v>4.1</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.8</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.2280041081821294</v>
+        <v>0.5424476295479603</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2526532009585758</v>
+        <v>0.2260198456449835</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5193426908592949</v>
+        <v>0.2315325248070562</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06972826485021599</v>
+        <v>0.05342624854819977</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1419416928438318</v>
+        <v>0.4699022232407611</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3752684862615773</v>
+        <v>0.3262462883616376</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4827898208945908</v>
+        <v>0.2038514883976014</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.03655286996470403</v>
+        <v>-0.07254540630719924</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.03655286996470403</v>
+        <v>-0.07254540630719924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4827898208945908</v>
+        <v>0.4699022232407611</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1162,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>1.68913890836943</v>
+        <v>1.504113136730728</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.68913890836943</v>
+        <v>1.504113136730728</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.4375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bayer leverkusen</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5393258426966292</v>
+        <v>0.3883495145631068</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2359550561797753</v>
+        <v>0.2718446601941747</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2247191011235955</v>
+        <v>0.3398058252427185</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05952380952380953</v>
+        <v>0.05102040816326525</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3839512902815304</v>
+        <v>0.3564029345553034</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3170760805874334</v>
+        <v>0.4294844966159586</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2989726291310363</v>
+        <v>0.2141125688287381</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.1553745524150988</v>
+        <v>0.1576398364217838</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1553745524150988</v>
+        <v>0.1576398364217838</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3839512902815304</v>
+        <v>0.4294844966159586</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1261,29 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>0.8652305925669825</v>
+        <v>2.004255503155188</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.8652305925669825</v>
+        <v>2.004255503155188</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45536.4375</v>
+        <v>45536.52083333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>11</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3772968558595345</v>
+        <v>0.7942238267148014</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2858309514087382</v>
+        <v>0.1191335740072202</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3368721927317272</v>
+        <v>0.08664259927797834</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06017316017316032</v>
+        <v>0.04924242424242431</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.345798198928346</v>
+        <v>0.6268951432858159</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4220051128978362</v>
+        <v>0.2780414885682527</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2321966881738179</v>
+        <v>0.09506336814593143</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.136174161489098</v>
+        <v>-0.1673286834289855</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.136174161489098</v>
+        <v>-0.1673286834289855</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4220051128978362</v>
+        <v>0.6268951432858159</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1360,29 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>1.975943822505304</v>
+        <v>1.739595044086204</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.975943822505304</v>
+        <v>1.739595044086204</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45536.52083333334</v>
+        <v>45548.64583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1402,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="K10" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7809330628803246</v>
+        <v>0.7046463956269218</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1338742393509128</v>
+        <v>0.1703963102152375</v>
       </c>
       <c r="N10" t="n">
-        <v>0.08519269776876268</v>
+        <v>0.1249572941578408</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0670995670995671</v>
+        <v>0.06703121439963544</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6441791259908952</v>
+        <v>0.6517349581870295</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2630939763086747</v>
+        <v>0.2694621337434124</v>
       </c>
       <c r="S10" t="n">
-        <v>0.09272689770043006</v>
+        <v>0.078802908069558</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.1367539368894294</v>
+        <v>-0.05291143743989224</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1367539368894294</v>
+        <v>-0.05291143743989224</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.6441791259908952</v>
+        <v>0.6517349581870295</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,10 +1459,604 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>1.920754496488732</v>
+        <v>2.266724228087704</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.920754496488732</v>
+        <v>2.266724228087704</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UwsvBA74</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>b  monchengladbach</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" t="n">
+        <v>591</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3570181225503512</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2347394155768559</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.4082424618727929</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06501074557778153</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.2609738702362804</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3151971158037243</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.4238290139599953</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.01558655208720239</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.01558655208720239</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4238290139599953</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.663317948024701</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.663317948024701</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>bochum</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F12" t="n">
+        <v>591</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5210981189628877</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2501270971021861</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.2287747839349263</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.06612466124661243</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.5220803696232176</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3572046928668826</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.1207149375098998</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.0009822506603298642</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.0009822506603298642</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.5220803696232176</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.979946800894633</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.979946800894633</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>hoffenheim</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>bayer leverkusen</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F13" t="n">
+        <v>591</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.1877107530910453</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2502810041213938</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.562008242787561</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06546906187624746</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1885000430231332</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3498987717869242</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.4616011851899426</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.1004070575976184</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.1004070575976184</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4616011851899426</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.367226656419602</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.367226656419602</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>rb leipzig</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>union berlin</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>59</v>
+      </c>
+      <c r="F14" t="n">
+        <v>591</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6487025948103793</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2075848303393213</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.1437125748502994</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.07051282051282048</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.5556668482530058</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.2890699526820363</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1552631990649579</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.09303574655737346</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.09303574655737346</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.5556668482530058</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.751195620325689</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.751195620325689</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>wolfsburg</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>eintracht frankfurt</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>59</v>
+      </c>
+      <c r="F15" t="n">
+        <v>591</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.3988317051062543</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2603484741665827</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.3408198207271628</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06694605630775863</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.4341752177734234</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3142214322882965</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2516033499382802</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.03534351266716912</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.03534351266716912</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4341752177734234</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.777267333291799</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.777267333291799</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>holstein kiel</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>bayern munich</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>59</v>
+      </c>
+      <c r="F16" t="n">
+        <v>591</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1100846805234796</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.170130869899923</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.7197844495765975</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06869600987248026</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.05898923245477277</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.299416402447634</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.6415943650975932</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>-0.07819008447900433</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.07819008447900433</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.6415943650975932</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.132651923045866</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.132651923045866</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.4375</v>
+        <v>45548.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>dortmund</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>heidenheim</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>augsburg</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.45</v>
+        <v>1.33</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3883495145631068</v>
+        <v>0.7046463956269218</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2718446601941747</v>
+        <v>0.1703963102152375</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3398058252427185</v>
+        <v>0.1249572941578408</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05102040816326525</v>
+        <v>0.06703121439963544</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3531098058101107</v>
+        <v>0.6301985710788685</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4268674293428796</v>
+        <v>0.2676795307407086</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2200227648470096</v>
+        <v>0.1021218981804229</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1550227691487049</v>
+        <v>-0.07444782454805332</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1550227691487049</v>
+        <v>-0.07444782454805332</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4268674293428796</v>
+        <v>0.6301985710788685</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.5</v>
+        <v>1.33</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>2.849070184567517</v>
+        <v>3.005258616891353</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.849070184567517</v>
+        <v>3.005258616891353</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>UwsvBA74</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.52083333334</v>
+        <v>45549.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>stuttgart</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.2</v>
+        <v>2.88</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>2.1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7942238267148014</v>
+        <v>0.3253230559963727</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1191335740072202</v>
+        <v>0.2285196100657448</v>
       </c>
       <c r="N3" t="n">
-        <v>0.08664259927797834</v>
+        <v>0.4461573339378825</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04924242424242431</v>
+        <v>0.06731513743708861</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6335494808107793</v>
+        <v>0.4210235021706287</v>
       </c>
       <c r="R3" t="n">
-        <v>0.277645986166426</v>
+        <v>0.3165316368448189</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08880453302279478</v>
+        <v>0.2624448609845524</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.1606743459040221</v>
+        <v>0.09570044617425594</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1606743459040221</v>
+        <v>0.09570044617425594</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6335494808107793</v>
+        <v>0.4210235021706287</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.2</v>
+        <v>2.88</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,10 +766,703 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2.55710331072564</v>
+        <v>2.79421864569908</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.55710331072564</v>
+        <v>2.79421864569908</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>bochum</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F4" t="n">
+        <v>591</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5513666352497643</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2403393025447691</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.2082940622054665</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0668677727501259</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5497807657398153</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.3466749983914207</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1035442358687641</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>-0.001585869509948989</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.001585869509948989</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.5497807657398153</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.964399860755415</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.964399860755415</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>hoffenheim</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bayer leverkusen</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>59</v>
+      </c>
+      <c r="F5" t="n">
+        <v>591</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.1962039789618111</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2389663846329751</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.5648296364052138</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.07299717826033625</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1693339708254916</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.3486141249265957</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.4820519042479127</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>-0.08277773215730111</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.08277773215730111</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.4820519042479127</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.159101276368574</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.159101276368574</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>rb leipzig</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>union berlin</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>59</v>
+      </c>
+      <c r="F6" t="n">
+        <v>591</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6690140845070423</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1971830985915493</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1338028169014084</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.06766917293233088</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5229476823637116</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.2981622140607649</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1788901035755235</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>-0.1460664021433307</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.1460664021433307</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.5229476823637116</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.038010244696167</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.038010244696167</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>wolfsburg</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>eintracht frankfurt</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>59</v>
+      </c>
+      <c r="F7" t="n">
+        <v>591</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3828316115075915</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2605381800537775</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.3566302084386309</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.06616917996602956</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.3689414637850182</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3128188361313728</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.318239700083609</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>-0.0138901477225733</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.0138901477225733</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.3689414637850182</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.919963281553799</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.919963281553799</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>holstein kiel</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>bayern munich</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>59</v>
+      </c>
+      <c r="F8" t="n">
+        <v>591</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.1043121149897331</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1564681724845996</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.7392197125256674</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.06517935258092722</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.0461408642279726</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.229733226407653</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.7241259093643743</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>-0.01509380316129316</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.01509380316129316</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.7241259093643743</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.8341376239632</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.8341376239632</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CnrLfkNN</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45550.4375</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>augsburg</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>st  pauli</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>59</v>
+      </c>
+      <c r="F9" t="n">
+        <v>591</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4833968426782799</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2618399564507349</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.2547632008709853</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.06086856086856085</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.4869027209649518</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3141283469344534</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1989689321005948</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.003505878286671926</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.003505878286671926</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.4869027209649518</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.651916669295632</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.651916669295632</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8OhVCWxh</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45550.52083333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>mainz</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>werder bremen</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>59</v>
+      </c>
+      <c r="F10" t="n">
+        <v>591</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.4983388704318937</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2524916943521595</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2491694352159468</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.05614035087719293</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.3694368715495164</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3280747474602825</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.3024883809902011</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>-0.1289019988823773</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.1289019988823773</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.3694368715495164</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.300708102073062</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.300708102073062</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="J2" t="n">
         <v>5.5</v>
       </c>
       <c r="K2" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7046463956269218</v>
+        <v>0.6936936936936937</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1703963102152375</v>
+        <v>0.1715315315315316</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1249572941578408</v>
+        <v>0.1347747747747748</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06703121439963544</v>
+        <v>0.05996944232238333</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6301985710788685</v>
+        <v>0.6521697862719137</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2676795307407086</v>
+        <v>0.2473930088057053</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1021218981804229</v>
+        <v>0.100437204922381</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.07444782454805332</v>
+        <v>-0.04152390742178003</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.07444782454805332</v>
+        <v>-0.04152390742178003</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6301985710788685</v>
+        <v>0.6521697862719137</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>3.005258616891353</v>
+        <v>2.605834907921949</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.005258616891353</v>
+        <v>2.605834907921949</v>
       </c>
     </row>
     <row r="3">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="J3" t="n">
         <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3253230559963727</v>
+        <v>0.3465232424126009</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2285196100657448</v>
+        <v>0.2281982328082982</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4461573339378825</v>
+        <v>0.4252785247791011</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06731513743708861</v>
+        <v>0.06881826394021506</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4210235021706287</v>
+        <v>0.275887892844442</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3165316368448189</v>
+        <v>0.3220669943246212</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2624448609845524</v>
+        <v>0.4020451128309369</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.09570044617425594</v>
+        <v>-0.02323341194816414</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>0.09570044617425594</v>
+        <v>-0.02323341194816414</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4210235021706287</v>
+        <v>0.4020451128309369</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2.79421864569908</v>
+        <v>1.616519144530047</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.79421864569908</v>
+        <v>1.616519144530047</v>
       </c>
     </row>
     <row r="4">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5513666352497643</v>
+        <v>0.5391413189859399</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2403393025447691</v>
+        <v>0.2454511794330726</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2082940622054665</v>
+        <v>0.2154075015809875</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0668677727501259</v>
+        <v>0.07213945903485719</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5497807657398153</v>
+        <v>0.4443047500546431</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3466749983914207</v>
+        <v>0.4073931544228655</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1035442358687641</v>
+        <v>0.1483020955224915</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.001585869509948989</v>
+        <v>-0.09483656893129677</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.001585869509948989</v>
+        <v>-0.09483656893129677</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5497807657398153</v>
+        <v>0.4443047500546431</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>2.964399860755415</v>
+        <v>1.491300305332449</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.964399860755415</v>
+        <v>1.491300305332449</v>
       </c>
     </row>
     <row r="5">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K5" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1962039789618111</v>
+        <v>0.1710966987400989</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2389663846329751</v>
+        <v>0.2295199617245229</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5648296364052138</v>
+        <v>0.5993833395353783</v>
       </c>
       <c r="O5" t="n">
-        <v>0.07299717826033625</v>
+        <v>0.06266329600180764</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1693339708254916</v>
+        <v>0.06194325775018764</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3486141249265957</v>
+        <v>0.3557797658226646</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4820519042479127</v>
+        <v>0.5822769764271478</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.08277773215730111</v>
+        <v>-0.01710636310823044</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.08277773215730111</v>
+        <v>-0.01710636310823044</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4820519042479127</v>
+        <v>0.5822769764271478</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2.159101276368574</v>
+        <v>2.411776389765068</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.159101276368574</v>
+        <v>2.411776389765068</v>
       </c>
     </row>
     <row r="6">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="J6" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6690140845070423</v>
+        <v>0.6518832181858704</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1971830985915493</v>
+        <v>0.2057053710719857</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1338028169014084</v>
+        <v>0.142411410742144</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06766917293233088</v>
+        <v>0.08029372818105207</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5229476823637116</v>
+        <v>0.4402286847727962</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2981622140607649</v>
+        <v>0.3241353731897077</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1788901035755235</v>
+        <v>0.235635942037496</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.1460664021433307</v>
+        <v>-0.2116545334130742</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1460664021433307</v>
+        <v>-0.2116545334130742</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5229476823637116</v>
+        <v>0.4402286847727962</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>2.038010244696167</v>
+        <v>0.9754041143835822</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.038010244696167</v>
+        <v>0.9754041143835822</v>
       </c>
     </row>
     <row r="7">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="J7" t="n">
         <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3828316115075915</v>
+        <v>0.3620273531777956</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2605381800537775</v>
+        <v>0.2614641995172969</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3566302084386309</v>
+        <v>0.3765084473049075</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06616917996602956</v>
+        <v>0.06239316239316239</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3689414637850182</v>
+        <v>0.2069675172176749</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3128188361313728</v>
+        <v>0.3155790929892039</v>
       </c>
       <c r="S7" t="n">
-        <v>0.318239700083609</v>
+        <v>0.4774533897931211</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.0138901477225733</v>
+        <v>0.1009449424882136</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0138901477225733</v>
+        <v>0.1009449424882136</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3689414637850182</v>
+        <v>0.4774533897931211</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>1.919963281553799</v>
+        <v>2.464191199741273</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.919963281553799</v>
+        <v>2.464191199741273</v>
       </c>
     </row>
     <row r="8">
@@ -1207,53 +1207,53 @@
         <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="K8" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1043121149897331</v>
+        <v>0.1037344398340249</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1564681724845996</v>
+        <v>0.1493775933609958</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7392197125256674</v>
+        <v>0.7468879668049793</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06517935258092722</v>
+        <v>0.07111111111111112</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0461408642279726</v>
+        <v>0.01449579566287897</v>
       </c>
       <c r="R8" t="n">
-        <v>0.229733226407653</v>
+        <v>0.1792187644636374</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7241259093643743</v>
+        <v>0.8062854398734836</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.01509380316129316</v>
+        <v>0.05939747306850429</v>
       </c>
       <c r="W8" t="n">
         <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.01509380316129316</v>
+        <v>0.05939747306850429</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.7241259093643743</v>
+        <v>0.8062854398734836</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>3.8341376239632</v>
+        <v>3.694165197648735</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.8341376239632</v>
+        <v>3.694165197648735</v>
       </c>
     </row>
     <row r="9">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="J9" t="n">
         <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4833968426782799</v>
+        <v>0.4640029460504511</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2618399564507349</v>
+        <v>0.2642238998342846</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2547632008709853</v>
+        <v>0.2717731541152641</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06086856086856085</v>
+        <v>0.05129694154084419</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4869027209649518</v>
+        <v>0.2974476288799689</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3141283469344534</v>
+        <v>0.4344291760472956</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1989689321005948</v>
+        <v>0.2681231950727354</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.003505878286671926</v>
+        <v>0.170205276213011</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003505878286671926</v>
+        <v>0.170205276213011</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4869027209649518</v>
+        <v>0.4344291760472956</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>2.651916669295632</v>
+        <v>2.280592158221691</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.651916669295632</v>
+        <v>2.280592158221691</v>
       </c>
     </row>
     <row r="10">
@@ -1402,56 +1402,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4983388704318937</v>
+        <v>0.473491773308958</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2524916943521595</v>
+        <v>0.2559414990859232</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2491694352159468</v>
+        <v>0.2705667276051189</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05614035087719293</v>
+        <v>0.05598455598455576</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3694368715495164</v>
+        <v>0.2802764840529549</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3280747474602825</v>
+        <v>0.3886144100375855</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3024883809902011</v>
+        <v>0.3311091059094596</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.1289019988823773</v>
+        <v>0.1326729109516623</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1289019988823773</v>
+        <v>0.1326729109516623</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3694368715495164</v>
+        <v>0.3886144100375855</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,10 +1459,901 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>1.300708102073062</v>
+        <v>2.085084875357217</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.300708102073062</v>
+        <v>2.085084875357217</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>dCL13J5e</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45555.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>augsburg</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>mainz</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" t="n">
+        <v>591</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.375767498976668</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2762996316004912</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.3479328694228407</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06448801742919397</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.2246809074918049</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.4330810099541464</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.3422380825540488</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.1567813783536552</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1567813783536552</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4330810099541464</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.274839072204276</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.274839072204276</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pY1dP0SE</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bochum</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>holstein kiel</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F12" t="n">
+        <v>591</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4851944345344275</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2782732786300393</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.2365322868355333</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.05693815987933637</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.3906853740595259</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3493616931744958</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.2599529327659784</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.0945090604749016</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.0945090604749016</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.3906853740595259</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.263885671826282</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.263885671826282</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>heidenheim</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F13" t="n">
+        <v>591</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.375767498976668</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2762996316004912</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.3479328694228407</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06448801742919397</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.3180876397036733</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3522621892191041</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.3296501710772227</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.07596255761861287</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.07596255761861287</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.3522621892191041</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.827381519133489</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.827381519133489</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>union berlin</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>hoffenheim</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>59</v>
+      </c>
+      <c r="F14" t="n">
+        <v>591</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.4093097913322633</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2768860353130017</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3138041733547351</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06223358908780896</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3358295024682346</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3902985262178974</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.2738719713138679</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.1134124909048957</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.1134124909048957</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.3902985262178974</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.092271575347588</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.092271575347588</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>werder bremen</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>bayern munich</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>59</v>
+      </c>
+      <c r="F15" t="n">
+        <v>591</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.1439701173959445</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.1970117395944503</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.6590181430096052</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06859782174830364</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.02401729133322567</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.2491012201425768</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.7268814885241974</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.06786334551459228</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.06786334551459228</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.7268814885241974</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.391448142299144</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.391448142299144</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>eintracht frankfurt</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>b  monchengladbach</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>59</v>
+      </c>
+      <c r="F16" t="n">
+        <v>591</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.5221774193548387</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2540322580645161</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.2237903225806452</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06392106392106389</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2640634116133532</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.4066768673448945</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.3292597210417523</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.1526446092803784</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.1526446092803784</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4066768673448945</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.162163561064333</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.162163561064333</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45557.4375</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>bayer leverkusen</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>wolfsburg</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>59</v>
+      </c>
+      <c r="F17" t="n">
+        <v>591</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.678820791311094</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1873545384018619</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1338246702870442</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06749482401656315</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.3739466352486511</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3939930287248131</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2320603360265359</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.2066384903229511</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.2066384903229511</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.3939930287248131</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.108037281681437</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.108037281681437</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45557.52083333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>dortmund</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>59</v>
+      </c>
+      <c r="F18" t="n">
+        <v>591</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.3937947494033414</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2625298329355609</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3436754176610979</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.05808080808080796</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.08589391203498097</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.2617593806790985</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.6523467072859205</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.3086712896248226</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.3086712896248226</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.6523467072859205</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>3.210520828204814</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.210520828204814</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45557.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>st  pauli</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>rb leipzig</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>59</v>
+      </c>
+      <c r="F19" t="n">
+        <v>591</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.1789903110657828</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2409484956654768</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.5800611932687404</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.06417039750373088</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.0825888751624162</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2678222701325234</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.6495888547050603</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.06952766143631994</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.06952766143631994</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.6495888547050603</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.068716232316248</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.068716232316248</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,11 +577,11 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>dCL13J5e</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.4375</v>
+        <v>45555.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>st  pauli</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,53 +610,53 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="J2" t="n">
         <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4509283819628647</v>
+        <v>0.3859649122807017</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2705570291777188</v>
+        <v>0.2701754385964912</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2785145888594164</v>
+        <v>0.343859649122807</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05602240896358546</v>
+        <v>0.0575139146567718</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2743164930647941</v>
+        <v>0.2200578825859809</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4490411663621273</v>
+        <v>0.4055704857505991</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2766423405730786</v>
+        <v>0.37437163166342</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1784841371844085</v>
+        <v>0.1353950471541079</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1784841371844085</v>
+        <v>0.1353950471541079</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4490411663621273</v>
+        <v>0.4055704857505991</v>
       </c>
       <c r="Z2" t="n">
         <v>3.5</v>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>2.342946520635968</v>
+        <v>4.284393209359865</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.342946520635968</v>
+        <v>4.284393209359865</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>pY1dP0SE</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.52083333334</v>
+        <v>45556.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>holstein kiel</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,67 +709,1651 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>0.473491773308958</v>
+        <v>0.4861111111111112</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2559414990859232</v>
+        <v>0.2708333333333333</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2705667276051189</v>
+        <v>0.2430555555555556</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05598455598455576</v>
+        <v>0.05494505494505497</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3254690356489645</v>
+        <v>0.4043013681521349</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3653762396167273</v>
+        <v>0.354726561336707</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3091547247343083</v>
+        <v>0.240972070511158</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.109434740530804</v>
+        <v>-0.08180974295897625</v>
       </c>
       <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.08180974295897625</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.4043013681521349</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.732914535154623</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.732914535154623</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>heidenheim</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F4" t="n">
+        <v>591</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3479328694228407</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2762996316004912</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.375767498976668</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.06448801742919397</v>
+      </c>
+      <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="X3" t="n">
-        <v>0.109434740530804</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.3653762396167273</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="Q4" t="n">
+        <v>0.3173817778480428</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.35255214608097</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.3300660760709871</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>0.07625251448047882</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.07625251448047882</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.35255214608097</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA4" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AB3" t="n">
-        <v>1.985919650836356</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.985919650836356</v>
+      <c r="AB4" t="n">
+        <v>3.633850922139507</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.633850922139507</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>union berlin</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>hoffenheim</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>59</v>
+      </c>
+      <c r="F5" t="n">
+        <v>591</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4471544715447154</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2682926829268293</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.2845528455284553</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.06493506493506485</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.3275806931514269</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.3995376946676207</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.2728816121809524</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.1312450117407914</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.1312450117407914</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.3995376946676207</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>4.2332690834904</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.2332690834904</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>werder bremen</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bayern munich</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>59</v>
+      </c>
+      <c r="F6" t="n">
+        <v>591</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.1338246702870442</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1873545384018619</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.6788207913110939</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.06749482401656337</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.01950023530550831</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.2344056638602497</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.746094100834242</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.06727330952314814</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.06727330952314814</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.746094100834242</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>6.892779360876074</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>6.892779360876074</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>eintracht frankfurt</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>b  monchengladbach</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>59</v>
+      </c>
+      <c r="F7" t="n">
+        <v>591</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5425559600191486</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2406722591879813</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.21677178079287</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.06539182070827154</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.2619964027976606</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.4051360552278787</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.3328675419744606</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.1644637960398973</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.1644637960398973</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.4051360552278787</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.280711682779612</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.280711682779612</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45557.4375</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bayer leverkusen</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>wolfsburg</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>59</v>
+      </c>
+      <c r="F8" t="n">
+        <v>591</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.7197844495765973</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.170130869899923</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.1100846805234796</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.06869600987248048</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.3867146001136043</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3870007073448847</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.226284692541511</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.2168698374449617</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.2168698374449617</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.3870007073448847</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>4.127025968306146</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.127025968306146</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45557.52083333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>dortmund</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>59</v>
+      </c>
+      <c r="F9" t="n">
+        <v>591</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4055228347977214</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2541276431399054</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.3403495220623733</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.04934143870314078</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.07524729583176168</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.2264390827402074</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.6983136214280308</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.3579640993656575</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.3579640993656575</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.6983136214280308</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>6.765207928441032</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>6.765207928441032</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45557.60416666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>st  pauli</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>rb leipzig</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>59</v>
+      </c>
+      <c r="F10" t="n">
+        <v>591</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.1882404563405002</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2413339183852567</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.5704256252742431</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.06247086247086253</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.08338334869124665</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.2743570026545971</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.6422596486541563</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.07183402337991318</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.07183402337991318</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.6422596486541563</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>6.051496607376852</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>6.051496607376852</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rsNyMnwK</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45562.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>dortmund</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>bochum</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" t="n">
+        <v>591</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.7419115512402826</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1638656817522016</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0942227670075159</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06131461828141038</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.7996942646087062</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.1670784112694209</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.03322732412187282</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.05778271336842355</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.05778271336842355</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.7996942646087062</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>7.266580319010007</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.266580319010007</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>b  monchengladbach</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>union berlin</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F12" t="n">
+        <v>591</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4664634146341464</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2591463414634146</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.274390243902439</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.07189542483660127</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.3050668382830748</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3118030646433951</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.38313009707353</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.108739853171091</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.108739853171091</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.38313009707353</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>4.094224970561885</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.094224970561885</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>st  pauli</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F13" t="n">
+        <v>591</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5468942289008355</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2383897920849796</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.2147159790141848</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.07559243274499372</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.5667186379892287</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3189632088281983</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1143181531825728</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.01982440908839322</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.01982440908839322</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.5667186379892287</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>4.970584950515239</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.970584950515239</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>mainz</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>heidenheim</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>59</v>
+      </c>
+      <c r="F14" t="n">
+        <v>591</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5513666352497643</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2403393025447691</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.2082940622054665</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0668677727501259</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3454135085836392</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.335088664056902</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3194978273594588</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.205953126666125</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.205953126666125</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.3454135085836392</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.181839387588149</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.181839387588149</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>rb leipzig</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>augsburg</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>59</v>
+      </c>
+      <c r="F15" t="n">
+        <v>591</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6934812760055478</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.188626907073509</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1178918169209431</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06029411764705883</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.5084774707898273</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3376759526651047</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.153846576545068</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-0.1850038052157205</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.1850038052157205</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.5084774707898273</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.741236712295176</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.741236712295176</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>wolfsburg</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>59</v>
+      </c>
+      <c r="F16" t="n">
+        <v>591</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3027681660899654</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2502883506343714</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.4469434832756632</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06543778801843314</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.3171420371343472</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3091250411221166</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.3737329217435362</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>-0.07321056153212702</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.07321056153212702</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.3737329217435362</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.546738774592391</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.546738774592391</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>bayern munich</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>bayer leverkusen</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>59</v>
+      </c>
+      <c r="F17" t="n">
+        <v>591</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.4689603590127151</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2468212415856395</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2842183994016455</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06618819776714502</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.3368076471299556</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.389315328275623</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2738770245944215</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.1424940866899835</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.1424940866899835</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.389315328275623</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>4.146640930961994</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.146640930961994</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45564.4375</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>holstein kiel</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>eintracht frankfurt</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>59</v>
+      </c>
+      <c r="F18" t="n">
+        <v>591</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2180839497146315</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2360758755660886</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.54584017471928</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.05898156429801493</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.03546160964513555</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.2105706752994542</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.7539677150554103</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.2081275403361302</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.2081275403361302</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.7539677150554103</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>7.236841513728779</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.236841513728779</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45564.52083333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>hoffenheim</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>werder bremen</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>59</v>
+      </c>
+      <c r="F19" t="n">
+        <v>591</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.443213296398892</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2659279778393352</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.2908587257617729</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.07440476190476186</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2523896731336179</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.337836971759304</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.4097733551070781</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.1189146293453052</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.1189146293453052</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.4097733551070781</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>4.320009894744478</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.320009894744478</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>rsNyMnwK</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.4375</v>
+        <v>45562.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>st  pauli</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,86 +610,88 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4509283819628647</v>
+        <v>0.7564469914040115</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2705570291777188</v>
+        <v>0.157593123209169</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2785145888594164</v>
+        <v>0.08595988538681948</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05602240896358546</v>
+        <v>0.05757575757575761</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2743164930647941</v>
+        <v>0.5774268327176915</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4490411663621273</v>
+        <v>0.396775791913545</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2766423405730786</v>
+        <v>0.02579737536876358</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
       <c r="V2" t="n">
-        <v>0.1784841371844085</v>
+        <v>-0.17902015868632</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1784841371844085</v>
+        <v>-0.17902015868632</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4490411663621273</v>
+        <v>0.5774268327176915</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>2.342946520635968</v>
+        <v>0.8354303547849534</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.342946520635968</v>
+        <v>0.8354303547849534</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>CIlrT3pm</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.52083333334</v>
+        <v>45563.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,67 +711,1685 @@
         </is>
       </c>
       <c r="I3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.4505119453924915</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.2627986348122867</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.2866894197952219</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.05699855699855694</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.4454932601191379</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.33730299563461</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2172037442462521</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-0.005018685273353585</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.005018685273353585</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.4454932601191379</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9236437397336097</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.9236437397336097</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>st  pauli</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F4" t="n">
+        <v>591</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5618659104350859</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2405938642119471</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.197540225352967</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.06573896740931096</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5870329970487868</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.3748839913535729</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.03808301159764039</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.02516708661370082</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.02516708661370082</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.5870329970487868</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.230966288873778</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.230966288873778</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>mainz</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>heidenheim</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>59</v>
+      </c>
+      <c r="F5" t="n">
+        <v>591</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5362840799830516</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2469729315711422</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.2167429884458061</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.06553334838250358</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.2108979739376808</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.4352521315001535</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.3538498945621656</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.1882791999290113</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.1882791999290113</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.4352521315001535</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9126926488471626</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.9126926488471626</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>rb leipzig</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>augsburg</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>59</v>
+      </c>
+      <c r="F6" t="n">
+        <v>591</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6750355281856939</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1989578398863098</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1260066319279962</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.05814536340852139</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.3674057324418328</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3244977167184592</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.3080965508397079</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.3076297957438611</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.3076297957438611</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.3674057324418328</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.1253458720906294</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.1253458720906294</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>wolfsburg</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>59</v>
+      </c>
+      <c r="F7" t="n">
+        <v>591</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2938513768389287</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2474537910222558</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.4586948321388156</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.06346277278562251</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.2822317277175186</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.5171743781991709</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.2005938940833105</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.2697205871769152</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.2697205871769152</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.5171743781991709</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.084477752073499</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.084477752073499</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bayern munich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>bayer leverkusen</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>59</v>
+      </c>
+      <c r="F8" t="n">
+        <v>591</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5496329396744335</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2224704755825088</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2278965847430578</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.07023297123727534</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.6246114380529718</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.205268451967144</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.1701201099798841</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.07497849837853832</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.07497849837853832</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.6246114380529718</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.309765597084965</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.309765597084965</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45564.4375</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>holstein kiel</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>eintracht frankfurt</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>59</v>
+      </c>
+      <c r="F9" t="n">
+        <v>591</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2083897158322057</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2232746955345061</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.5683355886332883</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.06637806637806642</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.1132208384480762</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.4725774303371734</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.4142017312147504</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.2493027348026673</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.2493027348026673</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.4725774303371734</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9909611360046104</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.9909611360046104</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45564.52083333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>hoffenheim</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>werder bremen</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>59</v>
+      </c>
+      <c r="F10" t="n">
+        <v>591</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.4374145674672915</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2686975200156219</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2938879125170865</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.06333056478405319</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.4270044711800133</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3756374554965607</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.1973580733234259</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.01041009628727818</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.01041009628727818</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.4270044711800133</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8735686651440194</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.8735686651440194</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UajsPCkT</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45569.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>augsburg</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>b  monchengladbach</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" t="n">
+        <v>591</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.391304347826087</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2608695652173913</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.3478260869565217</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06481481481481488</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.3601135621224944</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3985688718367391</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2413175660407665</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.1376993066193478</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1376993066193478</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.3985688718367391</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8357704720041569</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.8357704720041569</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tbtaPLqC</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bayer leverkusen</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>holstein kiel</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F12" t="n">
+        <v>591</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.8613971040649739</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.09389228434308217</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.04471061159194389</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.06505024027959805</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.6388911558360927</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3486733933012182</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.01243545086268916</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.2225059482288813</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.2225059482288813</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.6388911558360927</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8731300562778921</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.8731300562778921</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>bochum</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>wolfsburg</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F13" t="n">
+        <v>591</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.3127962085308056</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2606635071090047</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.4265402843601895</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06565656565656575</v>
+      </c>
+      <c r="P13" t="n">
         <v>2</v>
       </c>
-      <c r="J3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="Q13" t="n">
+        <v>0.298048522029823</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.1315828244190213</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.5703686535511557</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.1438283691909662</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.1438283691909662</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.5703686535511557</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.196022350160071</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.196022350160071</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>union berlin</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>dortmund</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>59</v>
+      </c>
+      <c r="F14" t="n">
+        <v>591</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
         <v>3.5</v>
       </c>
-      <c r="L3" t="n">
-        <v>0.473491773308958</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.2559414990859232</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.2705667276051189</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.05598455598455576</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="K14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.3134328358208955</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2686567164179104</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.417910447761194</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06349206349206349</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3633996633773815</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.2118340739994814</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.424766262623137</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.006855814861943033</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.006855814861943033</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.424766262623137</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8907045303562947</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.8907045303562947</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>werder bremen</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>59</v>
+      </c>
+      <c r="F15" t="n">
+        <v>591</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.3692307692307692</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2615384615384615</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.3692307692307692</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06209150326797408</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.06429179858218267</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3301243084142019</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.6055838930036154</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.2363531237728462</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.2363531237728462</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.6055838930036154</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.269866193416795</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.269866193416795</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>st  pauli</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>mainz</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>59</v>
+      </c>
+      <c r="F16" t="n">
+        <v>591</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3409090909090908</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2840909090909091</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.3749999999999999</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06666666666666687</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.3710429734968926</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.1781560823309521</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4508009441721554</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.07580094417215544</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.07580094417215544</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4508009441721554</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9452973990528091</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.9452973990528091</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45571.4375</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>heidenheim</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>rb leipzig</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>59</v>
+      </c>
+      <c r="F17" t="n">
+        <v>591</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2229680769384942</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2162738852521191</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.5607580378093866</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06784451552190918</v>
+      </c>
+      <c r="P17" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0.3254690356489645</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.3653762396167273</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.3091547247343083</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="n">
-        <v>0.109434740530804</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="Q17" t="n">
+        <v>0.120976844268987</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.5732200848935138</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3058030708374991</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.3569461996413947</v>
+      </c>
+      <c r="W17" t="n">
         <v>0</v>
       </c>
-      <c r="X3" t="n">
-        <v>0.109434740530804</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.3653762396167273</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.985919650836356</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.985919650836356</v>
+      <c r="X17" t="n">
+        <v>0.3569461996413947</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.5732200848935138</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.202001598132718</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.202001598132718</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45571.52083333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>eintracht frankfurt</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>bayern munich</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>59</v>
+      </c>
+      <c r="F18" t="n">
+        <v>591</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.1879485355919054</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.197840563780953</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.6142109006271417</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06412108703130381</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.03118237737892513</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.2647505846172384</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.7040670380038365</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.08985613737669484</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.08985613737669484</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.7040670380038365</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.47637831816447</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.47637831816447</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45571.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>hoffenheim</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>59</v>
+      </c>
+      <c r="F19" t="n">
+        <v>591</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.7035790761700825</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1627408993576017</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.1336800244723157</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.06864988558352403</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.3936000744620654</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.4316931316048285</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.1747067939331062</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.2689522322472268</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.2689522322472268</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.4316931316048285</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9052296801294325</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.9052296801294325</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,52 +613,50 @@
         <v>1.25</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7564469914040115</v>
+        <v>0.7590361445783133</v>
       </c>
       <c r="M2" t="n">
-        <v>0.157593123209169</v>
+        <v>0.1355421686746988</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08595988538681948</v>
+        <v>0.1054216867469879</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05757575757575761</v>
+        <v>0.053968253968254</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5774268327176915</v>
+        <v>0.5892837836535917</v>
       </c>
       <c r="R2" t="n">
-        <v>0.396775791913545</v>
+        <v>0.3878278581361462</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02579737536876358</v>
+        <v>0.02288835821026206</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.17902015868632</v>
+        <v>-0.1697523609247216</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.17902015868632</v>
+        <v>-0.1697523609247216</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5774268327176915</v>
+        <v>0.5892837836535917</v>
       </c>
       <c r="Z2" t="n">
         <v>1.25</v>
@@ -669,10 +667,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0.8354303547849534</v>
+        <v>0.8797274447922977</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8354303547849534</v>
+        <v>0.8797274447922977</v>
       </c>
     </row>
     <row r="3">
@@ -714,52 +712,50 @@
         <v>2.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4505119453924915</v>
+        <v>0.4509283819628647</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2627986348122867</v>
+        <v>0.2705570291777188</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2866894197952219</v>
+        <v>0.2785145888594164</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05699855699855694</v>
+        <v>0.05602240896358546</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4454932601191379</v>
+        <v>0.4380040079976603</v>
       </c>
       <c r="R3" t="n">
-        <v>0.33730299563461</v>
+        <v>0.3391504721056778</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2172037442462521</v>
+        <v>0.2228455198966618</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.005018685273353585</v>
+        <v>-0.01292437396520435</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.005018685273353585</v>
+        <v>-0.01292437396520435</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4454932601191379</v>
+        <v>0.4380040079976603</v>
       </c>
       <c r="Z3" t="n">
         <v>2.1</v>
@@ -770,10 +766,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0.9236437397336097</v>
+        <v>0.8913616478313051</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.9236437397336097</v>
+        <v>0.8913616478313051</v>
       </c>
     </row>
     <row r="4">
@@ -812,58 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5618659104350859</v>
+        <v>0.5883926183471516</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2405938642119471</v>
+        <v>0.2382990104305964</v>
       </c>
       <c r="N4" t="n">
-        <v>0.197540225352967</v>
+        <v>0.173308371222252</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06573896740931096</v>
+        <v>0.04910213243546568</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5870329970487868</v>
+        <v>0.588075155299527</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3748839913535729</v>
+        <v>0.3742380171735891</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03808301159764039</v>
+        <v>0.03768682752688374</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.02516708661370082</v>
+        <v>-0.0003174630476245888</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02516708661370082</v>
+        <v>-0.0003174630476245888</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5870329970487868</v>
+        <v>0.588075155299527</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -871,10 +865,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>1.230966288873778</v>
+        <v>1.23248592298162</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.230966288873778</v>
+        <v>1.23248592298162</v>
       </c>
     </row>
     <row r="5">
@@ -913,58 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5362840799830516</v>
+        <v>0.5198277142432793</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2469729315711422</v>
+        <v>0.2536759245507204</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2167429884458061</v>
+        <v>0.2264963612060003</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06553334838250358</v>
+        <v>0.05120999219359867</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2108979739376808</v>
+        <v>0.2304664227619649</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4352521315001535</v>
+        <v>0.4347551084120429</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3538498945621656</v>
+        <v>0.3347784688259922</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1882791999290113</v>
+        <v>0.1810791838613225</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1882791999290113</v>
+        <v>0.1810791838613225</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4352521315001535</v>
+        <v>0.4347551084120429</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -972,10 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0.9126926488471626</v>
+        <v>0.9116504269118848</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.9126926488471626</v>
+        <v>0.9116504269118848</v>
       </c>
     </row>
     <row r="6">
@@ -1017,34 +1009,34 @@
         <v>1.4</v>
       </c>
       <c r="J6" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="K6" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6750355281856939</v>
+        <v>0.6747404844290658</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1989578398863098</v>
+        <v>0.1799307958477508</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1260066319279962</v>
+        <v>0.1453287197231834</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05814536340852139</v>
+        <v>0.05860805860805862</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3674057324418328</v>
+        <v>0.3776218287814722</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3244977167184592</v>
+        <v>0.3228405945965028</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3080965508397079</v>
+        <v>0.2995375766220251</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1053,16 +1045,16 @@
         <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3076297957438611</v>
+        <v>-0.2971186556475936</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3076297957438611</v>
+        <v>-0.2971186556475936</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3674057324418328</v>
+        <v>0.3776218287814722</v>
       </c>
       <c r="Z6" t="n">
         <v>1.4</v>
@@ -1073,10 +1065,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0.1253458720906294</v>
+        <v>0.168809407262226</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1253458720906294</v>
+        <v>0.168809407262226</v>
       </c>
     </row>
     <row r="7">
@@ -1118,34 +1110,34 @@
         <v>3.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K7" t="n">
         <v>2.05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2938513768389287</v>
+        <v>0.2957277603107084</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2474537910222558</v>
+        <v>0.2426484187164787</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4586948321388156</v>
+        <v>0.4616238209728131</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06346277278562251</v>
+        <v>0.05671513445903686</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2822317277175186</v>
+        <v>0.3348519046927033</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5171743781991709</v>
+        <v>0.4780350397247529</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2005938940833105</v>
+        <v>0.1871130555825437</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1154,19 +1146,19 @@
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2697205871769152</v>
+        <v>0.2353866210082742</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2697205871769152</v>
+        <v>0.2353866210082742</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5171743781991709</v>
+        <v>0.4780350397247529</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1174,10 +1166,10 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>1.084477752073499</v>
+        <v>1.002405353293461</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.084477752073499</v>
+        <v>1.002405353293461</v>
       </c>
     </row>
     <row r="8">
@@ -1216,37 +1208,37 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="J8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K8" t="n">
         <v>4.2</v>
       </c>
-      <c r="K8" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.5496329396744335</v>
+        <v>0.5520461161585652</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2224704755825088</v>
+        <v>0.2205634598046923</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2278965847430578</v>
+        <v>0.2273904240367423</v>
       </c>
       <c r="O8" t="n">
-        <v>0.07023297123727534</v>
+        <v>0.04707680239325307</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6246114380529718</v>
+        <v>0.632805475920491</v>
       </c>
       <c r="R8" t="n">
-        <v>0.205268451967144</v>
+        <v>0.2032764625324963</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1701201099798841</v>
+        <v>0.1639180615470127</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1255,19 +1247,19 @@
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>0.07497849837853832</v>
+        <v>0.08075935976192572</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.07497849837853832</v>
+        <v>0.08075935976192572</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6246114380529718</v>
+        <v>0.632805475920491</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1275,10 +1267,10 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>1.309765597084965</v>
+        <v>1.326947909553565</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.309765597084965</v>
+        <v>1.326947909553565</v>
       </c>
     </row>
     <row r="9">
@@ -1317,55 +1309,53 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J9" t="n">
         <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2083897158322057</v>
+        <v>0.2258485639686684</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2232746955345061</v>
+        <v>0.2258485639686684</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5683355886332883</v>
+        <v>0.5483028720626633</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06637806637806642</v>
+        <v>0.05422515827140106</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1132208384480762</v>
+        <v>0.1055901570843876</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4725774303371734</v>
+        <v>0.4701445522532986</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4142017312147504</v>
+        <v>0.4242652906623138</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2493027348026673</v>
+        <v>0.2442959882846302</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2493027348026673</v>
+        <v>0.2442959882846302</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4725774303371734</v>
+        <v>0.4701445522532986</v>
       </c>
       <c r="Z9" t="n">
         <v>4.2</v>
@@ -1376,10 +1366,10 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>0.9909611360046104</v>
+        <v>0.98585956433616</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.9909611360046104</v>
+        <v>0.98585956433616</v>
       </c>
     </row>
     <row r="10">
@@ -1418,58 +1408,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4374145674672915</v>
+        <v>0.3987563155849203</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2686975200156219</v>
+        <v>0.2497473766031869</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2938879125170865</v>
+        <v>0.3514963078118927</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06333056478405319</v>
+        <v>0.05369633233410331</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4270044711800133</v>
+        <v>0.4374378707181061</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3756374554965607</v>
+        <v>0.3726193202087587</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1973580733234259</v>
+        <v>0.1899428090731352</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.01041009628727818</v>
+        <v>0.03868155513318577</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.01041009628727818</v>
+        <v>0.03868155513318577</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4270044711800133</v>
+        <v>0.4374378707181061</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1477,919 +1465,10 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>0.8735686651440194</v>
+        <v>0.9172759879560293</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.8735686651440194</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>UajsPCkT</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45569.64583333334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>augsburg</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>b  monchengladbach</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>59</v>
-      </c>
-      <c r="F11" t="n">
-        <v>591</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.391304347826087</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.2608695652173913</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.3478260869565217</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.06481481481481488</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.3601135621224944</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.3985688718367391</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.2413175660407665</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.1376993066193478</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.1376993066193478</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.3985688718367391</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.8357704720041569</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.8357704720041569</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>tbtaPLqC</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>bayer leverkusen</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>holstein kiel</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>59</v>
-      </c>
-      <c r="F12" t="n">
-        <v>591</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="J12" t="n">
-        <v>10</v>
-      </c>
-      <c r="K12" t="n">
-        <v>21</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.8613971040649739</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.09389228434308217</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.04471061159194389</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.06505024027959805</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.6388911558360927</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.3486733933012182</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.01243545086268916</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>-0.2225059482288813</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-0.2225059482288813</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.6388911558360927</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>0.8731300562778921</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0.8731300562778921</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ENOasf5c</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>bochum</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>wolfsburg</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>59</v>
-      </c>
-      <c r="F13" t="n">
-        <v>591</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.3127962085308056</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.2606635071090047</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.4265402843601895</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.06565656565656575</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.298048522029823</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.1315828244190213</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.5703686535511557</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.1438283691909662</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.1438283691909662</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.5703686535511557</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
-        </is>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.196022350160071</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.196022350160071</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lpXDJjDj</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>union berlin</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>dortmund</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>59</v>
-      </c>
-      <c r="F14" t="n">
-        <v>591</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.3134328358208955</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.2686567164179104</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.417910447761194</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.06349206349206349</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.3633996633773815</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.2118340739994814</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.424766262623137</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.006855814861943033</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.006855814861943033</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.424766262623137</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>0.8907045303562947</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0.8907045303562947</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dnhZQYKG</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>werder bremen</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>freiburg</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>59</v>
-      </c>
-      <c r="F15" t="n">
-        <v>591</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.3692307692307692</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2615384615384615</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.3692307692307692</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.06209150326797408</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.06429179858218267</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.3301243084142019</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.6055838930036154</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.2363531237728462</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.2363531237728462</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.6055838930036154</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.269866193416795</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.269866193416795</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zwD8uYZ9</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45570.5625</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>st  pauli</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>mainz</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>59</v>
-      </c>
-      <c r="F16" t="n">
-        <v>591</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.3409090909090908</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.2840909090909091</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.3749999999999999</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.06666666666666687</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.3710429734968926</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.1781560823309521</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.4508009441721554</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.07580094417215544</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.07580094417215544</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.4508009441721554</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
-        </is>
-      </c>
-      <c r="AB16" t="n">
-        <v>0.9452973990528091</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0.9452973990528091</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>0KbQSfj4</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45571.4375</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>heidenheim</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>rb leipzig</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>59</v>
-      </c>
-      <c r="F17" t="n">
-        <v>591</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.2229680769384942</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.2162738852521191</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.5607580378093866</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.06784451552190918</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.120976844268987</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.5732200848935138</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.3058030708374991</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.3569461996413947</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.3569461996413947</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.5732200848935138</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
-        </is>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.202001598132718</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.202001598132718</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>ShoJUGLi</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45571.52083333334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>eintracht frankfurt</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>bayern munich</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>59</v>
-      </c>
-      <c r="F18" t="n">
-        <v>591</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.1879485355919054</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.197840563780953</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.6142109006271417</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.06412108703130381</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.03118237737892513</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.2647505846172384</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.7040670380038365</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.08985613737669484</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.08985613737669484</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.7040670380038365</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
-        </is>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.47637831816447</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.47637831816447</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>nc8W6DTp</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45571.60416666666</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>stuttgart</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>hoffenheim</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>59</v>
-      </c>
-      <c r="F19" t="n">
-        <v>591</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="J19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K19" t="n">
-        <v>7</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.7035790761700825</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.1627408993576017</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.1336800244723157</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.06864988558352403</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.3936000744620654</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.4316931316048285</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.1747067939331062</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.2689522322472268</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0.2689522322472268</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.4316931316048285</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
-        </is>
-      </c>
-      <c r="AB19" t="n">
-        <v>0.9052296801294325</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0.9052296801294325</v>
+        <v>0.9172759879560293</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,12 +510,12 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>prob_class_0</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>prob_class_1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>prob_class_0</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pWnjRsFa</t>
+          <t>UajsPCkT</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.4375</v>
+        <v>45569.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>holstein kiel</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,86 +610,86 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.33</v>
+        <v>2.35</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2205634598046923</v>
+        <v>0.4041349717183538</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2273904240367423</v>
+        <v>0.2566803198751706</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5520461161585652</v>
+        <v>0.3391847084064756</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04707680239325307</v>
+        <v>0.05294504230674435</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1161647488819046</v>
+        <v>0.3847192411139503</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4734474829440071</v>
+        <v>0.2597202205625364</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4103877681740883</v>
+        <v>0.3555605383235134</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2460570589072648</v>
+        <v>0.1280389212387796</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2460570589072648</v>
+        <v>0.1280389212387796</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4734474829440071</v>
+        <v>0.3847192411139503</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0.9871087357820967</v>
+        <v>2.554001209384591</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.9871087357820967</v>
+        <v>2.554001209384591</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bFO8E4Vg</t>
+          <t>tbtaPLqC</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.52083333334</v>
+        <v>45570.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>holstein kiel</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,67 +709,1366 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.4</v>
+        <v>1.09</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7</v>
+        <v>21</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3967517401392111</v>
+        <v>0.868812998345118</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2505800464037123</v>
+        <v>0.08609146983601625</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3526682134570765</v>
+        <v>0.04509553181886565</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05019493177387924</v>
+        <v>0.05595933118868901</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4343303897590789</v>
+        <v>0.3302809723445485</v>
       </c>
       <c r="R3" t="n">
-        <v>0.373530595637641</v>
+        <v>0.6239079533864633</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1921390146032801</v>
+        <v>0.04581107426898828</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.03757864961986779</v>
+        <v>-0.2449050449586547</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.03757864961986779</v>
+        <v>-0.2449050449586547</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4343303897590789</v>
+        <v>0.6239079533864633</v>
       </c>
       <c r="Z3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.516052702958508</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.516052702958508</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bochum</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>wolfsburg</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F4" t="n">
+        <v>591</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.315015479876161</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2554179566563468</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4295665634674923</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.05814905814905802</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.3603683922789779</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.2630596340438405</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.3765719736771816</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>-0.05299458979031069</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.05299458979031069</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.3765719736771816</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.148104231500585</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.148104231500585</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>union berlin</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>dortmund</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>59</v>
+      </c>
+      <c r="F5" t="n">
+        <v>591</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.2875429881543752</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2711119602598395</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.4413450515857852</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.05386086781435617</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.3137532115234424</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.2621291023508467</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.4241176861257108</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>-0.01722736546007442</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.01722736546007442</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.4241176861257108</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.701186371801764</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.701186371801764</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>werder bremen</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>59</v>
+      </c>
+      <c r="F6" t="n">
+        <v>591</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.3645833333333334</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2708333333333334</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.3645833333333334</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.05494505494505475</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.3668185239221092</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3702700078158437</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.262911468262047</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.005686674482510368</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.005686674482510368</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.3702700078158437</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.458078376902413</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.458078376902413</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>st  pauli</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>mainz</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>59</v>
+      </c>
+      <c r="F7" t="n">
+        <v>591</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>2.4</v>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.9055520145146365</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.9055520145146365</v>
+      <c r="J7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3914110429447853</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2846625766871166</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.3239263803680982</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0645245559038663</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.4511806019112184</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.152249633447322</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.3965697646414596</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.1665180252241019</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.1665180252241019</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.4511806019112184</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.99521229974254</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.99521229974254</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45571.4375</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>heidenheim</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>rb leipzig</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>59</v>
+      </c>
+      <c r="F8" t="n">
+        <v>591</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2199223803363519</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2199223803363519</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5601552393272963</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.05012905855182725</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.3974842518274433</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.1339439024769403</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.4685718456956164</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>-0.09158339363167989</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.09158339363167989</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.4685718456956164</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.502679511706922</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.502679511706922</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.52083333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>eintracht frankfurt</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>bayern munich</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>59</v>
+      </c>
+      <c r="F9" t="n">
+        <v>591</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1719101123595506</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2101123595505618</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.6179775280898876</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.05763517528223416</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.3580811440158347</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.2782981347277904</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.3636207212563748</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>-0.2543568068335128</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.2543568068335128</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.3636207212563748</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.7253605740385335</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.7253605740385335</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.60416666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>hoffenheim</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>59</v>
+      </c>
+      <c r="F10" t="n">
+        <v>591</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7250755287009064</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1570996978851964</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.1178247734138973</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.06089743589743568</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.3680524492004706</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.354855940898232</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2770916099012975</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.2109527513152742</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.2109527513152742</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.3680524492004706</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.443356868903111</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.443356868903111</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45583.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>dortmund</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>st  pauli</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" t="n">
+        <v>591</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.718358038768529</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.17787913340935</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1037628278221209</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.07081807081807079</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.3495555644850348</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.6104046287537624</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.04003980676120279</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.1079534100147665</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.1079534100147665</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.6104046287537624</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.335577957058995</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.335577957058995</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fHjVr7t2</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>b  monchengladbach</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>heidenheim</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F12" t="n">
+        <v>591</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5143906919779547</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2614819350887937</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.2241273729332517</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.06232110330470975</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.2816042413040077</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.4135614921904666</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.3048342665055257</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.1008291997874881</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.1008291997874881</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4135614921904666</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.076107892857507</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.076107892857507</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>r3GGwC4M</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>bayer leverkusen</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>eintracht frankfurt</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F13" t="n">
+        <v>591</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6585824796153043</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2078193602341626</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1335981601505331</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06930471719204112</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4000447103063517</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.4825943259909106</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1173609637027377</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.1759881536243937</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.1759881536243937</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4825943259909106</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.035438967808022</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.035438967808022</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>augsburg</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>59</v>
+      </c>
+      <c r="F14" t="n">
+        <v>591</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5220012055455093</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2610006027727547</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.216998191681736</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0642802155504234</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3991107265074292</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.4157547728654518</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.185134500627119</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.1062464326800576</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.1062464326800576</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.4157547728654518</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.054705329682172</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.054705329682172</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Eq0zfXl3</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>hoffenheim</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>bochum</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>59</v>
+      </c>
+      <c r="F15" t="n">
+        <v>591</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5652658981033842</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2359985124581629</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1987355894384529</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.05932871099905457</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3623804293386554</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.4624846491888538</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.1751349214724907</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.1027812489145304</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.1027812489145304</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4624846491888538</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.387930784694666</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.387930784694666</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>E7rNpTBk</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>mainz</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>rb leipzig</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>59</v>
+      </c>
+      <c r="F16" t="n">
+        <v>591</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.2283456379328273</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2600603098679423</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.5115940521992306</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06812830423386185</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.3860774980492348</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.1620703781245434</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4518521238262218</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.05974192837300885</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.05974192837300885</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4518521238262218</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.60306687676927</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.60306687676927</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UajsPCkT</t>
+          <t>0KbQSfj4</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45569.64583333334</v>
+        <v>45571.4375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>b  monchengladbach</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.35</v>
+        <v>4.33</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4041349717183538</v>
+        <v>0.2199223803363519</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2566803198751706</v>
+        <v>0.2199223803363519</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3391847084064756</v>
+        <v>0.5601552393272963</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05294504230674435</v>
+        <v>0.05012905855182725</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3847192411139503</v>
+        <v>0.3982479451849764</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2597202205625364</v>
+        <v>0.1395610075338734</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3555605383235134</v>
+        <v>0.4621910472811503</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1280389212387796</v>
+        <v>-0.09796419204614598</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1280389212387796</v>
+        <v>-0.09796419204614598</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3847192411139503</v>
+        <v>0.4621910472811503</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>2.554001209384591</v>
+        <v>0.3642268552350043</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.554001209384591</v>
+        <v>0.3642268552350043</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tbtaPLqC</t>
+          <t>ShoJUGLi</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45570.4375</v>
+        <v>45571.52083333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bayer leverkusen</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>holstein kiel</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.09</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="K3" t="n">
-        <v>21</v>
+        <v>1.53</v>
       </c>
       <c r="L3" t="n">
-        <v>0.868812998345118</v>
+        <v>0.1719101123595506</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08609146983601625</v>
+        <v>0.2101123595505618</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04509553181886565</v>
+        <v>0.6179775280898876</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05595933118868901</v>
+        <v>0.05763517528223416</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3302809723445485</v>
+        <v>0.3580811440158347</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6239079533864633</v>
+        <v>0.2782981347277904</v>
       </c>
       <c r="S3" t="n">
-        <v>0.04581107426898828</v>
+        <v>0.3636207212563748</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.2449050449586547</v>
+        <v>-0.2543568068335128</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2449050449586547</v>
+        <v>-0.2543568068335128</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6239079533864633</v>
+        <v>0.3636207212563748</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.09</v>
+        <v>1.53</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2.516052702958508</v>
+        <v>0.109263914422862</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.516052702958508</v>
+        <v>0.109263914422862</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ENOasf5c</t>
+          <t>nc8W6DTp</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.4375</v>
+        <v>45571.60416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bochum</t>
+          <t>stuttgart</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>wolfsburg</t>
+          <t>hoffenheim</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>6.25</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2</v>
+        <v>8.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.315015479876161</v>
+        <v>0.7347856154910097</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2554179566563468</v>
+        <v>0.15283540802213</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4295665634674923</v>
+        <v>0.1123789764868603</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05814905814905802</v>
+        <v>0.04687782805429852</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3603683922789779</v>
+        <v>0.3681677580459124</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2630596340438405</v>
+        <v>0.3553656713533631</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3765719736771816</v>
+        <v>0.2764665706007245</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.05299458979031069</v>
+        <v>0.2153323500237824</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.05299458979031069</v>
+        <v>0.2153323500237824</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3765719736771816</v>
+        <v>0.3681677580459124</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.2</v>
+        <v>6.25</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>2.148104231500585</v>
+        <v>0.3681677580459124</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.148104231500585</v>
+        <v>0.3681677580459124</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lpXDJjDj</t>
+          <t>z1eeWTdd</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.4375</v>
+        <v>45583.64583333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>st  pauli</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,58 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3.3</v>
+        <v>1.33</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="K5" t="n">
-        <v>2.15</v>
+        <v>8.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2875429881543752</v>
+        <v>0.7093184979137691</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2711119602598395</v>
+        <v>0.1796940194714882</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4413450515857852</v>
+        <v>0.1109874826147427</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05386086781435617</v>
+        <v>0.06000294854784016</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3137532115234424</v>
+        <v>0.3174980032675303</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2621291023508467</v>
+        <v>0.6384495816509406</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4241176861257108</v>
+        <v>0.0440524150815292</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
       <c r="V5" t="n">
-        <v>-0.01722736546007442</v>
+        <v>-0.07086891626282854</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.01722736546007442</v>
+        <v>-0.07086891626282854</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4241176861257108</v>
+        <v>0.6384495816509406</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.15</v>
+        <v>1.33</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +966,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2.701186371801764</v>
+        <v>0.567580665388112</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.701186371801764</v>
+        <v>0.567580665388112</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dnhZQYKG</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45570.4375</v>
+        <v>45584.4375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1008,58 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3645833333333334</v>
+        <v>0.5220012055455093</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2708333333333334</v>
+        <v>0.2610006027727547</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3645833333333334</v>
+        <v>0.216998191681736</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05494505494505475</v>
+        <v>0.0642802155504234</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3668185239221092</v>
+        <v>0.2558319805251948</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3702700078158437</v>
+        <v>0.4172778385915271</v>
       </c>
       <c r="S6" t="n">
-        <v>0.262911468262047</v>
+        <v>0.3268901808832782</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
       <c r="V6" t="n">
-        <v>0.005686674482510368</v>
+        <v>-0.1047233669539823</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.005686674482510368</v>
+        <v>-0.1047233669539823</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3702700078158437</v>
+        <v>0.4172778385915271</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1067,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>2.458078376902413</v>
+        <v>0.3125544716375448</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.458078376902413</v>
+        <v>0.3125544716375448</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>zwD8uYZ9</t>
+          <t>r3GGwC4M</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45570.5625</v>
+        <v>45584.4375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>st  pauli</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1109,58 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.4</v>
+        <v>1.42</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>7</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3914110429447853</v>
+        <v>0.6585824796153043</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2846625766871166</v>
+        <v>0.2078193602341626</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3239263803680982</v>
+        <v>0.1335981601505331</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0645245559038663</v>
+        <v>0.06930471719204112</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4511806019112184</v>
+        <v>0.3843591962445855</v>
       </c>
       <c r="R7" t="n">
-        <v>0.152249633447322</v>
+        <v>0.4926733222577763</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3965697646414596</v>
+        <v>0.1229674814976382</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
       <c r="V7" t="n">
-        <v>0.1665180252241019</v>
+        <v>-0.165909157357528</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1665180252241019</v>
+        <v>-0.165909157357528</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4511806019112184</v>
+        <v>0.4926733222577763</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.3</v>
+        <v>1.42</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1168,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>2.99521229974254</v>
+        <v>0.3267641649002483</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.99521229974254</v>
+        <v>0.3267641649002483</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>M93rhBJF</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.4375</v>
+        <v>45584.4375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1210,58 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.33</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2199223803363519</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2199223803363519</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5601552393272963</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05012905855182725</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3974842518274433</v>
+        <v>0.3261957094859789</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1339439024769403</v>
+        <v>0.4300777016963417</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4685718456956164</v>
+        <v>0.2437265888176793</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
       <c r="V8" t="n">
-        <v>-0.09158339363167989</v>
+        <v>-0.09623808777734244</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.09158339363167989</v>
+        <v>-0.09623808777734244</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4685718456956164</v>
+        <v>0.4300777016963417</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1269,29 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>2.502679511706922</v>
+        <v>0.3338396139189993</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.502679511706922</v>
+        <v>0.3338396139189993</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>Eq0zfXl3</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.52083333334</v>
+        <v>45584.4375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>hoffenheim</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1311,58 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.5</v>
+        <v>1.67</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>1.53</v>
+        <v>4.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1719101123595506</v>
+        <v>0.5652658981033842</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2101123595505618</v>
+        <v>0.2359985124581629</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6179775280898876</v>
+        <v>0.1987355894384529</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05763517528223416</v>
+        <v>0.05932871099905457</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3580811440158347</v>
+        <v>0.3644492937320996</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2782981347277904</v>
+        <v>0.4636484229593923</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3636207212563748</v>
+        <v>0.1719022833085081</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
       <c r="V9" t="n">
-        <v>-0.2543568068335128</v>
+        <v>-0.1016174751439919</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2543568068335128</v>
+        <v>-0.1016174751439919</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3636207212563748</v>
+        <v>0.4636484229593923</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1370,29 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>0.7253605740385335</v>
+        <v>0.3620309478154005</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.7253605740385335</v>
+        <v>0.3620309478154005</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>E7rNpTBk</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.60416666666</v>
+        <v>45584.4375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>stuttgart</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1412,58 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>1.83</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7250755287009064</v>
+        <v>0.2283456379328273</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1570996978851964</v>
+        <v>0.2600603098679423</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1178247734138973</v>
+        <v>0.5115940521992306</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06089743589743568</v>
+        <v>0.06812830423386185</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3680524492004706</v>
+        <v>0.3961456009831124</v>
       </c>
       <c r="R10" t="n">
-        <v>0.354855940898232</v>
+        <v>0.1727582813184825</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2770916099012975</v>
+        <v>0.4310961176984052</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
       <c r="V10" t="n">
-        <v>0.2109527513152742</v>
+        <v>-0.08049793450082543</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2109527513152742</v>
+        <v>-0.08049793450082543</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3680524492004706</v>
+        <v>0.4310961176984052</v>
       </c>
       <c r="Z10" t="n">
-        <v>6</v>
+        <v>1.83</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,29 +1471,29 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>2.443356868903111</v>
+        <v>0.3505981831975797</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.443356868903111</v>
+        <v>0.3505981831975797</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45583.64583333334</v>
+        <v>45584.5625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>st  pauli</t>
+          <t>stuttgart</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1501,37 +1513,37 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="J11" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
-        <v>0.718358038768529</v>
+        <v>0.6934812760055478</v>
       </c>
       <c r="M11" t="n">
-        <v>0.17787913340935</v>
+        <v>0.188626907073509</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1037628278221209</v>
+        <v>0.1178918169209431</v>
       </c>
       <c r="O11" t="n">
-        <v>0.07081807081807079</v>
+        <v>0.06029411764705883</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3495555644850348</v>
+        <v>0.3475105219699873</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6104046287537624</v>
+        <v>0.5386629937908096</v>
       </c>
       <c r="S11" t="n">
-        <v>0.04003980676120279</v>
+        <v>0.113826484239203</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
@@ -1540,19 +1552,19 @@
         <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1079534100147665</v>
+        <v>-0.1548182822147381</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1079534100147665</v>
+        <v>-0.1548182822147381</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.6104046287537624</v>
+        <v>0.5386629937908096</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1560,29 +1572,29 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>3.335577957058995</v>
+        <v>0.3838447115760715</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.335577957058995</v>
+        <v>0.3838447115760715</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45585.4375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>b  monchengladbach</t>
+          <t>holstein kiel</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1602,37 +1614,37 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.83</v>
+        <v>3.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5143906919779547</v>
+        <v>0.2697368421052632</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2614819350887937</v>
+        <v>0.2697368421052632</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2241273729332517</v>
+        <v>0.4605263157894737</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06232110330470975</v>
+        <v>0.05923344947735187</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2816042413040077</v>
+        <v>0.3677293184163819</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4135614921904666</v>
+        <v>0.2497558300231082</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3048342665055257</v>
+        <v>0.3825148515605099</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1641,19 +1653,19 @@
         <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1008291997874881</v>
+        <v>-0.07801146422896382</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1008291997874881</v>
+        <v>-0.07801146422896382</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4135614921904666</v>
+        <v>0.3825148515605099</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1661,29 +1673,29 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>2.076107892857507</v>
+        <v>0.3045033873315461</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.076107892857507</v>
+        <v>0.3045033873315461</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45585.52083333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bayer leverkusen</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>werder bremen</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1703,37 +1715,37 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6585824796153043</v>
+        <v>0.4436536180308422</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2078193602341626</v>
+        <v>0.2823250296559905</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1335981601505331</v>
+        <v>0.2740213523131673</v>
       </c>
       <c r="O13" t="n">
-        <v>0.06930471719204112</v>
+        <v>0.07333842627960285</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4000447103063517</v>
+        <v>0.3690503156071357</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4825943259909106</v>
+        <v>0.3731370625607071</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1173609637027377</v>
+        <v>0.2578126218321573</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
@@ -1742,19 +1754,19 @@
         <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1759881536243937</v>
+        <v>-0.07051655547013513</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1759881536243937</v>
+        <v>-0.07051655547013513</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4825943259909106</v>
+        <v>0.3731370625607071</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1762,313 +1774,10 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>2.035438967808022</v>
+        <v>0.3026205070905719</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.035438967808022</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>M93rhBJF</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45584.4375</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>freiburg</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>augsburg</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>59</v>
-      </c>
-      <c r="F14" t="n">
-        <v>591</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.5220012055455093</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.2610006027727547</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.216998191681736</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.0642802155504234</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.3991107265074292</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.4157547728654518</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.185134500627119</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>-0.1062464326800576</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-0.1062464326800576</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.4157547728654518</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.054705329682172</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.054705329682172</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Eq0zfXl3</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45584.4375</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>hoffenheim</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>bochum</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>59</v>
-      </c>
-      <c r="F15" t="n">
-        <v>591</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.5652658981033842</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2359985124581629</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.1987355894384529</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.05932871099905457</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.3623804293386554</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.4624846491888538</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.1751349214724907</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-0.1027812489145304</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.1027812489145304</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.4624846491888538</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.387930784694666</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.387930784694666</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>E7rNpTBk</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45584.4375</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>mainz</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>rb leipzig</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>59</v>
-      </c>
-      <c r="F16" t="n">
-        <v>591</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.2283456379328273</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.2600603098679423</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.5115940521992306</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.06812830423386185</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.3860774980492348</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.1620703781245434</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.4518521238262218</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-0.05974192837300885</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-0.05974192837300885</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.4518521238262218</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.60306687676927</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.60306687676927</v>
+        <v>0.3026205070905719</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,14 +510,14 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>prob_class_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>prob_class_0</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>prob_class_1</t>
-        </is>
-      </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>prob_class_2</t>
@@ -565,10 +565,15 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>multiplier</t>
+          <t>stake_to_bet_raw</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>stake_to_bet_norm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -577,20 +582,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>z1eeWTdd</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45571.4375</v>
+        <v>45583.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>st  pauli</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +615,58 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.33</v>
+        <v>1.29</v>
       </c>
       <c r="J2" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7</v>
+        <v>9.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2199223803363519</v>
+        <v>0.7238489169478611</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2199223803363519</v>
+        <v>0.177860019592903</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5601552393272963</v>
+        <v>0.09829106345923588</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05012905855182725</v>
+        <v>0.07093314682053964</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3982479451849764</v>
+        <v>0.533005595670592</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1395610075338734</v>
+        <v>0.3102523233424003</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4621910472811503</v>
+        <v>0.1567420809870077</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
       <c r="V2" t="n">
-        <v>-0.09796419204614598</v>
+        <v>-0.1908433212772691</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.09796419204614598</v>
+        <v>-0.1908433212772691</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4621910472811503</v>
+        <v>0.533005595670592</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +674,32 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0.3642268552350043</v>
+        <v>-107.731993649978</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3642268552350043</v>
+        <v>-2.15463987299956</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.1882573947523236</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45571.52083333334</v>
+        <v>45584.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +719,58 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>5.5</v>
+        <v>1.83</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>1.53</v>
+        <v>4.33</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1719101123595506</v>
+        <v>0.5140093406910212</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2101123595505618</v>
+        <v>0.2687534552755911</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6179775280898876</v>
+        <v>0.2172372040333877</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05763517528223416</v>
+        <v>0.06310925536306966</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3580811440158347</v>
+        <v>0.3594975492852748</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2782981347277904</v>
+        <v>0.3482094466124229</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3636207212563748</v>
+        <v>0.2922930041023024</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
       <c r="V3" t="n">
-        <v>-0.2543568068335128</v>
+        <v>-0.1545117914057464</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2543568068335128</v>
+        <v>-0.1545117914057464</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3636207212563748</v>
+        <v>0.3594975492852748</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +778,32 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0.109263914422862</v>
+        <v>-41.21921503710206</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.109263914422862</v>
+        <v>-0.8243843007420412</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.5523395234174531</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>r3GGwC4M</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45571.60416666666</v>
+        <v>45584.4375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>stuttgart</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +823,58 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J4" t="n">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="K4" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7347856154910097</v>
+        <v>0.6690140845070423</v>
       </c>
       <c r="M4" t="n">
-        <v>0.15283540802213</v>
+        <v>0.1971830985915493</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1123789764868603</v>
+        <v>0.1338028169014084</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04687782805429852</v>
+        <v>0.06766917293233088</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3681677580459124</v>
+        <v>0.489689331131483</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3553656713533631</v>
+        <v>0.3271781694361988</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2764665706007245</v>
+        <v>0.1831324994323181</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
       <c r="V4" t="n">
-        <v>0.2153323500237824</v>
+        <v>-0.1793247533755593</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2153323500237824</v>
+        <v>-0.1793247533755593</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3681677580459124</v>
+        <v>0.489689331131483</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.25</v>
+        <v>1.4</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +882,32 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0.3681677580459124</v>
+        <v>-78.60873410398099</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.3681677580459124</v>
+        <v>-1.57217468207962</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.3114838652546875</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>M93rhBJF</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45583.64583333334</v>
+        <v>45584.4375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>st  pauli</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,37 +927,37 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
-        <v>5.25</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7093184979137691</v>
+        <v>0.5557224391709222</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1796940194714882</v>
+        <v>0.2553319315109642</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1109874826147427</v>
+        <v>0.1889456293181136</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06000294854784016</v>
+        <v>0.05850556438791732</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3174980032675303</v>
+        <v>0.3864998697000389</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6384495816509406</v>
+        <v>0.335577206624032</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0440524150815292</v>
+        <v>0.2779229236759292</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -946,19 +966,19 @@
         <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.07086891626282854</v>
+        <v>-0.1692225694708834</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.07086891626282854</v>
+        <v>-0.1692225694708834</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6384495816509406</v>
+        <v>0.3864998697000389</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -966,16 +986,19 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0.567580665388112</v>
+        <v>-48.99288878713343</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.567580665388112</v>
+        <v>-0.9798577757426686</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.4945137693516743</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>Eq0zfXl3</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -983,12 +1006,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>b  monchengladbach</t>
+          <t>hoffenheim</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1008,37 +1031,37 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5220012055455093</v>
+        <v>0.5682242990654205</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2610006027727547</v>
+        <v>0.234392523364486</v>
       </c>
       <c r="N6" t="n">
-        <v>0.216998191681736</v>
+        <v>0.1973831775700934</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0642802155504234</v>
+        <v>0.06658692185007986</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2558319805251948</v>
+        <v>0.3824937066336742</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4172778385915271</v>
+        <v>0.344658366537651</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3268901808832782</v>
+        <v>0.2728479268286748</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1047,19 +1070,19 @@
         <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1047233669539823</v>
+        <v>-0.1857305924317463</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1047233669539823</v>
+        <v>-0.1857305924317463</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4172778385915271</v>
+        <v>0.3824937066336742</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1067,16 +1090,19 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0.3125544716375448</v>
+        <v>-56.75159754683656</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.3125544716375448</v>
+        <v>-1.135031950936731</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.4407240064816078</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>E7rNpTBk</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1084,12 +1110,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bayer leverkusen</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1109,37 +1135,37 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.42</v>
+        <v>4.2</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6585824796153043</v>
+        <v>0.2237903225806452</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2078193602341626</v>
+        <v>0.2540322580645161</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1335981601505331</v>
+        <v>0.5221774193548387</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06930471719204112</v>
+        <v>0.06392106392106389</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3843591962445855</v>
+        <v>0.1964973149715032</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4926733222577763</v>
+        <v>0.3791722029115259</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1229674814976382</v>
+        <v>0.4243304821169709</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1148,19 +1174,19 @@
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.165909157357528</v>
+        <v>-0.0978469372378678</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.165909157357528</v>
+        <v>-0.0978469372378678</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4926733222577763</v>
+        <v>0.4243304821169709</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1168,29 +1194,32 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>0.3267641649002483</v>
+        <v>-29.52564152368154</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.3267641649002483</v>
+        <v>-0.5905128304736308</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.6459865863227952</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M93rhBJF</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45584.5625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>stuttgart</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1210,37 +1239,37 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.6934812760055478</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.188626907073509</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.1178918169209431</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.06029411764705883</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3261957094859789</v>
+        <v>0.4901233034693709</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4300777016963417</v>
+        <v>0.3136940934930733</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2437265888176793</v>
+        <v>0.1961826030375558</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1249,19 +1278,19 @@
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.09623808777734244</v>
+        <v>-0.2033579725361769</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.09623808777734244</v>
+        <v>-0.2033579725361769</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4300777016963417</v>
+        <v>0.4901233034693709</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1269,29 +1298,32 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>0.3338396139189993</v>
+        <v>-92.62008535601542</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.3338396139189993</v>
+        <v>-1.852401707120308</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.2456825891514715</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Eq0zfXl3</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45585.4375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>holstein kiel</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>bochum</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1311,37 +1343,37 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.67</v>
+        <v>3.6</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.75</v>
+        <v>2.05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5652658981033842</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2359985124581629</v>
+        <v>0.2775479503572772</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1987355894384529</v>
+        <v>0.46032342986085</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05932871099905457</v>
+        <v>0.05970030288538175</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3644492937320996</v>
+        <v>0.2176548029257694</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4636484229593923</v>
+        <v>0.3766298803319589</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1719022833085081</v>
+        <v>0.4057153167422716</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
@@ -1350,19 +1382,19 @@
         <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1016174751439919</v>
+        <v>-0.05460811311857838</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1016174751439919</v>
+        <v>-0.05460811311857838</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4636484229593923</v>
+        <v>0.4057153167422716</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1370,29 +1402,32 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>0.3620309478154005</v>
+        <v>-16.02700958841365</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.3620309478154005</v>
+        <v>-0.320540191768273</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.7619992912455799</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>E7rNpTBk</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45585.52083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>werder bremen</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1412,88 +1447,91 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>1.83</v>
+        <v>3.7</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2283456379328273</v>
+        <v>0.4697535474234503</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2600603098679423</v>
+        <v>0.2763256161314414</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5115940521992306</v>
+        <v>0.2539208364451083</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06812830423386185</v>
+        <v>0.06438791732909377</v>
       </c>
       <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.3584965701867451</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3335320970234635</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.3079713327897913</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.1112569772367052</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.1112569772367052</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.3584965701867451</v>
+      </c>
+      <c r="Z10" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0.3961456009831124</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.1727582813184825</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.4310961176984052</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.08049793450082543</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.08049793450082543</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.4310961176984052</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>0.3505981831975797</v>
+        <v>-28.30068596265098</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.3505981831975797</v>
+        <v>-0.5660137192530196</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.6562058192716992</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2mcmYkSq</t>
+          <t>4E8uaJWa</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45584.5625</v>
+        <v>45590.64583333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>stuttgart</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1513,37 +1551,37 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6934812760055478</v>
+        <v>0.4352087825916487</v>
       </c>
       <c r="M11" t="n">
-        <v>0.188626907073509</v>
+        <v>0.2528915898843364</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1178918169209431</v>
+        <v>0.3118996275240149</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06029411764705883</v>
+        <v>0.06871988267337104</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3475105219699873</v>
+        <v>0.3152064586474116</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5386629937908096</v>
+        <v>0.3401004086964048</v>
       </c>
       <c r="S11" t="n">
-        <v>0.113826484239203</v>
+        <v>0.3446931326561834</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
@@ -1552,19 +1590,19 @@
         <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1548182822147381</v>
+        <v>0.0327935051321685</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1548182822147381</v>
+        <v>0.0327935051321685</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5386629937908096</v>
+        <v>0.3446931326561834</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.36</v>
+        <v>3</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1572,29 +1610,32 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>0.3838447115760715</v>
+        <v>1.70396989842751</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.3838447115760715</v>
+        <v>0.0340793979685502</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.921404276934878</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>x0haJmIE</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45585.4375</v>
+        <v>45591.4375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>holstein kiel</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1614,37 +1655,37 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2697368421052632</v>
+        <v>0.253366100169603</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2697368421052632</v>
+        <v>0.2343636426568828</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4605263157894737</v>
+        <v>0.5122702571735143</v>
       </c>
       <c r="O12" t="n">
-        <v>0.05923344947735187</v>
+        <v>0.0667183577019641</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3677293184163819</v>
+        <v>0.1672306140399552</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2497558300231082</v>
+        <v>0.3865776432051026</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3825148515605099</v>
+        <v>0.4461917427549421</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1653,19 +1694,19 @@
         <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.07801146422896382</v>
+        <v>-0.06607851441857215</v>
       </c>
       <c r="W12" t="n">
         <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.07801146422896382</v>
+        <v>-0.06607851441857215</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.3825148515605099</v>
+        <v>0.4461917427549421</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1673,29 +1714,32 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>0.3045033873315461</v>
+        <v>-22.104712139573</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.3045033873315461</v>
+        <v>-0.44209424279146</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.7089058532387609</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>ELNeaSQr</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45585.52083333334</v>
+        <v>45591.4375</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>wolfsburg</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1715,69 +1759,696 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="J13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6044325050369376</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2081934184016118</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1873740765614507</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06738351254480279</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4417751078536791</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3064274967257183</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.2517973954206027</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.1626573971832585</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.1626573971832585</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4417751078536791</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>-57.3179241503268</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-1.146358483006536</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.4369573186783126</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>st  pauli</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>wolfsburg</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>59</v>
+      </c>
+      <c r="F14" t="n">
+        <v>591</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.3617021276595744</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2765957446808511</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3617021276595744</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06334841628959276</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.238150866720009</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3571376583882965</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.4047114748916944</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.04300934723211997</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.04300934723211997</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.4047114748916944</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.265614669900346</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.06531229339800693</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9355432657260341</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>holstein kiel</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>59</v>
+      </c>
+      <c r="F15" t="n">
+        <v>591</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.7449392712550608</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.1619433198380567</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.0931174089068826</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.07391304347826089</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.5091481278053708</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.2794691730686739</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2113826991259553</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.23579114344969</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.23579114344969</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.5091481278053708</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>-145.4259360973146</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-2.908518721946292</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.09373883260926454</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45591.5625</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>werder bremen</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>bayer leverkusen</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>59</v>
+      </c>
+      <c r="F16" t="n">
+        <v>591</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1994210357027983</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1894499839176584</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.6111289803795432</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.05568760611205437</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1242853202011915</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3841806166704361</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4915340631283723</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.1195949172511709</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.1195949172511709</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4915340631283723</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>-43.29494584564055</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.865898916912811</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.5365296150664491</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45592.47916666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>bochum</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>bayern munich</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>59</v>
+      </c>
+      <c r="F17" t="n">
+        <v>591</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.1052404571921501</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1183955143411689</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.7763640284666811</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.05578324225865217</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.09214327017688557</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.4096576064363935</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.4981991233867209</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-0.2781649050799602</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.2781649050799602</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.4981991233867209</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>-178.2713952128184</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-3.565427904256369</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.04984067368227356</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45592.5625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>union berlin</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>eintracht frankfurt</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>59</v>
+      </c>
+      <c r="F18" t="n">
+        <v>591</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J18" t="n">
         <v>3.3</v>
       </c>
-      <c r="K13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.4436536180308422</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.2823250296559905</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.2740213523131673</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.07333842627960285</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.3690503156071357</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.3731370625607071</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.2578126218321573</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" t="n">
-        <v>-0.07051655547013513</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-0.07051655547013513</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.3731370625607071</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA13" t="inlineStr">
+      <c r="K18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.3635250917992656</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2864137086903305</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3500611995104039</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.05801605801605803</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.271833047385438</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3725647627838288</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.3556021898307333</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.08615105409349827</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.08615105409349827</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.3725647627838288</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA18" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AB13" t="n">
-        <v>0.3026205070905719</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.3026205070905719</v>
+      <c r="AB18" t="n">
+        <v>9.976683355940647</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.1995336671188129</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9960552430807968</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45592.64583333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>heidenheim</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>hoffenheim</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>59</v>
+      </c>
+      <c r="F19" t="n">
+        <v>591</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.4394012554321584</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.269917914051183</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.2906808305166586</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.0585228724763609</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.3171114500406904</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3436295775216426</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.3392589724376669</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.07371166347045965</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.07371166347045965</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.3436295775216426</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>8.108140853029971</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.1621628170605994</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.979264980562929</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -615,58 +615,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="K2" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7238489169478611</v>
+        <v>0.7197844495765973</v>
       </c>
       <c r="M2" t="n">
-        <v>0.177860019592903</v>
+        <v>0.170130869899923</v>
       </c>
       <c r="N2" t="n">
-        <v>0.09829106345923588</v>
+        <v>0.1100846805234796</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07093314682053964</v>
+        <v>0.06869600987248048</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.533005595670592</v>
+        <v>0.5334666201787054</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3102523233424003</v>
+        <v>0.3101993965773246</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1567420809870077</v>
+        <v>0.15633398324397</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1908433212772691</v>
+        <v>-0.1863178293978919</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1908433212772691</v>
+        <v>-0.1863178293978919</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.533005595670592</v>
+        <v>0.5334666201787054</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -674,13 +672,13 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-107.731993649978</v>
+        <v>-102.1644645892276</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.15463987299956</v>
+        <v>-2.043289291784553</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.1882573947523236</v>
+        <v>0.2078875170719314</v>
       </c>
     </row>
     <row r="3">
@@ -725,49 +723,47 @@
         <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5140093406910212</v>
+        <v>0.5105762217359592</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2687534552755911</v>
+        <v>0.2669584245076587</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2172372040333877</v>
+        <v>0.2224653537563822</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06310925536306966</v>
+        <v>0.07025761124121765</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3594975492852748</v>
+        <v>0.3589086568094497</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3482094466124229</v>
+        <v>0.3481517232265687</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2922930041023024</v>
+        <v>0.2929396199639817</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.1545117914057464</v>
+        <v>-0.1516675649265095</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1545117914057464</v>
+        <v>-0.1516675649265095</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3594975492852748</v>
+        <v>0.3589086568094497</v>
       </c>
       <c r="Z3" t="n">
         <v>1.83</v>
@@ -778,13 +774,13 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-41.21921503710206</v>
+        <v>-41.34905518538639</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.8243843007420412</v>
+        <v>-0.8269811037077278</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5523395234174531</v>
+        <v>0.55134294039892</v>
       </c>
     </row>
     <row r="4">
@@ -823,58 +819,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="J4" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6690140845070423</v>
+        <v>0.6449948400412796</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1971830985915493</v>
+        <v>0.2063983488132095</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1338028169014084</v>
+        <v>0.1486068111455108</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06766917293233088</v>
+        <v>0.07666666666666666</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.489689331131483</v>
+        <v>0.4967959899678761</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3271781694361988</v>
+        <v>0.3253100089473399</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1831324994323181</v>
+        <v>0.1778940010847841</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.1793247533755593</v>
+        <v>-0.1481988500734035</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1793247533755593</v>
+        <v>-0.1481988500734035</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.489689331131483</v>
+        <v>0.4967959899678761</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -882,13 +876,13 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-78.60873410398099</v>
+        <v>-64.68494873778602</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.57217468207962</v>
+        <v>-1.29369897475572</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3114838652546875</v>
+        <v>0.3899783839213068</v>
       </c>
     </row>
     <row r="5">
@@ -951,31 +945,29 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3864998697000389</v>
+        <v>0.3876746774015735</v>
       </c>
       <c r="R5" t="n">
-        <v>0.335577206624032</v>
+        <v>0.3355014801438096</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2779229236759292</v>
+        <v>0.2768238424546168</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.1692225694708834</v>
+        <v>-0.1680477617693488</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1692225694708834</v>
+        <v>-0.1680477617693488</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3864998697000389</v>
+        <v>0.3876746774015735</v>
       </c>
       <c r="Z5" t="n">
         <v>1.7</v>
@@ -986,13 +978,13 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-48.99288878713343</v>
+        <v>-48.70757834533216</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.9798577757426686</v>
+        <v>-0.9741515669066432</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4945137693516743</v>
+        <v>0.4965680991946713</v>
       </c>
     </row>
     <row r="6">
@@ -1031,58 +1023,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5682242990654205</v>
+        <v>0.5590930268675262</v>
       </c>
       <c r="M6" t="n">
-        <v>0.234392523364486</v>
+        <v>0.2334213387171921</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1973831775700934</v>
+        <v>0.2074856344152819</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06658692185007986</v>
+        <v>0.07102461743180299</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3824937066336742</v>
+        <v>0.3857783886646933</v>
       </c>
       <c r="R6" t="n">
-        <v>0.344658366537651</v>
+        <v>0.3445749432805242</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2728479268286748</v>
+        <v>0.2696466680547824</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.1857305924317463</v>
+        <v>-0.1733146382028328</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1857305924317463</v>
+        <v>-0.1733146382028328</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3824937066336742</v>
+        <v>0.3857783886646933</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1090,13 +1080,13 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>-56.75159754683656</v>
+        <v>-53.0970284970093</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.135031950936731</v>
+        <v>-1.061940569940186</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.4407240064816078</v>
+        <v>0.4655568086901336</v>
       </c>
     </row>
     <row r="7">
@@ -1135,58 +1125,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J7" t="n">
         <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2237903225806452</v>
+        <v>0.2299619616899878</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2540322580645161</v>
+        <v>0.2548227143051216</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5221774193548387</v>
+        <v>0.5152153240048907</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06392106392106389</v>
+        <v>0.06062079672635434</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1964973149715032</v>
+        <v>0.1969229322402854</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3791722029115259</v>
+        <v>0.3791724152914838</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4243304821169709</v>
+        <v>0.4239046524682308</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.0978469372378678</v>
+        <v>-0.09131067153665989</v>
       </c>
       <c r="W7" t="n">
         <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0978469372378678</v>
+        <v>-0.09131067153665989</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4243304821169709</v>
+        <v>0.4239046524682308</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1194,13 +1182,13 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>-29.52564152368154</v>
+        <v>-27.01861276905272</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.5905128304736308</v>
+        <v>-0.5403722553810545</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.6459865863227952</v>
+        <v>0.6669756887033489</v>
       </c>
     </row>
     <row r="8">
@@ -1263,31 +1251,29 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4901233034693709</v>
+        <v>0.4955682892105192</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3136940934930733</v>
+        <v>0.3126776390602697</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1961826030375558</v>
+        <v>0.1917540717292111</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.2033579725361769</v>
+        <v>-0.1979129867950286</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2033579725361769</v>
+        <v>-0.1979129867950286</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4901233034693709</v>
+        <v>0.4955682892105192</v>
       </c>
       <c r="Z8" t="n">
         <v>1.36</v>
@@ -1298,13 +1284,13 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>-92.62008535601542</v>
+        <v>-90.56309074269269</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.852401707120308</v>
+        <v>-1.811261814853854</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.2456825891514715</v>
+        <v>0.254551181255875</v>
       </c>
     </row>
     <row r="9">
@@ -1343,58 +1329,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.2768780487804878</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2775479503572772</v>
+        <v>0.2852682926829269</v>
       </c>
       <c r="N9" t="n">
-        <v>0.46032342986085</v>
+        <v>0.4378536585365854</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05970030288538175</v>
+        <v>0.06226422915889396</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2176548029257694</v>
+        <v>0.2190719802106852</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3766298803319589</v>
+        <v>0.3763810442695905</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4057153167422716</v>
+        <v>0.4045469755197244</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.05460811311857838</v>
+        <v>-0.03330668301686096</v>
       </c>
       <c r="W9" t="n">
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.05460811311857838</v>
+        <v>-0.03330668301686096</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4057153167422716</v>
+        <v>0.4045469755197244</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1402,13 +1386,13 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>-16.02700958841365</v>
+        <v>-11.32382631587762</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.320540191768273</v>
+        <v>-0.2264765263175523</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.7619992912455799</v>
+        <v>0.8038143256144191</v>
       </c>
     </row>
     <row r="10">
@@ -1453,19 +1437,19 @@
         <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4697535474234503</v>
+        <v>0.4664634146341463</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2763256161314414</v>
+        <v>0.274390243902439</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2539208364451083</v>
+        <v>0.2591463414634146</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06438791732909377</v>
+        <v>0.0718954248366015</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
@@ -1482,17 +1466,15 @@
       <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.1112569772367052</v>
+        <v>-0.1079668444474011</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1112569772367052</v>
+        <v>-0.1079668444474011</v>
       </c>
       <c r="Y10" t="n">
         <v>0.3584965701867451</v>
@@ -1551,58 +1533,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="J11" t="n">
         <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4352087825916487</v>
+        <v>0.4454368932038835</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2528915898843364</v>
+        <v>0.2528155339805825</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3118996275240149</v>
+        <v>0.301747572815534</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06871988267337104</v>
+        <v>0.06904139162203671</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3152064586474116</v>
+        <v>0.3148017923440429</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3401004086964048</v>
+        <v>0.3401414299776316</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3446931326561834</v>
+        <v>0.3450567776783255</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.0327935051321685</v>
+        <v>0.04330920486279155</v>
       </c>
       <c r="W11" t="n">
         <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0327935051321685</v>
+        <v>0.04330920486279155</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3446931326561834</v>
+        <v>0.3450567776783255</v>
       </c>
       <c r="Z11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1610,13 +1590,13 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>1.70396989842751</v>
+        <v>3.317905276324246</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0340793979685502</v>
+        <v>0.06635810552648491</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.921404276934878</v>
+        <v>0.9360164891007222</v>
       </c>
     </row>
     <row r="12">
@@ -1679,31 +1659,29 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1672306140399552</v>
+        <v>0.1669980959623882</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3865776432051026</v>
+        <v>0.3866322058421756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4461917427549421</v>
+        <v>0.4463696981954363</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>-0.06607851441857215</v>
+        <v>-0.06590055897807801</v>
       </c>
       <c r="W12" t="n">
         <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.06607851441857215</v>
+        <v>-0.06590055897807801</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4461917427549421</v>
+        <v>0.4463696981954363</v>
       </c>
       <c r="Z12" t="n">
         <v>1.83</v>
@@ -1714,13 +1692,13 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>-22.104712139573</v>
+        <v>-22.06547618100621</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.44209424279146</v>
+        <v>-0.4413095236201243</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.7089058532387609</v>
+        <v>0.7092445293022357</v>
       </c>
     </row>
     <row r="13">
@@ -1783,31 +1761,29 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4417751078536791</v>
+        <v>0.4404587456083536</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3064274967257183</v>
+        <v>0.3064480657429559</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2517973954206027</v>
+        <v>0.2530931886486905</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>-0.1626573971832585</v>
+        <v>-0.1639737594285839</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1626573971832585</v>
+        <v>-0.1639737594285839</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4417751078536791</v>
+        <v>0.4404587456083536</v>
       </c>
       <c r="Z13" t="n">
         <v>1.55</v>
@@ -1818,13 +1794,13 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>-57.3179241503268</v>
+        <v>-57.68889896491852</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.146358483006536</v>
+        <v>-1.15377797929837</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.4369573186783126</v>
+        <v>0.4345018672277963</v>
       </c>
     </row>
     <row r="14">
@@ -1887,31 +1863,29 @@
         <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.238150866720009</v>
+        <v>0.2378793258306978</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3571376583882965</v>
+        <v>0.3570999288367895</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4047114748916944</v>
+        <v>0.4050207453325126</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.04300934723211997</v>
+        <v>0.04331861767293821</v>
       </c>
       <c r="W14" t="n">
         <v>2</v>
       </c>
       <c r="X14" t="n">
-        <v>0.04300934723211997</v>
+        <v>0.04331861767293821</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.4047114748916944</v>
+        <v>0.4050207453325126</v>
       </c>
       <c r="Z14" t="n">
         <v>2.6</v>
@@ -1922,13 +1896,13 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>3.265614669900346</v>
+        <v>3.315871116533309</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.06531229339800693</v>
+        <v>0.06631742233066618</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.9355432657260341</v>
+        <v>0.9359980805170577</v>
       </c>
     </row>
     <row r="15">
@@ -1973,49 +1947,47 @@
         <v>5.75</v>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7449392712550608</v>
+        <v>0.7512991833704529</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1619433198380567</v>
+        <v>0.1633259094283593</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0931174089068826</v>
+        <v>0.08537490720118782</v>
       </c>
       <c r="O15" t="n">
-        <v>0.07391304347826089</v>
+        <v>0.06482213438735185</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.5091481278053708</v>
+        <v>0.5084470222710094</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2794691730686739</v>
+        <v>0.2795301883910938</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2113826991259553</v>
+        <v>0.2120227893378969</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>-0.23579114344969</v>
+        <v>-0.2428521610994435</v>
       </c>
       <c r="W15" t="n">
         <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.23579114344969</v>
+        <v>-0.2428521610994435</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5091481278053708</v>
+        <v>0.5084470222710094</v>
       </c>
       <c r="Z15" t="n">
         <v>1.25</v>
@@ -2026,13 +1998,13 @@
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>-145.4259360973146</v>
+        <v>-145.7764888644953</v>
       </c>
       <c r="AC15" t="n">
-        <v>-2.908518721946292</v>
+        <v>-2.915529777289906</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.09373883260926454</v>
+        <v>0.09311757953811441</v>
       </c>
     </row>
     <row r="16">
@@ -2077,52 +2049,50 @@
         <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1994210357027983</v>
+        <v>0.197840563780953</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1894499839176584</v>
+        <v>0.1879485355919054</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6111289803795432</v>
+        <v>0.6142109006271417</v>
       </c>
       <c r="O16" t="n">
-        <v>0.05568760611205437</v>
+        <v>0.06412108703130381</v>
       </c>
       <c r="P16" t="n">
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1242853202011915</v>
+        <v>0.1195523256994929</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3841806166704361</v>
+        <v>0.3853122815084659</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4915340631283723</v>
+        <v>0.4951353927920412</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>-0.1195949172511709</v>
+        <v>-0.1190755078351005</v>
       </c>
       <c r="W16" t="n">
         <v>2</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1195949172511709</v>
+        <v>-0.1190755078351005</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.4915340631283723</v>
+        <v>0.4951353927920412</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2130,13 +2100,13 @@
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>-43.29494584564055</v>
+        <v>-45.7439337789013</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.865898916912811</v>
+        <v>-0.914878675578026</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.5365296150664491</v>
+        <v>0.5182185083656299</v>
       </c>
     </row>
     <row r="17">
@@ -2181,52 +2151,50 @@
         <v>8</v>
       </c>
       <c r="K17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1052404571921501</v>
+        <v>0.1038961038961039</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1183955143411689</v>
+        <v>0.1168831168831169</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7763640284666811</v>
+        <v>0.7792207792207793</v>
       </c>
       <c r="O17" t="n">
-        <v>0.05578324225865217</v>
+        <v>0.06944444444444442</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.09214327017688557</v>
+        <v>0.08973593565029485</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4096576064363935</v>
+        <v>0.4100188559815401</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4981991233867209</v>
+        <v>0.500245208368165</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>-0.2781649050799602</v>
+        <v>-0.2789755708526143</v>
       </c>
       <c r="W17" t="n">
         <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2781649050799602</v>
+        <v>-0.2789755708526143</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.4981991233867209</v>
+        <v>0.500245208368165</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2234,13 +2202,13 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>-178.2713952128184</v>
+        <v>-199.852874979101</v>
       </c>
       <c r="AC17" t="n">
-        <v>-3.565427904256369</v>
+        <v>-3.997057499582021</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.04984067368227356</v>
+        <v>0.03268417827542294</v>
       </c>
     </row>
     <row r="18">
@@ -2303,31 +2271,29 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.271833047385438</v>
+        <v>0.2701630991415704</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3725647627838288</v>
+        <v>0.3727973553968514</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3556021898307333</v>
+        <v>0.3570395454615783</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.08615105409349827</v>
+        <v>0.08638364670652088</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.08615105409349827</v>
+        <v>0.08638364670652088</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.3725647627838288</v>
+        <v>0.3727973553968514</v>
       </c>
       <c r="Z18" t="n">
         <v>3.3</v>
@@ -2338,13 +2304,13 @@
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>9.976683355940647</v>
+        <v>10.01005533954823</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.1995336671188129</v>
+        <v>0.2002011067909647</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.9960552430807968</v>
+        <v>0.9963545832864301</v>
       </c>
     </row>
     <row r="19">
@@ -2407,31 +2373,29 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.3171114500406904</v>
+        <v>0.3149298234116497</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3436295775216426</v>
+        <v>0.3436526017499043</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3392589724376669</v>
+        <v>0.3414175748384461</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.07371166347045965</v>
+        <v>0.07373468769872127</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.07371166347045965</v>
+        <v>0.07373468769872127</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.3436295775216426</v>
+        <v>0.3436526017499043</v>
       </c>
       <c r="Z19" t="n">
         <v>3.5</v>
@@ -2442,13 +2406,13 @@
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>8.108140853029971</v>
+        <v>8.111364244986591</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.1621628170605994</v>
+        <v>0.1622272848997318</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.979264980562929</v>
+        <v>0.9792939922506444</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -618,50 +618,50 @@
         <v>1.3</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="K2" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7197844495765973</v>
+        <v>0.7296439901304195</v>
       </c>
       <c r="M2" t="n">
-        <v>0.170130869899923</v>
+        <v>0.1649629890729644</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1100846805234796</v>
+        <v>0.1053930207966162</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06869600987248048</v>
+        <v>0.05425492382014108</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5334666201787054</v>
+        <v>0.5331592001430043</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3101993965773246</v>
+        <v>0.3100206384208382</v>
       </c>
       <c r="S2" t="n">
-        <v>0.15633398324397</v>
+        <v>0.1568201614361574</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1863178293978919</v>
+        <v>-0.1964847899874151</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1863178293978919</v>
+        <v>-0.1964847899874151</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5334666201787054</v>
+        <v>0.5331592001430043</v>
       </c>
       <c r="Z2" t="n">
         <v>1.3</v>
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-102.1644645892276</v>
+        <v>-102.2976799380314</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.043289291784553</v>
+        <v>-2.045953598760629</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.2078875170719314</v>
+        <v>0.2073976914330725</v>
       </c>
     </row>
     <row r="3">
@@ -717,25 +717,25 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5105762217359592</v>
+        <v>0.5125</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2669584245076587</v>
+        <v>0.25625</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2224653537563822</v>
+        <v>0.23125</v>
       </c>
       <c r="O3" t="n">
-        <v>0.07025761124121765</v>
+        <v>0.05471324983520098</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -754,19 +754,19 @@
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.1516675649265095</v>
+        <v>-0.1535913431905503</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1516675649265095</v>
+        <v>-0.1535913431905503</v>
       </c>
       <c r="Y3" t="n">
         <v>0.3589086568094497</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-41.34905518538639</v>
+        <v>-39.53164528264918</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.8269811037077278</v>
+        <v>-0.7906329056529836</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.55134294039892</v>
+        <v>0.5653836566430673</v>
       </c>
     </row>
     <row r="4">
@@ -822,22 +822,22 @@
         <v>1.44</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="K4" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6449948400412796</v>
+        <v>0.6558682952734998</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2063983488132095</v>
+        <v>0.1988316516197557</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1486068111455108</v>
+        <v>0.1453000531067446</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07666666666666666</v>
+        <v>0.05881691408007184</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -856,13 +856,13 @@
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.1481988500734035</v>
+        <v>-0.1590723053056237</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1481988500734035</v>
+        <v>-0.1590723053056237</v>
       </c>
       <c r="Y4" t="n">
         <v>0.4967959899678761</v>
@@ -921,56 +921,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5557224391709222</v>
+        <v>0.5477819635580841</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2553319315109642</v>
+        <v>0.2527100791881294</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1889456293181136</v>
+        <v>0.1995079572537864</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05850556438791732</v>
+        <v>0.05522766453706529</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3876746774015735</v>
+        <v>0.387086895390314</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3355014801438096</v>
+        <v>0.3356173100422264</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2768238424546168</v>
+        <v>0.2772957945674596</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.1680477617693488</v>
+        <v>-0.16069506816777</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1680477617693488</v>
+        <v>-0.16069506816777</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3876746774015735</v>
+        <v>0.387086895390314</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-48.70757834533216</v>
+        <v>-45.25200972256941</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.9741515669066432</v>
+        <v>-0.9050401944513883</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4965680991946713</v>
+        <v>0.5218664632633849</v>
       </c>
     </row>
     <row r="6">
@@ -1026,50 +1026,50 @@
         <v>1.67</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5590930268675262</v>
+        <v>0.5692192187805826</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2334213387171921</v>
+        <v>0.2112435767474606</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2074856344152819</v>
+        <v>0.2195372044719568</v>
       </c>
       <c r="O6" t="n">
-        <v>0.07102461743180299</v>
+        <v>0.05197149964889314</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3857783886646933</v>
+        <v>0.3848862879181934</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3445749432805242</v>
+        <v>0.3446340222656522</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2696466680547824</v>
+        <v>0.2704796898161545</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.1733146382028328</v>
+        <v>-0.1843329308623892</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1733146382028328</v>
+        <v>-0.1843329308623892</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3857783886646933</v>
+        <v>0.3848862879181934</v>
       </c>
       <c r="Z6" t="n">
         <v>1.67</v>
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>-53.0970284970093</v>
+        <v>-53.31938793680852</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.061940569940186</v>
+        <v>-1.066387758736171</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.4655568086901336</v>
+        <v>0.4640200243159465</v>
       </c>
     </row>
     <row r="7">
@@ -1125,25 +1125,25 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2299619616899878</v>
+        <v>0.25</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2548227143051216</v>
+        <v>0.25</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5152153240048907</v>
+        <v>0.5</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06062079672635434</v>
+        <v>0.05263157894736836</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
@@ -1162,19 +1162,19 @@
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.09131067153665989</v>
+        <v>-0.07609534753176922</v>
       </c>
       <c r="W7" t="n">
         <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.09131067153665989</v>
+        <v>-0.07609534753176922</v>
       </c>
       <c r="Y7" t="n">
         <v>0.4239046524682308</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>-27.01861276905272</v>
+        <v>-21.6201289233735</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.5403722553810545</v>
+        <v>-0.43240257846747</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.6669756887033489</v>
+        <v>0.7130926913106456</v>
       </c>
     </row>
     <row r="8">
@@ -1230,22 +1230,22 @@
         <v>1.36</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6934812760055478</v>
+        <v>0.6942607775720708</v>
       </c>
       <c r="M8" t="n">
-        <v>0.188626907073509</v>
+        <v>0.1798466014281936</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1178918169209431</v>
+        <v>0.1258926209997355</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06029411764705883</v>
+        <v>0.05910364145658265</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.1979129867950286</v>
+        <v>-0.1986924883615516</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1979129867950286</v>
+        <v>-0.1986924883615516</v>
       </c>
       <c r="Y8" t="n">
         <v>0.4955682892105192</v>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J9" t="n">
         <v>3.3</v>
@@ -1338,16 +1338,16 @@
         <v>2.15</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2768780487804878</v>
+        <v>0.2711119602598395</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2852682926829269</v>
+        <v>0.2875429881543752</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4378536585365854</v>
+        <v>0.4413450515857852</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06226422915889396</v>
+        <v>0.05386086781435617</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
@@ -1366,13 +1366,13 @@
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.03330668301686096</v>
+        <v>-0.03679807606606084</v>
       </c>
       <c r="W9" t="n">
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.03330668301686096</v>
+        <v>-0.03679807606606084</v>
       </c>
       <c r="Y9" t="n">
         <v>0.4045469755197244</v>
@@ -1431,25 +1431,25 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
         <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4664634146341463</v>
+        <v>0.4640029460504511</v>
       </c>
       <c r="M10" t="n">
-        <v>0.274390243902439</v>
+        <v>0.2717731541152641</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2591463414634146</v>
+        <v>0.2642238998342846</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0718954248366015</v>
+        <v>0.05129694154084419</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
@@ -1468,19 +1468,19 @@
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.1079668444474011</v>
+        <v>-0.1055063758637059</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1079668444474011</v>
+        <v>-0.1055063758637059</v>
       </c>
       <c r="Y10" t="n">
         <v>0.3584965701867451</v>
       </c>
       <c r="Z10" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>-28.30068596265098</v>
+        <v>-25.24590772544501</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.5660137192530196</v>
+        <v>-0.5049181545089002</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.6562058192716992</v>
+        <v>0.6819868445388029</v>
       </c>
     </row>
     <row r="11">
@@ -1533,25 +1533,25 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="J11" t="n">
         <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4454368932038835</v>
+        <v>0.4352087825916487</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2528155339805825</v>
+        <v>0.2528915898843364</v>
       </c>
       <c r="N11" t="n">
-        <v>0.301747572815534</v>
+        <v>0.3118996275240149</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06904139162203671</v>
+        <v>0.06871988267337104</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
@@ -1570,19 +1570,19 @@
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.04330920486279155</v>
+        <v>0.03315715015431064</v>
       </c>
       <c r="W11" t="n">
         <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04330920486279155</v>
+        <v>0.03315715015431064</v>
       </c>
       <c r="Y11" t="n">
         <v>0.3450567776783255</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>3.317905276324246</v>
+        <v>1.758516651748832</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.06635810552648491</v>
+        <v>0.03517033303497663</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.9360164891007222</v>
+        <v>0.9218983051547678</v>
       </c>
     </row>
     <row r="12">
@@ -1659,29 +1659,29 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1669980959623882</v>
+        <v>0.1675011224249515</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3866322058421756</v>
+        <v>0.3865535043308641</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4463696981954363</v>
+        <v>0.4459453732441845</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>-0.06590055897807801</v>
+        <v>-0.06632488392932973</v>
       </c>
       <c r="W12" t="n">
         <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.06590055897807801</v>
+        <v>-0.06632488392932973</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4463696981954363</v>
+        <v>0.4459453732441845</v>
       </c>
       <c r="Z12" t="n">
         <v>1.83</v>
@@ -1692,13 +1692,13 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>-22.06547618100621</v>
+        <v>-22.15903216423401</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.4413095236201243</v>
+        <v>-0.4431806432846802</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.7092445293022357</v>
+        <v>0.7084370703004019</v>
       </c>
     </row>
     <row r="13">
@@ -2169,29 +2169,29 @@
         <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.08973593565029485</v>
+        <v>0.09018482993288715</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4100188559815401</v>
+        <v>0.4100386714906</v>
       </c>
       <c r="S17" t="n">
-        <v>0.500245208368165</v>
+        <v>0.4997764985765128</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>-0.2789755708526143</v>
+        <v>-0.2794442806442665</v>
       </c>
       <c r="W17" t="n">
         <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2789755708526143</v>
+        <v>-0.2794442806442665</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.500245208368165</v>
+        <v>0.4997764985765128</v>
       </c>
       <c r="Z17" t="n">
         <v>1.2</v>
@@ -2202,13 +2202,13 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>-199.852874979101</v>
+        <v>-200.1341008540924</v>
       </c>
       <c r="AC17" t="n">
-        <v>-3.997057499582021</v>
+        <v>-4.002682017081848</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.03268417827542294</v>
+        <v>0.0325041500601822</v>
       </c>
     </row>
     <row r="18">

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,16 +565,6 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>stake_to_bet_raw</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>stake_to_bet_norm</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
           <t>stake_to_bet</t>
         </is>
       </c>
@@ -582,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>4E8uaJWa</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.4375</v>
+        <v>45590.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>holstein kiel</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -615,56 +605,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2711119602598395</v>
+        <v>0.4249504950495049</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2875429881543752</v>
+        <v>0.2526732673267326</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4413450515857852</v>
+        <v>0.3223762376237624</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05386086781435617</v>
+        <v>0.06964331102262133</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2190719802106852</v>
+        <v>0.3040100641906198</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3763810442695905</v>
+        <v>0.3490229784832968</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4045469755197244</v>
+        <v>0.3469669573260834</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.03679807606606084</v>
+        <v>0.09634971115656421</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.03679807606606084</v>
+        <v>0.09634971115656421</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4045469755197244</v>
+        <v>0.3490229784832968</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.15</v>
+        <v>3.7</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -672,32 +662,26 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-11.32382631587762</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-0.2264765263175523</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.8038143256144191</v>
+        <v>3.034982421624235</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>x0haJmIE</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45585.52083333334</v>
+        <v>45591.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wolfsburg</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -717,56 +701,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.2635228848821082</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.2371705963938974</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.4993065187239945</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3561049651071056</v>
+        <v>0.1600571541108064</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3337767159932192</v>
+        <v>0.3905296563595927</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3101183188996752</v>
+        <v>0.4494131895296009</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.1042184647537443</v>
+        <v>-0.04989332919439354</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1042184647537443</v>
+        <v>-0.04989332919439354</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3561049651071056</v>
+        <v>0.4494131895296009</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -774,13 +758,1543 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-25.7128401457556</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-0.5142568029151119</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.6780197553899253</v>
+        <v>3.907940778557348</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ELNeaSQr</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>rb leipzig</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F4" t="n">
+        <v>591</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5830269494941478</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2181301750994271</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1988428754064251</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.05875714862384762</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.4368846360551495</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.3124861485723202</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.2506292153725302</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>-0.1461423134389983</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.1461423134389983</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.4368846360551495</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>3.163595472515552</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>st  pauli</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>wolfsburg</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>59</v>
+      </c>
+      <c r="F5" t="n">
+        <v>591</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.3677036001398113</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2757777001048585</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.3565186997553303</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.06650264668605077</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.2440618180108188</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.3514457502376762</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.4044924317515049</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.04797373199617455</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.04797373199617455</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.4044924317515049</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>3.51732549352652</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>holstein kiel</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>59</v>
+      </c>
+      <c r="F6" t="n">
+        <v>591</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.7564469914040115</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.157593123209169</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.08595988538681948</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.05757575757575761</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.4899833271001774</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.2905350197557416</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2194816531440808</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>-0.2664636643038341</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.2664636643038341</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.4899833271001774</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>3.10218691262459</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45591.5625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>werder bremen</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>bayer leverkusen</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>59</v>
+      </c>
+      <c r="F7" t="n">
+        <v>591</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1891891891891892</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1801801801801802</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.6306306306306306</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.05714285714285716</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1257827098404777</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3780876819404719</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.4961296082190503</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>-0.1345010224115803</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.1345010224115803</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.4961296082190503</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.729383452326513</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.47916666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bochum</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>bayern munich</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>59</v>
+      </c>
+      <c r="F8" t="n">
+        <v>591</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>11</v>
+      </c>
+      <c r="J8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.08650815270265011</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1001673347083317</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.8133245125890182</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.05087310350468255</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.08643594660021311</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.4122180377554751</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5013460156443118</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>-0.3119784969447064</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.3119784969447064</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.5013460156443118</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.003102323264454</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.5625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>union berlin</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>eintracht frankfurt</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>59</v>
+      </c>
+      <c r="F9" t="n">
+        <v>591</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.3608748481166464</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.287606318347509</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.3515188335358444</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.05362881028280286</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.2833317539602925</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3647476241394124</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.351920621900295</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.07714130579190331</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.07714130579190331</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.3647476241394124</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.171718470809216</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45592.64583333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>heidenheim</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>hoffenheim</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>59</v>
+      </c>
+      <c r="F10" t="n">
+        <v>591</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.4243156199677939</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2745571658615137</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.3011272141706924</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.07124374676556844</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.2959731725294592</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3527285859666317</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.3512982415039091</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.07817142010511802</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.07817142010511802</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.3527285859666317</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.067205095392687</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IHYEDIog</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45597.6875</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>bayer leverkusen</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" t="n">
+        <v>591</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6179775280898876</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2101123595505618</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1719101123595506</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05763517528223416</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.5133008931362973</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3200688928273175</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1666302140363851</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-0.1046766349535903</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.1046766349535903</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.5133008931362973</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.00837022316619</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bayern munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>union berlin</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F12" t="n">
+        <v>591</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.794066317626527</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1338568935427574</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.07207678883071553</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.06723784689886392</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.5570080744887819</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.2821140056139682</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.1608779198972498</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.2370582431377452</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.2370582431377452</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.5570080744887819</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.812860460211252</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>eintracht frankfurt</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>bochum</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F13" t="n">
+        <v>591</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.7046463956269218</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.1703963102152375</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1249572941578408</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06703121439963544</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4480436777080846</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3113133196995683</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.2406430025923472</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.2566027179188372</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.2566027179188372</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4480436777080846</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.780367989146638</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>hoffenheim</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>st  pauli</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>59</v>
+      </c>
+      <c r="F14" t="n">
+        <v>591</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5029554003224072</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2385814078452445</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.2584631918323482</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.07472857472857486</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3958540068290565</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3521671742280995</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.2519788189428441</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.1071013934933507</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.1071013934933507</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.3958540068290565</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.976550522485253</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>holstein kiel</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>heidenheim</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>59</v>
+      </c>
+      <c r="F15" t="n">
+        <v>591</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.369093490164267</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2689109714053944</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.3619955384303387</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06248653307476837</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.2701157294961343</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3535757399068384</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.3763085305970272</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.01431299216668858</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.01431299216668858</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.3763085305970272</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.272248092180785</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>wolfsburg</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>augsburg</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>59</v>
+      </c>
+      <c r="F16" t="n">
+        <v>591</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4792284866468843</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2459198813056379</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.2748516320474777</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.07009605461617863</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.3593873865627473</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3387849130708476</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.3018277003664052</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>-0.119841100084137</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.119841100084137</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.3593873865627473</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.604059448031943</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45598.60416666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>dortmund</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>rb leipzig</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>59</v>
+      </c>
+      <c r="F17" t="n">
+        <v>591</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.4438612933458295</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2579194001874414</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2982193064667292</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.04788654934003755</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.3291125126874511</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3525067318188922</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3183807554936567</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.09458733163145083</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.09458733163145083</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.3525067318188922</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.065275928890585</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>GnZmQeVb</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45599.47916666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>mainz</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>59</v>
+      </c>
+      <c r="F18" t="n">
+        <v>591</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.5425559600191486</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2406722591879813</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.21677178079287</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06539182070827154</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.3776069020931788</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3365999861787921</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.2857931117280292</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-0.1649490579259699</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.1649490579259699</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.3776069020931788</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.566368462027349</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>raQ4MDUN</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45599.5625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>b  monchengladbach</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>werder bremen</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>59</v>
+      </c>
+      <c r="F19" t="n">
+        <v>591</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.4669187145557656</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2457466918714556</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.2873345935727789</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.07085020242914974</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.343734436783285</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3533941493590095</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.3028714138577057</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.107647457487554</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.107647457487554</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.3533941493590095</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.072992603152552</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,56 +605,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4249504950495049</v>
+        <v>0.4213444213444214</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2526732673267326</v>
+        <v>0.2494802494802495</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3223762376237624</v>
+        <v>0.3291753291753292</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06964331102262133</v>
+        <v>0.05482456140350855</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3040100641906198</v>
+        <v>0.3057234133193339</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3490229784832968</v>
+        <v>0.3488325774856244</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3469669573260834</v>
+        <v>0.3454440091950419</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.09634971115656421</v>
+        <v>0.09935232800537483</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.09634971115656421</v>
+        <v>0.09935232800537483</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3490229784832968</v>
+        <v>0.3488325774856244</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>3.034982421624235</v>
+        <v>3.033326760774893</v>
       </c>
     </row>
     <row r="3">
@@ -707,50 +707,50 @@
         <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2635228848821082</v>
+        <v>0.2642135841748513</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2371705963938974</v>
+        <v>0.2377922257573662</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4993065187239945</v>
+        <v>0.4979941900677826</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05409356725146197</v>
+        <v>0.05133798720186156</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1600571541108064</v>
+        <v>0.1626766719646279</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3905296563595927</v>
+        <v>0.3901446849135075</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4494131895296009</v>
+        <v>0.4471786431218648</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.04989332919439354</v>
+        <v>-0.05081554694591778</v>
       </c>
       <c r="W3" t="n">
         <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.04989332919439354</v>
+        <v>-0.05081554694591778</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4494131895296009</v>
+        <v>0.4471786431218648</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.907940778557348</v>
+        <v>3.888509940229013</v>
       </c>
     </row>
     <row r="4">
@@ -797,56 +797,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5830269494941478</v>
+        <v>0.5579074690051407</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2181301750994271</v>
+        <v>0.231327487148473</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1988428754064251</v>
+        <v>0.2107650438463864</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05875714862384762</v>
+        <v>0.05435995536425953</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4368846360551495</v>
+        <v>0.4356688828737934</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3124861485723202</v>
+        <v>0.3126612508253109</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2506292153725302</v>
+        <v>0.2516698663008958</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.1461423134389983</v>
+        <v>-0.1222385861313473</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1461423134389983</v>
+        <v>-0.1222385861313473</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4368846360551495</v>
+        <v>0.4356688828737934</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>3.163595472515552</v>
+        <v>3.256952954885784</v>
       </c>
     </row>
     <row r="5">
@@ -893,56 +893,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3677036001398113</v>
+        <v>0.3787575150300601</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2757777001048585</v>
+        <v>0.2705410821643286</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3565186997553303</v>
+        <v>0.3507014028056112</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06650264668605077</v>
+        <v>0.05608465608465618</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2440618180108188</v>
+        <v>0.2453634232083602</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3514457502376762</v>
+        <v>0.3514391272975689</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4044924317515049</v>
+        <v>0.4031974494940708</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.04797373199617455</v>
+        <v>0.05249604668845959</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04797373199617455</v>
+        <v>0.05249604668845959</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4044924317515049</v>
+        <v>0.4031974494940708</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>3.51732549352652</v>
+        <v>3.506064778244371</v>
       </c>
     </row>
     <row r="6">
@@ -992,50 +992,50 @@
         <v>1.25</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7564469914040115</v>
+        <v>0.763271162123386</v>
       </c>
       <c r="M6" t="n">
-        <v>0.157593123209169</v>
+        <v>0.1362984218077475</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08595988538681948</v>
+        <v>0.1004304160688666</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05757575757575761</v>
+        <v>0.04812030075187979</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4899833271001774</v>
+        <v>0.490289221539312</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2905350197557416</v>
+        <v>0.2904836320543195</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2194816531440808</v>
+        <v>0.2192271464063685</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.2664636643038341</v>
+        <v>-0.272981940584074</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2664636643038341</v>
+        <v>-0.272981940584074</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4899833271001774</v>
+        <v>0.490289221539312</v>
       </c>
       <c r="Z6" t="n">
         <v>1.25</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>3.10218691262459</v>
+        <v>3.076506532615765</v>
       </c>
     </row>
     <row r="7">
@@ -1085,19 +1085,19 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J7" t="n">
         <v>5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5.25</v>
       </c>
       <c r="K7" t="n">
         <v>1.5</v>
       </c>
       <c r="L7" t="n">
+        <v>0.1801801801801802</v>
+      </c>
+      <c r="M7" t="n">
         <v>0.1891891891891892</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.1801801801801802</v>
       </c>
       <c r="N7" t="n">
         <v>0.6306306306306306</v>
@@ -1109,29 +1109,29 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1257827098404777</v>
+        <v>0.1264956942324874</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3780876819404719</v>
+        <v>0.3779440136477314</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4961296082190503</v>
+        <v>0.4955602921197813</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.1345010224115803</v>
+        <v>-0.1350703385108493</v>
       </c>
       <c r="W7" t="n">
         <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1345010224115803</v>
+        <v>-0.1350703385108493</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4961296082190503</v>
+        <v>0.4955602921197813</v>
       </c>
       <c r="Z7" t="n">
         <v>1.5</v>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>3.729383452326513</v>
+        <v>3.72195759016206</v>
       </c>
     </row>
     <row r="8">
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
         <v>9.5</v>
@@ -1190,44 +1190,44 @@
         <v>1.17</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08650815270265011</v>
+        <v>0.0798749595774496</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1001673347083317</v>
+        <v>0.1008946857820416</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8133245125890182</v>
+        <v>0.8192303546405088</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05087310350468255</v>
+        <v>0.04329734592892498</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.08643594660021311</v>
+        <v>0.08628532659525594</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4122180377554751</v>
+        <v>0.4120976734785101</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5013460156443118</v>
+        <v>0.501616999926234</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.3119784969447064</v>
+        <v>-0.3176133547142748</v>
       </c>
       <c r="W8" t="n">
         <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3119784969447064</v>
+        <v>-0.3176133547142748</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5013460156443118</v>
+        <v>0.501616999926234</v>
       </c>
       <c r="Z8" t="n">
         <v>1.17</v>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>3.003102323264454</v>
+        <v>2.980959326717606</v>
       </c>
     </row>
     <row r="9">
@@ -1277,53 +1277,53 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="J9" t="n">
         <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3608748481166464</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="M9" t="n">
-        <v>0.287606318347509</v>
+        <v>0.2861952861952861</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3515188335358444</v>
+        <v>0.3434343434343434</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05362881028280286</v>
+        <v>0.05882352941176494</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2833317539602925</v>
+        <v>0.2848249650430095</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3647476241394124</v>
+        <v>0.3646918387919587</v>
       </c>
       <c r="S9" t="n">
-        <v>0.351920621900295</v>
+        <v>0.3504831961650319</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.07714130579190331</v>
+        <v>0.07849655259667254</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.07714130579190331</v>
+        <v>0.07849655259667254</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3647476241394124</v>
+        <v>0.3646918387919587</v>
       </c>
       <c r="Z9" t="n">
         <v>3.3</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>3.171718470809216</v>
+        <v>3.171233380831353</v>
       </c>
     </row>
     <row r="10">
@@ -1373,56 +1373,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
         <v>3.1</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4243156199677939</v>
+        <v>0.4221789883268482</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2745571658615137</v>
+        <v>0.2714007782101167</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3011272141706924</v>
+        <v>0.306420233463035</v>
       </c>
       <c r="O10" t="n">
-        <v>0.07124374676556844</v>
+        <v>0.05273937532002049</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2959731725294592</v>
+        <v>0.2976763994680412</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3527285859666317</v>
+        <v>0.3525824948054169</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3512982415039091</v>
+        <v>0.3497411057265418</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.07817142010511802</v>
+        <v>0.08118171659530021</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.07817142010511802</v>
+        <v>0.08118171659530021</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3527285859666317</v>
+        <v>0.3525824948054169</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1430,871 +1430,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>3.067205095392687</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>IHYEDIog</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45597.6875</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>bayer leverkusen</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>stuttgart</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>59</v>
-      </c>
-      <c r="F11" t="n">
-        <v>591</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.6179775280898876</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.2101123595505618</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.1719101123595506</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.05763517528223416</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.5133008931362973</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.3200688928273175</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.1666302140363851</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
-        <v>-0.1046766349535903</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-0.1046766349535903</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.5133008931362973</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>4.00837022316619</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>jVWMBdG5</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45598.47916666666</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>bayern munich</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>union berlin</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>59</v>
-      </c>
-      <c r="F12" t="n">
-        <v>591</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="J12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.794066317626527</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.1338568935427574</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.07207678883071553</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.06723784689886392</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.5570080744887819</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.2821140056139682</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.1608779198972498</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
-        <v>-0.2370582431377452</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-0.2370582431377452</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.5570080744887819</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>3.812860460211252</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>485V7EFU</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45598.47916666666</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>eintracht frankfurt</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>bochum</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>59</v>
-      </c>
-      <c r="F13" t="n">
-        <v>591</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="J13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.7046463956269218</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.1703963102152375</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.1249572941578408</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.06703121439963544</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.4480436777080846</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.3113133196995683</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.2406430025923472</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>-0.2566027179188372</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-0.2566027179188372</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.4480436777080846</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.780367989146638</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8MVuSH0n</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45598.47916666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>hoffenheim</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>st  pauli</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>59</v>
-      </c>
-      <c r="F14" t="n">
-        <v>591</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.5029554003224072</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.2385814078452445</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.2584631918323482</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.07472857472857486</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.3958540068290565</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.3521671742280995</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.2519788189428441</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>-0.1071013934933507</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-0.1071013934933507</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.3958540068290565</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.976550522485253</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>2q7yHiho</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45598.47916666666</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>holstein kiel</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>heidenheim</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>59</v>
-      </c>
-      <c r="F15" t="n">
-        <v>591</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.369093490164267</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2689109714053944</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.3619955384303387</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.06248653307476837</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.2701157294961343</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.3535757399068384</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.3763085305970272</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>0.01431299216668858</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.01431299216668858</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.3763085305970272</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>3.272248092180785</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>AoSdOZaB</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45598.47916666666</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>wolfsburg</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>augsburg</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>59</v>
-      </c>
-      <c r="F16" t="n">
-        <v>591</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.4792284866468843</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.2459198813056379</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.2748516320474777</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.07009605461617863</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.3593873865627473</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.3387849130708476</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.3018277003664052</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>-0.119841100084137</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-0.119841100084137</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.3593873865627473</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.604059448031943</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>dr2N9zoI</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45598.60416666666</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>dortmund</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>rb leipzig</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>59</v>
-      </c>
-      <c r="F17" t="n">
-        <v>591</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.4438612933458295</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.2579194001874414</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.2982193064667292</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.04788654934003755</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.3291125126874511</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.3525067318188922</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.3183807554936567</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>0.09458733163145083</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.09458733163145083</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.3525067318188922</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.065275928890585</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>GnZmQeVb</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45599.47916666666</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>freiburg</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>mainz</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>59</v>
-      </c>
-      <c r="F18" t="n">
-        <v>591</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.5425559600191486</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.2406722591879813</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.21677178079287</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.06539182070827154</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.3776069020931788</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.3365999861787921</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.2857931117280292</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="n">
-        <v>-0.1649490579259699</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-0.1649490579259699</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.3776069020931788</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.566368462027349</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>raQ4MDUN</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45599.5625</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>b  monchengladbach</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>werder bremen</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>59</v>
-      </c>
-      <c r="F19" t="n">
-        <v>591</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.4669187145557656</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.2457466918714556</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.2873345935727789</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.07085020242914974</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.343734436783285</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.3533941493590095</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.3028714138577057</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="n">
-        <v>0.107647457487554</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0.107647457487554</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.3533941493590095</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB19" t="n">
-        <v>3.072992603152552</v>
+        <v>3.065934737469067</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,6 +565,16 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>stake_to_bet_raw</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>stake_to_bet_norm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>stake_to_bet</t>
         </is>
       </c>
@@ -572,20 +582,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4E8uaJWa</t>
+          <t>IHYEDIog</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45590.64583333334</v>
+        <v>45597.6875</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>b  monchengladbach</t>
+          <t>stuttgart</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -605,56 +615,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="K2" t="n">
-        <v>2.88</v>
+        <v>5.25</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4213444213444214</v>
+        <v>0.6018171661844011</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2494802494802495</v>
+        <v>0.2182108431661685</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3291753291753292</v>
+        <v>0.1799719906494304</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05482456140350855</v>
+        <v>0.05836574785251614</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3057234133193339</v>
+        <v>0.5041168797533372</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3488325774856244</v>
+        <v>0.3229150368857269</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3454440091950419</v>
+        <v>0.1729680833609359</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.09935232800537483</v>
+        <v>-0.09770028643106388</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.09935232800537483</v>
+        <v>-0.09770028643106388</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3488325774856244</v>
+        <v>0.5041168797533372</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.8</v>
+        <v>1.57</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -662,26 +672,32 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>3.033326760774893</v>
+        <v>-36.58535066443168</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-0.7317070132886336</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.48970293090156</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>x0haJmIE</t>
+          <t>jVWMBdG5</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45591.4375</v>
+        <v>45598.47916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -701,56 +717,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.6</v>
+        <v>1.18</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>1.91</v>
+        <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2642135841748513</v>
+        <v>0.794066317626527</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2377922257573662</v>
+        <v>0.1338568935427574</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4979941900677826</v>
+        <v>0.07207678883071553</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05133798720186156</v>
+        <v>0.06723784689886392</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1626766719646279</v>
+        <v>0.5700007396295266</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3901446849135075</v>
+        <v>0.2737495700658632</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4471786431218648</v>
+        <v>0.1562496903046103</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.05081554694591778</v>
+        <v>-0.2240655779970004</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.05081554694591778</v>
+        <v>-0.2240655779970004</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4471786431218648</v>
+        <v>0.5700007396295266</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.91</v>
+        <v>1.18</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -758,26 +774,32 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.888509940229013</v>
+        <v>-181.8884040206438</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-3.637768080412875</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.3543503984049824</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ELNeaSQr</t>
+          <t>485V7EFU</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45591.4375</v>
+        <v>45598.47916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -797,56 +819,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5579074690051407</v>
+        <v>0.7046463956269218</v>
       </c>
       <c r="M4" t="n">
-        <v>0.231327487148473</v>
+        <v>0.1703963102152375</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2107650438463864</v>
+        <v>0.1249572941578408</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05435995536425953</v>
+        <v>0.06703121439963544</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4356688828737934</v>
+        <v>0.4588056541824632</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3126612508253109</v>
+        <v>0.3044884224430013</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2516698663008958</v>
+        <v>0.2367059233745355</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.1222385861313473</v>
+        <v>-0.2458407414444586</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1222385861313473</v>
+        <v>-0.2458407414444586</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4356688828737934</v>
+        <v>0.4588056541824632</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -854,26 +876,32 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>3.256952954885784</v>
+        <v>-118.1177211931284</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-2.362354423862568</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.18992896312922</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Mku6FvHt</t>
+          <t>8MVuSH0n</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45591.4375</v>
+        <v>45598.47916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>hoffenheim</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>st  pauli</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>wolfsburg</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -893,56 +921,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3787575150300601</v>
+        <v>0.5066666666666666</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2705410821643286</v>
+        <v>0.2466666666666667</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3507014028056112</v>
+        <v>0.2466666666666667</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05608465608465618</v>
+        <v>0.06685633001422464</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2453634232083602</v>
+        <v>0.3963485777535414</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3514391272975689</v>
+        <v>0.3528975789808169</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4031974494940708</v>
+        <v>0.2507538432656415</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.05249604668845959</v>
+        <v>-0.1103180889131252</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05249604668845959</v>
+        <v>-0.1103180889131252</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4031974494940708</v>
+        <v>0.3963485777535414</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -950,26 +978,32 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>3.506064778244371</v>
+        <v>-31.38295660658217</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0.6276591321316434</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>4.810669932882091</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>rwXP4l3L</t>
+          <t>2q7yHiho</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45591.4375</v>
+        <v>45598.47916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>stuttgart</t>
+          <t>holstein kiel</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>holstein kiel</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -989,56 +1023,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.25</v>
+        <v>2.75</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>9.5</v>
+        <v>2.45</v>
       </c>
       <c r="L6" t="n">
-        <v>0.763271162123386</v>
+        <v>0.3411487662537115</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1362984218077475</v>
+        <v>0.2759291491757961</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1004304160688666</v>
+        <v>0.3829220845704924</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04812030075187979</v>
+        <v>0.06591727600130959</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.490289221539312</v>
+        <v>0.266062541326221</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2904836320543195</v>
+        <v>0.3566749023371619</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2192271464063685</v>
+        <v>0.3772625563366171</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.272981940584074</v>
+        <v>-0.005659528233875333</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.272981940584074</v>
+        <v>-0.005659528233875333</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.490289221539312</v>
+        <v>0.3772625563366171</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.25</v>
+        <v>2.45</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1046,26 +1080,32 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>3.076506532615765</v>
+        <v>-5.221154274157796</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.1044230854831559</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>6.550548234865823</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MiACepQ7</t>
+          <t>AoSdOZaB</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45591.5625</v>
+        <v>45598.47916666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>bayer leverkusen</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1085,56 +1125,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.25</v>
+        <v>1.95</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1801801801801802</v>
+        <v>0.483021608861449</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1891891891891892</v>
+        <v>0.2478663519157435</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6306306306306306</v>
+        <v>0.2691120392228073</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05714285714285716</v>
+        <v>0.06169269327164084</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1264956942324874</v>
+        <v>0.3546675247881616</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3779440136477314</v>
+        <v>0.3426246177004782</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4955602921197813</v>
+        <v>0.3027078575113603</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.1350703385108493</v>
+        <v>-0.1283540840732874</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1350703385108493</v>
+        <v>-0.1283540840732874</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4955602921197813</v>
+        <v>0.3546675247881616</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1142,26 +1182,32 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>3.72195759016206</v>
+        <v>-32.46298175400893</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.6492596350801786</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>4.743147302463937</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WQadeyWO</t>
+          <t>dr2N9zoI</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45592.47916666666</v>
+        <v>45598.60416666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bochum</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1181,56 +1227,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>2.25</v>
       </c>
       <c r="J8" t="n">
-        <v>9.5</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>1.17</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0798749595774496</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1008946857820416</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8192303546405088</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04329734592892498</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.08628532659525594</v>
+        <v>0.3228394979812819</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4120976734785101</v>
+        <v>0.354442885408602</v>
       </c>
       <c r="S8" t="n">
-        <v>0.501616999926234</v>
+        <v>0.322717616610116</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.3176133547142748</v>
+        <v>0.09128499067175994</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3176133547142748</v>
+        <v>0.09128499067175994</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.501616999926234</v>
+        <v>0.354442885408602</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.17</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1238,26 +1284,32 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>2.980959326717606</v>
+        <v>10.61516874888336</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.2123033749776672</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>7.641934967067556</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ABBmcc1C</t>
+          <t>GnZmQeVb</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45592.5625</v>
+        <v>45599.47916666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1277,56 +1329,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.5513666352497643</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2861952861952861</v>
+        <v>0.2403393025447691</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3434343434343434</v>
+        <v>0.2082940622054665</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05882352941176494</v>
+        <v>0.0668677727501259</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2848249650430095</v>
+        <v>0.3653147247787745</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3646918387919587</v>
+        <v>0.341329200668983</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3504831961650319</v>
+        <v>0.2933560745522424</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.07849655259667254</v>
+        <v>-0.1860519104709897</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.07849655259667254</v>
+        <v>-0.1860519104709897</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3646918387919587</v>
+        <v>0.3653147247787745</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1334,26 +1386,32 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>3.171233380831353</v>
+        <v>-54.1378525537262</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-1.082757051074524</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.496782676235883</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zyC4c6ee</t>
+          <t>raQ4MDUN</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45592.64583333334</v>
+        <v>45599.5625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>heidenheim</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>werder bremen</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1373,64 +1431,988 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4221789883268482</v>
+        <v>0.4586948321388156</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2714007782101167</v>
+        <v>0.2474537910222558</v>
       </c>
       <c r="N10" t="n">
-        <v>0.306420233463035</v>
+        <v>0.2938513768389287</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05273937532002049</v>
+        <v>0.06346277278562251</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2976763994680412</v>
+        <v>0.3402871651523205</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3525824948054169</v>
+        <v>0.3505249816386133</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3497411057265418</v>
+        <v>0.3091878532090662</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.08118171659530021</v>
+        <v>0.1030711906163576</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.08118171659530021</v>
+        <v>0.1030711906163576</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3525824948054169</v>
+        <v>0.3505249816386133</v>
       </c>
       <c r="Z10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>11.85696179381181</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.2371392358762362</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>7.726680523759429</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>v3DAZKP9</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45604.6875</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>union berlin</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" t="n">
+        <v>591</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3901639344262295</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2754098360655738</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.3344262295081967</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06792717086834732</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.2990086924769021</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3492599605227888</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.351731347000309</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.01730511749211228</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.01730511749211228</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.351731347000309</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.8417904666186082</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.01683580933237216</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>6.852882439337695</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>biQrHC9r</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45605.47916666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bochum</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>bayer leverkusen</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F12" t="n">
+        <v>591</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.134020618556701</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1443298969072165</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.7216494845360825</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.06593406593406592</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0850220051071499</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3981345369630913</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.5168434579297588</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.2048060266063236</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.2048060266063236</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.5168434579297588</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>-109.3678348971045</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-2.187356697942089</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.394535630135924</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>nee3ysec</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45605.47916666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mainz</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>dortmund</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F13" t="n">
+        <v>591</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.2951006456513482</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2552221800227877</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.449677174325864</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.05896074646074645</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1885635084915402</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3771168515935309</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.4343196399149289</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.01535753441093507</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.01535753441093507</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4343196399149289</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>-7.993523288968108</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.1598704657793621</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>6.359794309307781</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>6HTjFjve</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45605.47916666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>st  pauli</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>bayern munich</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>59</v>
+      </c>
+      <c r="F14" t="n">
+        <v>591</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>11</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.08595988538681948</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.157593123209169</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.7564469914040115</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.05757575757575761</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.08419956102360941</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.4043108131538904</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.5114896258225001</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.2449573655815114</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.2449573655815114</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.5114896258225001</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>-144.2551870887499</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-2.885103741774999</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.7311189963166821</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YmumZjET</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45605.47916666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>werder bremen</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>holstein kiel</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>59</v>
+      </c>
+      <c r="F15" t="n">
+        <v>591</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6013630896699185</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2098089001737271</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1888280101563544</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.0591648973814578</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.4314942378384312</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.320029954525088</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2484758076364808</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-0.1698688518314873</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.1698688518314873</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4314942378384312</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>-56.5884292269584</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-1.131768584539168</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.370313604417392</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>j5mWxZE4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45605.60416666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>rb leipzig</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>b  monchengladbach</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>59</v>
+      </c>
+      <c r="F16" t="n">
+        <v>591</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.6464417351857102</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1973348454777431</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.1562234193365466</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06684815486993356</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.467417631311846</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.305670415332254</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.2269119533559001</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>-0.1790241038738642</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.1790241038738642</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.467417631311846</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>-71.60987435507185</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-1.432197487101437</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.664302876095882</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>UJQITUyi</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45606.47916666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>augsburg</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>hoffenheim</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>59</v>
+      </c>
+      <c r="F17" t="n">
+        <v>591</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.4512126339537507</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2526790750141004</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2961082910321489</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.05535714285714288</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.3027506963255377</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3530808096825865</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3441684939918758</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.1004017346684862</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.1004017346684862</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.3530808096825865</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>11.78374677489817</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.2356749354979633</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>7.721690636189637</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>UkaNveph</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45606.5625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>eintracht frankfurt</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>59</v>
+      </c>
+      <c r="F18" t="n">
+        <v>591</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.5228187919463088</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2295302013422819</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.2476510067114094</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06261588931678785</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.3246755134225318</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3481061763274639</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.3272183102500044</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.118575974985182</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.118575974985182</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.3481061763274639</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>13.78178461105168</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.2756356922210336</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>7.857539930949808</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xMovyDqH</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45606.64583333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>heidenheim</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>wolfsburg</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>59</v>
+      </c>
+      <c r="F19" t="n">
+        <v>591</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J19" t="n">
         <v>3.5</v>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="K19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.3664921465968586</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2670157068062827</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.3664921465968586</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.07002801120448199</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2701385049118458</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3664490687969839</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.3634124262911704</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.09943336199070124</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.09943336199070124</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.3664490687969839</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA19" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AB10" t="n">
-        <v>3.065934737469067</v>
+      <c r="AB19" t="n">
+        <v>11.30286963157775</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.226057392631555</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>7.688895928064805</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,56 +615,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="J2" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="K2" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6018171661844011</v>
+        <v>0.6111289803795432</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2182108431661685</v>
+        <v>0.1994210357027983</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1799719906494304</v>
+        <v>0.1894499839176584</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05836574785251614</v>
+        <v>0.05568760611205437</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5041168797533372</v>
+        <v>0.5042694737416966</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3229150368857269</v>
+        <v>0.3214848863097585</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1729680833609359</v>
+        <v>0.1742456399485449</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.09770028643106388</v>
+        <v>-0.1068595066378466</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.09770028643106388</v>
+        <v>-0.1068595066378466</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5041168797533372</v>
+        <v>0.5042694737416966</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-36.58535066443168</v>
+        <v>-39.70587558188549</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.7317070132886336</v>
+        <v>-0.7941175116377098</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.48970293090156</v>
+        <v>4.302620562970569</v>
       </c>
     </row>
     <row r="3">
@@ -720,50 +720,50 @@
         <v>1.18</v>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="K3" t="n">
         <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>0.794066317626527</v>
+        <v>0.8012162051113485</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1338568935427574</v>
+        <v>0.1260580162708521</v>
       </c>
       <c r="N3" t="n">
-        <v>0.07207678883071553</v>
+        <v>0.07272577861779932</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06723784689886392</v>
+        <v>0.05771403737505443</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5700007396295266</v>
+        <v>0.5784697536459851</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2737495700658632</v>
+        <v>0.2684906159244962</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1562496903046103</v>
+        <v>0.1530396304295186</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.2240655779970004</v>
+        <v>-0.2227464514653634</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2240655779970004</v>
+        <v>-0.2227464514653634</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5700007396295266</v>
+        <v>0.5784697536459851</v>
       </c>
       <c r="Z3" t="n">
         <v>1.18</v>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-181.8884040206438</v>
+        <v>-176.3364948320765</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3.637768080412875</v>
+        <v>-3.526729896641531</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.3543503984049824</v>
+        <v>0.3947759032083871</v>
       </c>
     </row>
     <row r="4">
@@ -822,50 +822,50 @@
         <v>1.33</v>
       </c>
       <c r="J4" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="K4" t="n">
         <v>7.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7046463956269218</v>
+        <v>0.7099057574385776</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1703963102152375</v>
+        <v>0.1642042882423145</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1249572941578408</v>
+        <v>0.1258899543191078</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06703121439963544</v>
+        <v>0.05912607605971454</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4588056541824632</v>
+        <v>0.4558685645880888</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3044884224430013</v>
+        <v>0.3050879621116344</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2367059233745355</v>
+        <v>0.2390434733002767</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.2458407414444586</v>
+        <v>-0.2540371928504888</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2458407414444586</v>
+        <v>-0.2540371928504888</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4588056541824632</v>
+        <v>0.4558685645880888</v>
       </c>
       <c r="Z4" t="n">
         <v>1.33</v>
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-118.1177211931284</v>
+        <v>-119.3014573023763</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.362354423862568</v>
+        <v>-2.386029146047525</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.18992896312922</v>
+        <v>1.164433974946298</v>
       </c>
     </row>
     <row r="5">
@@ -921,56 +921,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="J5" t="n">
         <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5066666666666666</v>
+        <v>0.5157087602632829</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2466666666666667</v>
+        <v>0.2483544819162652</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2466666666666667</v>
+        <v>0.235936757820452</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06685633001422464</v>
+        <v>0.05960598216853596</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3963485777535414</v>
+        <v>0.4051067889656215</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3528975789808169</v>
+        <v>0.3504369266995791</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2507538432656415</v>
+        <v>0.2444562843347994</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.1103180889131252</v>
+        <v>-0.1106019712976614</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1103180889131252</v>
+        <v>-0.1106019712976614</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3963485777535414</v>
+        <v>0.4051067889656215</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-31.38295660658217</v>
+        <v>-31.16320195095333</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.6276591321316434</v>
+        <v>-0.6232640390190666</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.810669932882091</v>
+        <v>4.824463704622143</v>
       </c>
     </row>
     <row r="6">
@@ -1023,53 +1023,53 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
         <v>2.45</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3411487662537115</v>
+        <v>0.3506261180679785</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2759291491757961</v>
+        <v>0.2629695885509839</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3829220845704924</v>
+        <v>0.3864042933810375</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06591727600130959</v>
+        <v>0.0563114134542706</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.266062541326221</v>
+        <v>0.2680619258462033</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3566749023371619</v>
+        <v>0.3598475668993034</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3772625563366171</v>
+        <v>0.3720905072544934</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.005659528233875333</v>
+        <v>-0.01431378612654416</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.005659528233875333</v>
+        <v>-0.01431378612654416</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3772625563366171</v>
+        <v>0.3720905072544934</v>
       </c>
       <c r="Z6" t="n">
         <v>2.45</v>
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>-5.221154274157796</v>
+        <v>-6.095052222516633</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.1044230854831559</v>
+        <v>-0.1219010444503327</v>
       </c>
       <c r="AD6" t="n">
-        <v>6.550548234865823</v>
+        <v>6.490345962294962</v>
       </c>
     </row>
     <row r="7">
@@ -1125,56 +1125,58 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
         <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.483021608861449</v>
+        <v>0.4751131221719458</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2478663519157435</v>
+        <v>0.2533936651583711</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2691120392228073</v>
+        <v>0.2714932126696833</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06169269327164084</v>
+        <v>0.05238095238095219</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3546675247881616</v>
+        <v>0.3840486142344168</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3426246177004782</v>
+        <v>0.3421801725583295</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3027078575113603</v>
+        <v>0.2737712132072537</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
       <c r="V7" t="n">
-        <v>-0.1283540840732874</v>
+        <v>-0.09106450793752902</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1283540840732874</v>
+        <v>-0.09106450793752902</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3546675247881616</v>
+        <v>0.3840486142344168</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1182,13 +1184,13 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>-32.46298175400893</v>
+        <v>-23.19027715311664</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.6492596350801786</v>
+        <v>-0.4638055430623328</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.743147302463937</v>
+        <v>5.336489749730713</v>
       </c>
     </row>
     <row r="8">
@@ -1227,56 +1229,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.4324734446130501</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2503793626707132</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.3171471927162368</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.05103668261562988</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3228394979812819</v>
+        <v>0.3208187904059995</v>
       </c>
       <c r="R8" t="n">
-        <v>0.354442885408602</v>
+        <v>0.3539467366738068</v>
       </c>
       <c r="S8" t="n">
-        <v>0.322717616610116</v>
+        <v>0.3252344729201937</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.09128499067175994</v>
+        <v>0.1035673740030936</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.09128499067175994</v>
+        <v>0.1035673740030936</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.354442885408602</v>
+        <v>0.3539467366738068</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1284,13 +1286,13 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>10.61516874888336</v>
+        <v>12.32134283430234</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.2123033749776672</v>
+        <v>0.2464268566860469</v>
       </c>
       <c r="AD8" t="n">
-        <v>7.641934967067556</v>
+        <v>7.75830960250165</v>
       </c>
     </row>
     <row r="9">
@@ -1335,47 +1337,47 @@
         <v>3.9</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5513666352497643</v>
+        <v>0.5574781823653325</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2403393025447691</v>
+        <v>0.2430033102618116</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2082940622054665</v>
+        <v>0.1995185073728558</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0668677727501259</v>
+        <v>0.05517186631737725</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3653147247787745</v>
+        <v>0.3866457809441306</v>
       </c>
       <c r="R9" t="n">
-        <v>0.341329200668983</v>
+        <v>0.331929516360415</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2933560745522424</v>
+        <v>0.2814247026954545</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.1860519104709897</v>
+        <v>-0.1708324014212019</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1860519104709897</v>
+        <v>-0.1708324014212019</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3653147247787745</v>
+        <v>0.3866457809441306</v>
       </c>
       <c r="Z9" t="n">
         <v>1.7</v>
@@ -1386,13 +1388,13 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>-54.1378525537262</v>
+        <v>-48.95745319928258</v>
       </c>
       <c r="AC9" t="n">
-        <v>-1.082757051074524</v>
+        <v>-0.9791490639856515</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.496782676235883</v>
+        <v>3.774275956413769</v>
       </c>
     </row>
     <row r="10">
@@ -1431,7 +1433,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="J10" t="n">
         <v>3.8</v>
@@ -1440,44 +1442,44 @@
         <v>3.2</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4586948321388156</v>
+        <v>0.4527177959791511</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2474537910222558</v>
+        <v>0.2501861504095309</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2938513768389287</v>
+        <v>0.297096053611318</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06346277278562251</v>
+        <v>0.05184837092731831</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3402871651523205</v>
+        <v>0.3343018277056561</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3505249816386133</v>
+        <v>0.3551775591051438</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3091878532090662</v>
+        <v>0.3105206131892001</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1030711906163576</v>
+        <v>0.1049914086956129</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1030711906163576</v>
+        <v>0.1049914086956129</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3505249816386133</v>
+        <v>0.3551775591051438</v>
       </c>
       <c r="Z10" t="n">
         <v>3.8</v>
@@ -1488,931 +1490,13 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>11.85696179381181</v>
+        <v>12.48838302141237</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.2371392358762362</v>
+        <v>0.2497676604282473</v>
       </c>
       <c r="AD10" t="n">
-        <v>7.726680523759429</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>v3DAZKP9</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45604.6875</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>union berlin</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>freiburg</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>59</v>
-      </c>
-      <c r="F11" t="n">
-        <v>591</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.3901639344262295</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.2754098360655738</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.3344262295081967</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.06792717086834732</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.2990086924769021</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.3492599605227888</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.351731347000309</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
-        <v>0.01730511749211228</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.01730511749211228</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.351731347000309</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>-0.8417904666186082</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>-0.01683580933237216</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>6.852882439337695</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>biQrHC9r</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45605.47916666666</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>bochum</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>bayer leverkusen</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>59</v>
-      </c>
-      <c r="F12" t="n">
-        <v>591</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.134020618556701</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.1443298969072165</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.7216494845360825</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.06593406593406592</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.0850220051071499</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.3981345369630913</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.5168434579297588</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
-        <v>-0.2048060266063236</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-0.2048060266063236</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.5168434579297588</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>-109.3678348971045</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>-2.187356697942089</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.394535630135924</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>nee3ysec</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45605.47916666666</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>mainz</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>dortmund</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>59</v>
-      </c>
-      <c r="F13" t="n">
-        <v>591</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.2951006456513482</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.2552221800227877</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.449677174325864</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.05896074646074645</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.1885635084915402</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.3771168515935309</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.4343196399149289</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>-0.01535753441093507</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-0.01535753441093507</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.4343196399149289</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB13" t="n">
-        <v>-7.993523288968108</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>-0.1598704657793621</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>6.359794309307781</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>6HTjFjve</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45605.47916666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>st  pauli</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>bayern munich</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>59</v>
-      </c>
-      <c r="F14" t="n">
-        <v>591</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>11</v>
-      </c>
-      <c r="J14" t="n">
-        <v>6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.08595988538681948</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.157593123209169</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.7564469914040115</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.05757575757575761</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.08419956102360941</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.4043108131538904</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.5114896258225001</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>-0.2449573655815114</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-0.2449573655815114</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.5114896258225001</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>-144.2551870887499</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>-2.885103741774999</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.7311189963166821</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YmumZjET</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45605.47916666666</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>werder bremen</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>holstein kiel</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>59</v>
-      </c>
-      <c r="F15" t="n">
-        <v>591</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>5</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.6013630896699185</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2098089001737271</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.1888280101563544</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.0591648973814578</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.4314942378384312</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.320029954525088</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.2484758076364808</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>-0.1698688518314873</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.1698688518314873</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.4314942378384312</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>-56.5884292269584</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>-1.131768584539168</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.370313604417392</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>j5mWxZE4</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45605.60416666666</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>rb leipzig</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>b  monchengladbach</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>59</v>
-      </c>
-      <c r="F16" t="n">
-        <v>591</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="K16" t="n">
-        <v>6</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.6464417351857102</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.1973348454777431</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.1562234193365466</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.06684815486993356</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.467417631311846</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.305670415332254</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.2269119533559001</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>-0.1790241038738642</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-0.1790241038738642</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.467417631311846</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB16" t="n">
-        <v>-71.60987435507185</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>-1.432197487101437</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.664302876095882</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>UJQITUyi</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45606.47916666666</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>augsburg</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>hoffenheim</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>59</v>
-      </c>
-      <c r="F17" t="n">
-        <v>591</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.4512126339537507</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.2526790750141004</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.2961082910321489</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.05535714285714288</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.3027506963255377</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.3530808096825865</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.3441684939918758</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>0.1004017346684862</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.1004017346684862</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.3530808096825865</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB17" t="n">
-        <v>11.78374677489817</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0.2356749354979633</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>7.721690636189637</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>UkaNveph</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45606.5625</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>stuttgart</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>eintracht frankfurt</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>59</v>
-      </c>
-      <c r="F18" t="n">
-        <v>591</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.5228187919463088</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.2295302013422819</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.2476510067114094</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.06261588931678785</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.3246755134225318</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.3481061763274639</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.3272183102500044</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="n">
-        <v>0.118575974985182</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.118575974985182</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.3481061763274639</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB18" t="n">
-        <v>13.78178461105168</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0.2756356922210336</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>7.857539930949808</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xMovyDqH</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45606.64583333334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>heidenheim</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>wolfsburg</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>59</v>
-      </c>
-      <c r="F19" t="n">
-        <v>591</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.3664921465968586</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.2670157068062827</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.3664921465968586</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.07002801120448199</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.2701385049118458</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.3664490687969839</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.3634124262911704</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="n">
-        <v>0.09943336199070124</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0.09943336199070124</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.3664490687969839</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB19" t="n">
-        <v>11.30286963157775</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0.226057392631555</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>7.688895928064805</v>
+        <v>7.76967800676168</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,16 +565,6 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>stake_to_bet_raw</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>stake_to_bet_norm</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
           <t>stake_to_bet</t>
         </is>
       </c>
@@ -582,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IHYEDIog</t>
+          <t>v3DAZKP9</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45597.6875</v>
+        <v>45604.6875</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bayer leverkusen</t>
+          <t>union berlin</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>stuttgart</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -615,56 +605,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.55</v>
+        <v>2.38</v>
       </c>
       <c r="J2" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6111289803795432</v>
+        <v>0.3967168262653899</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1994210357027983</v>
+        <v>0.2777017783857729</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1894499839176584</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05568760611205437</v>
+        <v>0.05911330049261077</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5042694737416966</v>
+        <v>0.2832338194838178</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3214848863097585</v>
+        <v>0.3599540243199423</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1742456399485449</v>
+        <v>0.35681215619624</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1068595066378466</v>
+        <v>0.08225224593416935</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1068595066378466</v>
+        <v>0.08225224593416935</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5042694737416966</v>
+        <v>0.3599540243199423</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.55</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -672,32 +662,26 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-39.70587558188549</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-0.7941175116377098</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>4.302620562970569</v>
+        <v>1.397047696174947</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jVWMBdG5</t>
+          <t>biQrHC9r</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bayern munich</t>
+          <t>bochum</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>union berlin</t>
+          <t>bayer leverkusen</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -717,56 +701,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.18</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>1.27</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8012162051113485</v>
+        <v>0.118454363757495</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1260580162708521</v>
+        <v>0.1353764157228514</v>
       </c>
       <c r="N3" t="n">
-        <v>0.07272577861779932</v>
+        <v>0.7461692205196536</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05771403737505443</v>
+        <v>0.05525871766029233</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5784697536459851</v>
+        <v>0.08413534972857876</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2684906159244962</v>
+        <v>0.4044252063169132</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1530396304295186</v>
+        <v>0.511439443954508</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.2227464514653634</v>
+        <v>-0.2347297765651456</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2227464514653634</v>
+        <v>-0.2347297765651456</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5784697536459851</v>
+        <v>0.511439443954508</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -774,32 +758,26 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-176.3364948320765</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-3.526729896641531</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.3947759032083871</v>
+        <v>0.1629316684886378</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>485V7EFU</t>
+          <t>nee3ysec</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>eintracht frankfurt</t>
+          <t>mainz</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>bochum</t>
+          <t>dortmund</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -819,56 +797,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.33</v>
+        <v>3.4</v>
       </c>
       <c r="J4" t="n">
-        <v>5.75</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>7.5</v>
+        <v>2.05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7099057574385776</v>
+        <v>0.2775479503572772</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1642042882423145</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1258899543191078</v>
+        <v>0.46032342986085</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05912607605971454</v>
+        <v>0.05970030288538175</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4558685645880888</v>
+        <v>0.1800605865798936</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3050879621116344</v>
+        <v>0.384142145981388</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2390434733002767</v>
+        <v>0.4357972674387184</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.2540371928504888</v>
+        <v>-0.02452616242213157</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2540371928504888</v>
+        <v>-0.02452616242213157</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4558685645880888</v>
+        <v>0.4357972674387184</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.33</v>
+        <v>2.05</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -876,32 +854,26 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-119.3014573023763</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-2.386029146047525</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.164433974946298</v>
+        <v>1.501028171805223</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8MVuSH0n</t>
+          <t>6HTjFjve</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>hoffenheim</t>
+          <t>st  pauli</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>st  pauli</t>
+          <t>bayern munich</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -921,56 +893,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.83</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>1.27</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5157087602632829</v>
+        <v>0.08639711319471147</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2483544819162652</v>
+        <v>0.1652814339377089</v>
       </c>
       <c r="N5" t="n">
-        <v>0.235936757820452</v>
+        <v>0.7483214528675796</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05960598216853596</v>
+        <v>0.05222370919050134</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4051067889656215</v>
+        <v>0.0810188790521271</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3504369266995791</v>
+        <v>0.4049709805722032</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2444562843347994</v>
+        <v>0.5140101403756697</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.1106019712976614</v>
+        <v>-0.2343113124919098</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1106019712976614</v>
+        <v>-0.2343113124919098</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4051067889656215</v>
+        <v>0.5140101403756697</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.83</v>
+        <v>1.27</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -978,32 +950,26 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-31.16320195095333</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-0.6232640390190666</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>4.824463704622143</v>
+        <v>0.1761572854563473</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2q7yHiho</t>
+          <t>YmumZjET</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>werder bremen</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>holstein kiel</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>heidenheim</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1023,56 +989,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="K6" t="n">
-        <v>2.45</v>
+        <v>4.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3506261180679785</v>
+        <v>0.5830269494941478</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2629695885509839</v>
+        <v>0.2181301750994271</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3864042933810375</v>
+        <v>0.1988428754064251</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0563114134542706</v>
+        <v>0.05875714862384762</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2680619258462033</v>
+        <v>0.4225487020193431</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3598475668993034</v>
+        <v>0.3240030133796011</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3720905072544934</v>
+        <v>0.2534482846010558</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.01431378612654416</v>
+        <v>-0.1604782474748047</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.01431378612654416</v>
+        <v>-0.1604782474748047</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3720905072544934</v>
+        <v>0.4225487020193431</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.45</v>
+        <v>1.62</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1080,32 +1046,26 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>-6.095052222516633</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-0.1219010444503327</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>6.490345962294962</v>
+        <v>0.3942980193213431</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AoSdOZaB</t>
+          <t>j5mWxZE4</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.60416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>wolfsburg</t>
+          <t>rb leipzig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>augsburg</t>
+          <t>b  monchengladbach</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1125,58 +1085,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4751131221719458</v>
+        <v>0.6346967559943583</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2533936651583711</v>
+        <v>0.2087447108603667</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2714932126696833</v>
+        <v>0.156558533145275</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05238095238095219</v>
+        <v>0.0645645645645645</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3840486142344168</v>
+        <v>0.4593263614046247</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3421801725583295</v>
+        <v>0.3181009218034846</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2737712132072537</v>
+        <v>0.2225727167918907</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.09106450793752902</v>
+        <v>-0.1753703945897336</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.09106450793752902</v>
+        <v>-0.1753703945897336</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3840486142344168</v>
+        <v>0.4593263614046247</v>
       </c>
       <c r="Z7" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1184,32 +1142,26 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>-23.19027715311664</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-0.4638055430623328</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>5.336489749730713</v>
+        <v>0.4214405542530009</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dr2N9zoI</t>
+          <t>UJQITUyi</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45598.60416666666</v>
+        <v>45606.47916666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dortmund</t>
+          <t>augsburg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>rb leipzig</t>
+          <t>hoffenheim</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1229,56 +1181,58 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4324734446130501</v>
+        <v>0.4512126339537507</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2503793626707132</v>
+        <v>0.2526790750141004</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3171471927162368</v>
+        <v>0.2961082910321489</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05103668261562988</v>
+        <v>0.05535714285714288</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3208187904059995</v>
+        <v>0.2659409384668499</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3539467366738068</v>
+        <v>0.3510185330841873</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3252344729201937</v>
+        <v>0.3830405284489628</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
       <c r="V8" t="n">
-        <v>0.1035673740030936</v>
+        <v>0.08693223741681388</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1035673740030936</v>
+        <v>0.08693223741681388</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3539467366738068</v>
+        <v>0.3830405284489628</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1286,32 +1240,26 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>12.32134283430234</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.2464268566860469</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>7.75830960250165</v>
+        <v>1.486650659962105</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>GnZmQeVb</t>
+          <t>UkaNveph</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45599.47916666666</v>
+        <v>45606.5625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>freiburg</t>
+          <t>stuttgart</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>mainz</t>
+          <t>eintracht frankfurt</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1331,56 +1279,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5574781823653325</v>
+        <v>0.5293737895416398</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2430033102618116</v>
+        <v>0.2324080051646223</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1995185073728558</v>
+        <v>0.2382182052937379</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05517186631737725</v>
+        <v>0.04945799457994582</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3866457809441306</v>
+        <v>0.3145255144579812</v>
       </c>
       <c r="R9" t="n">
-        <v>0.331929516360415</v>
+        <v>0.3572530097404699</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2814247026954545</v>
+        <v>0.3282214758015489</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.1708324014212019</v>
+        <v>0.1248450045758476</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1708324014212019</v>
+        <v>0.1248450045758476</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3866457809441306</v>
+        <v>0.3572530097404699</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1388,32 +1336,26 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>-48.95745319928258</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-0.9791490639856515</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.774275956413769</v>
+        <v>1.386564562383858</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>raQ4MDUN</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45599.5625</v>
+        <v>45606.64583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>b  monchengladbach</t>
+          <t>heidenheim</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>werder bremen</t>
+          <t>wolfsburg</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1433,56 +1375,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4527177959791511</v>
+        <v>0.3593501499808749</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2501861504095309</v>
+        <v>0.2700259698427717</v>
       </c>
       <c r="N10" t="n">
-        <v>0.297096053611318</v>
+        <v>0.3706238801763534</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05184837092731831</v>
+        <v>0.05809928534151299</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3343018277056561</v>
+        <v>0.2609290332921262</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3551775591051438</v>
+        <v>0.3638643978490307</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3105206131892001</v>
+        <v>0.3752065688588429</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1049914086956129</v>
+        <v>0.004582688682489511</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1049914086956129</v>
+        <v>0.004582688682489511</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3551775591051438</v>
+        <v>0.3752065688588429</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1490,13 +1432,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>12.48838302141237</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.2497676604282473</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>7.76967800676168</v>
+        <v>1.456245623602304</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>1.397047696174947</v>
+        <v>1.676625605937493</v>
       </c>
     </row>
     <row r="3">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0.1629316684886378</v>
+        <v>0.1955376385173613</v>
       </c>
     </row>
     <row r="4">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>1.501028171805223</v>
+        <v>1.801414708297137</v>
       </c>
     </row>
     <row r="5">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0.1761572854563473</v>
+        <v>0.2114099728142472</v>
       </c>
     </row>
     <row r="6">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0.3942980193213431</v>
+        <v>0.4732051435141655</v>
       </c>
     </row>
     <row r="7">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>0.4214405542530009</v>
+        <v>0.5057794566181982</v>
       </c>
     </row>
     <row r="8">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>1.486650659962105</v>
+        <v>1.784159961324759</v>
       </c>
     </row>
     <row r="9">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>1.386564562383858</v>
+        <v>1.664044581973364</v>
       </c>
     </row>
     <row r="10">
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>1.456245623602304</v>
+        <v>1.747670253314161</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/predicciones.xlsx
+++ b/data/germany/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,53 +608,51 @@
         <v>2.38</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3967168262653899</v>
+        <v>0.3999920597109735</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2777017783857729</v>
+        <v>0.2929172621883437</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3255813953488372</v>
+        <v>0.3070906781006829</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05911330049261077</v>
+        <v>0.05044102008048879</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2832338194838178</v>
+        <v>0.2451816872879612</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3599540243199423</v>
+        <v>0.2823895203883839</v>
       </c>
       <c r="S2" t="n">
-        <v>0.35681215619624</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
+        <v>0.4724287923236548</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.08225224593416935</v>
+        <v>0.165338114222972</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.08225224593416935</v>
+        <v>0.165338114222972</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3599540243199423</v>
+        <v>0.4724287923236548</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -662,7 +660,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>1.676625605937493</v>
+        <v>7.086132807597141</v>
       </c>
     </row>
     <row r="3">
@@ -701,56 +699,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="K3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0.118454363757495</v>
+        <v>0.09938837920489296</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1353764157228514</v>
+        <v>0.1452599388379205</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7461692205196536</v>
+        <v>0.7553516819571866</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05525871766029233</v>
+        <v>0.05910931174089074</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.08413534972857876</v>
+        <v>0.05423050087842236</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4044252063169132</v>
+        <v>0.2116805041199112</v>
       </c>
       <c r="S3" t="n">
-        <v>0.511439443954508</v>
+        <v>0.7340889950016665</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.2347297765651456</v>
+        <v>-0.02126268695552014</v>
       </c>
       <c r="W3" t="n">
         <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2347297765651456</v>
+        <v>-0.02126268695552014</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.511439443954508</v>
+        <v>0.7340889950016665</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -758,7 +756,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0.1955376385173613</v>
+        <v>4.056489044872412</v>
       </c>
     </row>
     <row r="4">
@@ -797,56 +795,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J4" t="n">
         <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2775479503572772</v>
+        <v>0.2686567164179104</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.2611940298507463</v>
       </c>
       <c r="N4" t="n">
-        <v>0.46032342986085</v>
+        <v>0.4701492537313433</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05970030288538175</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1800605865798936</v>
+        <v>0.1379586541384551</v>
       </c>
       <c r="R4" t="n">
-        <v>0.384142145981388</v>
+        <v>0.2194789658739746</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4357972674387184</v>
+        <v>0.6425623799875704</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.02452616242213157</v>
+        <v>0.1724131262562271</v>
       </c>
       <c r="W4" t="n">
         <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.02452616242213157</v>
+        <v>0.1724131262562271</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4357972674387184</v>
+        <v>0.6425623799875704</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -854,7 +852,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>1.801414708297137</v>
+        <v>8.326343031327992</v>
       </c>
     </row>
     <row r="5">
@@ -893,56 +891,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="J5" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="K5" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08639711319471147</v>
+        <v>0.09946733340580496</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1652814339377089</v>
+        <v>0.125991955647353</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7483214528675796</v>
+        <v>0.774540710946842</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05222370919050134</v>
+        <v>0.05826862237561126</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0810188790521271</v>
+        <v>0.04048311270516788</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4049709805722032</v>
+        <v>0.08763839322117328</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5140101403756697</v>
+        <v>0.8718784940736588</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.2343113124919098</v>
+        <v>0.09733778312681685</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2343113124919098</v>
+        <v>0.09733778312681685</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5140101403756697</v>
+        <v>0.8718784940736588</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -950,7 +948,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0.2114099728142472</v>
+        <v>7.882685166130789</v>
       </c>
     </row>
     <row r="6">
@@ -989,56 +987,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5830269494941478</v>
+        <v>0.5968169761273209</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2181301750994271</v>
+        <v>0.2122015915119363</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1988428754064251</v>
+        <v>0.1909814323607427</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05875714862384762</v>
+        <v>0.04722222222222228</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4225487020193431</v>
+        <v>0.5305649849773443</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3240030133796011</v>
+        <v>0.2977688303422035</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2534482846010558</v>
+        <v>0.1716661846804522</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.1604782474748047</v>
+        <v>-0.0662519911499766</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1604782474748047</v>
+        <v>-0.0662519911499766</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4225487020193431</v>
+        <v>0.5305649849773443</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1046,7 +1044,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0.4732051435141655</v>
+        <v>1.659731377358987</v>
       </c>
     </row>
     <row r="7">
@@ -1085,56 +1083,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6346967559943583</v>
+        <v>0.5964499519258584</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2087447108603667</v>
+        <v>0.2162647631694221</v>
       </c>
       <c r="N7" t="n">
-        <v>0.156558533145275</v>
+        <v>0.1872852849047196</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0645645645645645</v>
+        <v>0.06788955737632563</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4593263614046247</v>
+        <v>0.5443949375586612</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3181009218034846</v>
+        <v>0.3369520895012321</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2225727167918907</v>
+        <v>0.1186529729401067</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.1753703945897336</v>
+        <v>-0.05205501436719717</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1753703945897336</v>
+        <v>-0.05205501436719717</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4593263614046247</v>
+        <v>0.5443949375586612</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1142,7 +1140,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>0.5057794566181982</v>
+        <v>2.101093000561703</v>
       </c>
     </row>
     <row r="8">
@@ -1181,37 +1179,37 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="J8" t="n">
         <v>3.75</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4512126339537507</v>
+        <v>0.4592557701365991</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2526790750141004</v>
+        <v>0.2510598210080075</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2961082910321489</v>
+        <v>0.2896844088553933</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05535714285714288</v>
+        <v>0.06216385240775502</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2659409384668499</v>
+        <v>0.3713369211320147</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3510185330841873</v>
+        <v>0.3192392031647657</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3830405284489628</v>
+        <v>0.3094238757032194</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1220,19 +1218,19 @@
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>0.08693223741681388</v>
+        <v>-0.08791884900458441</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.08693223741681388</v>
+        <v>-0.08791884900458441</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3830405284489628</v>
+        <v>0.3713369211320147</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1240,7 +1238,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>1.784159961324759</v>
+        <v>0.1228845319604818</v>
       </c>
     </row>
     <row r="9">
@@ -1279,56 +1277,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5293737895416398</v>
+        <v>0.5028882093102276</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2324080051646223</v>
+        <v>0.2388718994223581</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2382182052937379</v>
+        <v>0.2582398912674141</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04945799457994582</v>
+        <v>0.04658605974395447</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3145255144579812</v>
+        <v>0.3899514257709533</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3572530097404699</v>
+        <v>0.3914355888829029</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3282214758015489</v>
+        <v>0.2186129853461438</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1248450045758476</v>
+        <v>0.1525636894605448</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1248450045758476</v>
+        <v>0.1525636894605448</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3572530097404699</v>
+        <v>0.3914355888829029</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1336,7 +1334,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>1.664044581973364</v>
+        <v>6.260564667031762</v>
       </c>
     </row>
     <row r="10">
@@ -1375,56 +1373,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3593501499808749</v>
+        <v>0.3344262295081967</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2700259698427717</v>
+        <v>0.2754098360655738</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3706238801763534</v>
+        <v>0.3901639344262295</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05809928534151299</v>
+        <v>0.06792717086834732</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2609290332921262</v>
+        <v>0.2903942023150049</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3638643978490307</v>
+        <v>0.2457897659363611</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3752065688588429</v>
+        <v>0.463816031748634</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.004582688682489511</v>
+        <v>0.07365209732240446</v>
       </c>
       <c r="W10" t="n">
         <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>0.004582688682489511</v>
+        <v>0.07365209732240446</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3752065688588429</v>
+        <v>0.463816031748634</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1432,7 +1430,681 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>1.747670253314161</v>
+        <v>4.740152631489074</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EuQnZBVQ</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45618.6875</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>bayern munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>augsburg</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" t="n">
+        <v>591</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" t="n">
+        <v>15</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.8450704225352113</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.09295774647887325</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.06197183098591549</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.07575757575757569</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4207096998051714</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3667474441088974</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2125428560859311</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.4243607227300398</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.4243607227300398</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4207096998051714</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2qNaDU87</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bayer leverkusen</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>heidenheim</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F12" t="n">
+        <v>591</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7784120394395433</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1582771146860404</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.06331084587441618</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0530054644808744</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.6939419031995516</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.2565956046804507</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.04946249211999764</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.08447013623999167</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.08447013623999167</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.6939419031995516</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.225383488997406</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pOGITkgl</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>dortmund</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F13" t="n">
+        <v>591</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5746381507885073</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.225750702095485</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1996111471160078</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.05468215994531778</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.5353976182872061</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.2974335586995293</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1671688230132646</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.03924053250130122</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.03924053250130122</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.5353976182872061</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.365221801762508</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>E38ZP7hD</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>hoffenheim</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>rb leipzig</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>59</v>
+      </c>
+      <c r="F14" t="n">
+        <v>591</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2299619616899878</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2548227143051216</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.5152153240048907</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06062079672635434</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.1850353483586111</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3068453998404827</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.5081192518009061</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.00709607220398456</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.00709607220398456</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.5081192518009061</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.998343518656049</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>fwAoyY0E</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>bochum</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>59</v>
+      </c>
+      <c r="F15" t="n">
+        <v>591</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K15" t="n">
+        <v>12</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.7710892921400297</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.1505166298257338</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.07839407803423636</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06300546448087441</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.5040588622807577</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3973333315804643</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.09860780613877793</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-0.2670304298592721</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.2670304298592721</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.5040588622807577</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SrjMmBpK</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>wolfsburg</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>union berlin</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>59</v>
+      </c>
+      <c r="F16" t="n">
+        <v>591</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4512877939529675</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2430011198208287</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.3057110862262038</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.05518137776202292</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.347094786384264</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2445510541796648</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4083541594360711</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.1026430732098673</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.1026430732098673</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4083541594360711</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>5.118290326722128</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6w5RRTN0</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45619.60416666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>eintracht frankfurt</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>werder bremen</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>59</v>
+      </c>
+      <c r="F17" t="n">
+        <v>591</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.5830269494941478</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2181301750994271</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1988428754064251</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.05875714862384762</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.3959207641875817</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.2899290307132603</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.314150205099158</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-0.1871061853065661</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.1871061853065661</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.3959207641875817</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
